--- a/docs/testing-strategy/kiwishare-release-test-results-v0.2.xlsx
+++ b/docs/testing-strategy/kiwishare-release-test-results-v0.2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R7a77e86ae90548a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data &amp; Setup" sheetId="2" r:id="R4021531915df494e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="3" r:id="R19eec844b25042c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Log" sheetId="4" r:id="R72dae7d4a4614e54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Ra10e6dbd2e3d4a44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data &amp; Setup" sheetId="2" r:id="Rfaa681c271dc4c06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="3" r:id="Rfa5341b623cd40d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Log" sheetId="4" r:id="Rd6ff77a5a8d349ce"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1219,11 +1219,46 @@
       </x:c>
     </x:row>
     <x:row r="57" ht="15.75" customHeight="1"/>
-    <x:row r="58" ht="15.75" customHeight="1"/>
-    <x:row r="59" ht="15.75" customHeight="1"/>
-    <x:row r="60" ht="15.75" customHeight="1"/>
-    <x:row r="61" ht="15.75" customHeight="1"/>
-    <x:row r="62" ht="15.75" customHeight="1"/>
+    <x:row r="58" ht="15" hidden="0" customHeight="1">
+      <x:c r="A58" s="29" t="str">
+        <x:v>9. Automated Regression Evidence</x:v>
+      </x:c>
+      <x:c r="B58" s="29" t="str">
+        <x:v>Local pre-push run on 2026-10-02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="15" hidden="0" customHeight="1">
+      <x:c r="A59" s="30" t="str">
+        <x:v>Flutter tests</x:v>
+      </x:c>
+      <x:c r="B59" s="31" t="str">
+        <x:v>451 passed; 0 failed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="15" hidden="0" customHeight="1">
+      <x:c r="A60" s="30" t="str">
+        <x:v>Server Jest</x:v>
+      </x:c>
+      <x:c r="B60" s="31" t="str">
+        <x:v>24 test suites passed; 264 tests passed; 0 failed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="15" hidden="0" customHeight="1">
+      <x:c r="A61" s="30" t="str">
+        <x:v>Source revision</x:v>
+      </x:c>
+      <x:c r="B61" s="31" t="str">
+        <x:v>docs/consolidated-test-evidence based on origin/pre 8bcb615</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="15" hidden="0" customHeight="1">
+      <x:c r="A62" s="30" t="str">
+        <x:v>Web evidence gap</x:v>
+      </x:c>
+      <x:c r="B62" s="31" t="str">
+        <x:v>Web tests are not included in test:all; retain manual and CI evidence separately.</x:v>
+      </x:c>
+    </x:row>
     <x:row r="63" ht="15.75" customHeight="1"/>
     <x:row r="64" ht="15.75" customHeight="1"/>
     <x:row r="65" ht="15.75" customHeight="1"/>

--- a/docs/testing-strategy/kiwishare-release-test-results-v0.2.xlsx
+++ b/docs/testing-strategy/kiwishare-release-test-results-v0.2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Ra10e6dbd2e3d4a44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data &amp; Setup" sheetId="2" r:id="Rfaa681c271dc4c06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="3" r:id="Rfa5341b623cd40d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Log" sheetId="4" r:id="Rd6ff77a5a8d349ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Rdd307d4777844405"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data &amp; Setup" sheetId="2" r:id="R201d8dcc24af4d16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="3" r:id="R882edabbf8e04efe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Log" sheetId="4" r:id="R2dc9307139ac4bc0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,6 +13,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
+    <x:t xml:space="preserve">KiwiShare — Release Test Plan / UAT Checklist (v0.2)</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">1. Test Object</x:t>
   </x:si>
   <x:si>
@@ -215,6 +218,36 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">100% P0 Pass; P1 Pass or accepted deferral; zero open S1/S2 defects; all evidence linked.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">9. Automated Regression Evidence</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Local pre-push run on 2026-10-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Flutter tests</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">451 passed; 0 failed</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Server Jest</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">24 test suites passed; 264 tests passed; 0 failed</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Source revision</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">docs/consolidated-test-evidence based on origin/pre 8bcb615</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Web evidence gap</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Web tests are not included in test:all; retain manual and CI evidence separately.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Test Data &amp; Environment Setup — do this BEFORE Round 1</x:t>
@@ -403,6 +436,45 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Replace with friendly message</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-B-002</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-013</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Profile</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Registration accepted display names longer than 30 characters while Profile editing capped them at 30.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Register with a 32-character nickname, then edit the nickname in Profile and enter a 33rd character.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Closed</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Fixed in PR #309 by applying the 2-30 character limit consistently; the linked test case now passes.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-B-003</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-008</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Floating labels overlapped adjacent fields in the change-password dialog.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Open Profile &gt; Change password and inspect spacing between the three password fields.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">S4 Cosmetic</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Fixed in PR #309 by restoring spacing between fields; the linked test case now passes.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -410,10 +482,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:numFmts count="2">
-    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
-    <x:numFmt numFmtId="201" formatCode="0.0%"/>
+    <x:numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <x:numFmt numFmtId="165" formatCode="0.0%"/>
   </x:numFmts>
-  <x:fonts count="10">
+  <x:fonts count="11">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -443,6 +515,7 @@
     </x:font>
     <x:font>
       <x:b/>
+      <x:sz val="11"/>
       <x:color theme="1"/>
       <x:name val="Calibri"/>
       <x:scheme val="minor"/>
@@ -454,11 +527,13 @@
     </x:font>
     <x:font>
       <x:b/>
+      <x:sz val="11"/>
       <x:color rgb="FFC00000"/>
       <x:name val="Calibri"/>
       <x:scheme val="minor"/>
     </x:font>
     <x:font>
+      <x:sz val="11"/>
       <x:color theme="1"/>
       <x:name val="Calibri"/>
       <x:scheme val="minor"/>
@@ -476,13 +551,19 @@
       <x:name val="Calibri"/>
       <x:scheme val="minor"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
   </x:fonts>
   <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
-      <x:patternFill patternType="lightGray"/>
+      <x:patternFill patternType="gray125"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -496,7 +577,13 @@
     </x:fill>
   </x:fills>
   <x:borders count="2">
-    <x:border/>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
     <x:border>
       <x:left style="thin">
         <x:color rgb="FFBBBBBB"/>
@@ -510,88 +597,68 @@
       <x:bottom style="thin">
         <x:color rgb="FFBBBBBB"/>
       </x:bottom>
+      <x:diagonal/>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
+  <x:cellXfs count="25">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1" shrinkToFit="0"/>
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="top" wrapText="1" shrinkToFit="0"/>
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1" shrinkToFit="0"/>
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="top" wrapText="1" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="top" wrapText="1" shrinkToFit="0"/>
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="top" wrapText="1" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="bottom" wrapText="0"/>
+    <x:xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="bottom" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="bottom" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="bottom" wrapText="0"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="bottom" wrapText="0"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="bottom" wrapText="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="bottom" wrapText="0"/>
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="bottom" wrapText="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="bottom" wrapText="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="bottom" wrapText="1"/>
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
@@ -602,21 +669,38 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="4">
+  <x:dxfs count="9">
+    <x:dxf>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFEB9C"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFEB9C"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
     <x:dxf>
       <x:fill>
         <x:patternFill>
           <x:bgColor rgb="FFC6EFCE"/>
         </x:patternFill>
       </x:fill>
-      <x:border/>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
@@ -624,7 +708,13 @@
           <x:bgColor rgb="FFFFC7CE"/>
         </x:patternFill>
       </x:fill>
-      <x:border/>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFF2F2F2"/>
+        </x:patternFill>
+      </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
@@ -632,15 +722,20 @@
           <x:bgColor rgb="FFFFEB9C"/>
         </x:patternFill>
       </x:fill>
-      <x:border/>
     </x:dxf>
     <x:dxf>
       <x:fill>
         <x:patternFill>
-          <x:bgColor rgb="FFF2F2F2"/>
+          <x:bgColor rgb="FFFFC7CE"/>
         </x:patternFill>
       </x:fill>
-      <x:border/>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
     </x:dxf>
   </x:dxfs>
 </x:styleSheet>
@@ -839,424 +934,424 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultColWidth="14.430000305175781" defaultRowHeight="15"/>
+  <x:sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="78" hidden="0" customWidth="1"/>
-    <x:col min="3" max="26" width="8.710000038146973" customWidth="1"/>
+    <x:col min="1" max="1" width="30" customWidth="1"/>
+    <x:col min="2" max="2" width="78" customWidth="1"/>
+    <x:col min="3" max="26" width="8.6640625" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="1" t="str">
-        <x:v>KiwiShare — Release Test Plan / UAT Checklist (v0.2)</x:v>
+    <x:row r="1" ht="19">
+      <x:c r="A1" s="1" t="s">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="3" t="s">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="16">
       <x:c r="A4" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="16">
       <x:c r="A5" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="32">
       <x:c r="A6" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="16">
       <x:c r="A7" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="32">
       <x:c r="A8" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="32">
       <x:c r="A9" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="3" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="32">
       <x:c r="A12" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B12" s="5" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="16">
       <x:c r="A13" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B13" s="5" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="32">
       <x:c r="A14" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B14" s="5" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="16">
       <x:c r="A15" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="3" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="16">
       <x:c r="A18" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="5" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="16">
       <x:c r="A19" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B19" s="5" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="16">
       <x:c r="A20" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B20" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15.75" customHeight="1">
       <x:c r="A21" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B21" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15.75" customHeight="1">
       <x:c r="A22" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B22" s="5" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15.75" customHeight="1">
       <x:c r="A23" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B23" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15.75" customHeight="1">
       <x:c r="A24" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B24" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15.75" customHeight="1">
       <x:c r="A25" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B25" s="5" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="15.75" customHeight="1"/>
     <x:row r="27" ht="15.75" customHeight="1">
       <x:c r="A27" s="3" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15.75" customHeight="1">
       <x:c r="A28" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B28" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="15.75" customHeight="1">
       <x:c r="A29" s="4" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B29" s="5" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15.75" customHeight="1">
       <x:c r="A30" s="4" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B30" s="5" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15.75" customHeight="1">
       <x:c r="A31" s="4" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B31" s="5" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15.75" customHeight="1">
       <x:c r="A32" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B32" s="5" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="15.75" customHeight="1"/>
     <x:row r="34" ht="15.75" customHeight="1">
       <x:c r="A34" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="15.75" customHeight="1">
       <x:c r="A35" s="4" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B35" s="5" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1">
       <x:c r="A36" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B36" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="15.75" customHeight="1">
       <x:c r="A37" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B37" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15.75" customHeight="1"/>
     <x:row r="39" ht="15.75" customHeight="1">
       <x:c r="A39" s="3" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15.75" customHeight="1">
       <x:c r="A40" s="4" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B40" s="5" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="15.75" customHeight="1">
       <x:c r="A41" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B41" s="5" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="15.75" customHeight="1">
       <x:c r="A42" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B42" s="5" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="15.75" customHeight="1"/>
     <x:row r="44" ht="15.75" customHeight="1">
       <x:c r="A44" s="3" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="15.75" customHeight="1">
       <x:c r="A45" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B45" s="5" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="15.75" customHeight="1">
       <x:c r="A46" s="4" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B46" s="5" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
-      <x:c r="A47" s="29" t="str">
+      <x:c r="A47" s="22" t="str">
         <x:v>8. Consolidated Test Results</x:v>
       </x:c>
-      <x:c r="B47" s="29" t="str">
-        <x:v>As of 2026-09-19</x:v>
+      <x:c r="B47" s="22" t="str">
+        <x:v>As of 2026-10-02</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
-      <x:c r="A48" s="30" t="str">
+      <x:c r="A48" s="23" t="str">
         <x:v>Total test cases</x:v>
       </x:c>
-      <x:c r="B48" s="31" t="n">
+      <x:c r="B48" s="24" t="n">
         <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
-      <x:c r="A49" s="30" t="str">
+      <x:c r="A49" s="23" t="str">
         <x:v>Executed</x:v>
       </x:c>
-      <x:c r="B49" s="31" t="n">
-        <x:v>33</x:v>
+      <x:c r="B49" s="24" t="n">
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
-      <x:c r="A50" s="30" t="str">
+      <x:c r="A50" s="23" t="str">
         <x:v>Passed</x:v>
       </x:c>
-      <x:c r="B50" s="31" t="n">
-        <x:v>28</x:v>
+      <x:c r="B50" s="24" t="n">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
-      <x:c r="A51" s="30" t="str">
+      <x:c r="A51" s="23" t="str">
         <x:v>Failed</x:v>
       </x:c>
-      <x:c r="B51" s="31" t="n">
-        <x:v>5</x:v>
+      <x:c r="B51" s="24" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
-      <x:c r="A52" s="30" t="str">
+      <x:c r="A52" s="23" t="str">
         <x:v>Blocked</x:v>
       </x:c>
-      <x:c r="B52" s="31" t="n">
+      <x:c r="B52" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
-      <x:c r="A53" s="30" t="str">
+      <x:c r="A53" s="23" t="str">
         <x:v>Execution rate</x:v>
       </x:c>
-      <x:c r="B53" s="32" t="n">
-        <x:v>0.4714285714285714</x:v>
+      <x:c r="B53" s="21" t="n">
+        <x:v>0.7857142857142857</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
-      <x:c r="A54" s="30" t="str">
+      <x:c r="A54" s="23" t="str">
         <x:v>Pass rate (executed cases)</x:v>
       </x:c>
-      <x:c r="B54" s="32" t="n">
-        <x:v>0.8484848484848485</x:v>
+      <x:c r="B54" s="21" t="n">
+        <x:v>0.9272727272727272</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
-      <x:c r="A55" s="30" t="str">
-        <x:v>Imported source</x:v>
-      </x:c>
-      <x:c r="B55" s="31" t="str">
-        <x:v>26 results completed by Rui / Sam in the Chinese test plan on 2026-09-19.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" ht="15" hidden="0" customHeight="1">
-      <x:c r="A56" s="30" t="str">
+      <x:c r="A55" s="23" t="str">
+        <x:v>Latest update</x:v>
+      </x:c>
+      <x:c r="B55" s="24" t="str">
+        <x:v>Results updated by the team on 2026-10-02; 15 cases remain Not run.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A56" s="23" t="str">
         <x:v>Evidence limitation</x:v>
       </x:c>
-      <x:c r="B56" s="31" t="str">
-        <x:v>Five failed cases still require linked GitHub defect IDs and retest evidence.</x:v>
+      <x:c r="B56" s="24" t="str">
+        <x:v>4 failed cases require linked GitHub defects; 29 executed cases still need complete tester/date metadata or evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="15.75" customHeight="1"/>
-    <x:row r="58" ht="15" hidden="0" customHeight="1">
-      <x:c r="A58" s="29" t="str">
-        <x:v>9. Automated Regression Evidence</x:v>
-      </x:c>
-      <x:c r="B58" s="29" t="str">
-        <x:v>Local pre-push run on 2026-10-02</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" ht="15" hidden="0" customHeight="1">
-      <x:c r="A59" s="30" t="str">
-        <x:v>Flutter tests</x:v>
-      </x:c>
-      <x:c r="B59" s="31" t="str">
-        <x:v>451 passed; 0 failed</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" ht="15" hidden="0" customHeight="1">
-      <x:c r="A60" s="30" t="str">
-        <x:v>Server Jest</x:v>
-      </x:c>
-      <x:c r="B60" s="31" t="str">
-        <x:v>24 test suites passed; 264 tests passed; 0 failed</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" ht="15" hidden="0" customHeight="1">
-      <x:c r="A61" s="30" t="str">
-        <x:v>Source revision</x:v>
-      </x:c>
-      <x:c r="B61" s="31" t="str">
-        <x:v>docs/consolidated-test-evidence based on origin/pre 8bcb615</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" ht="15" hidden="0" customHeight="1">
-      <x:c r="A62" s="30" t="str">
-        <x:v>Web evidence gap</x:v>
-      </x:c>
-      <x:c r="B62" s="31" t="str">
-        <x:v>Web tests are not included in test:all; retain manual and CI evidence separately.</x:v>
+    <x:row r="58" ht="15" customHeight="1">
+      <x:c r="A58" s="15" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B58" s="15" t="s">
+        <x:v>70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="15" customHeight="1">
+      <x:c r="A59" s="16" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B59" s="17" t="s">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="15" customHeight="1">
+      <x:c r="A60" s="16" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B60" s="17" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="15" customHeight="1">
+      <x:c r="A61" s="16" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B61" s="17" t="s">
+        <x:v>76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="15" customHeight="1">
+      <x:c r="A62" s="16" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B62" s="17" t="s">
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="15.75" customHeight="1"/>
@@ -2204,157 +2299,157 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultColWidth="14.430000305175781" defaultRowHeight="15"/>
+  <x:sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" customWidth="1"/>
     <x:col min="2" max="2" width="100" customWidth="1"/>
-    <x:col min="3" max="26" width="8.710000038146973" customWidth="1"/>
+    <x:col min="3" max="26" width="8.6640625" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
+    <x:row r="1" ht="19">
       <x:c r="A1" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="3" t="s">
-        <x:v>69</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="16">
       <x:c r="A4" s="4" t="s">
-        <x:v>70</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="16">
       <x:c r="A5" s="4" t="s">
-        <x:v>72</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>73</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="16">
       <x:c r="A6" s="4" t="s">
-        <x:v>74</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
+        <x:v>86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="32">
       <x:c r="A7" s="4" t="s">
-        <x:v>76</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>77</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="3" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
+        <x:v>89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="16">
       <x:c r="A10" s="4" t="s">
-        <x:v>79</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
+        <x:v>91</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="16">
       <x:c r="A11" s="4" t="s">
-        <x:v>81</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B11" s="5" t="s">
-        <x:v>82</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
+        <x:v>93</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="16">
       <x:c r="A12" s="4" t="s">
-        <x:v>83</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B12" s="5" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="16">
       <x:c r="A13" s="4" t="s">
-        <x:v>85</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B13" s="5" t="s">
-        <x:v>86</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="16">
       <x:c r="A14" s="4" t="s">
-        <x:v>87</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B14" s="5" t="s">
-        <x:v>88</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="16">
       <x:c r="A15" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B15" s="5" t="s">
-        <x:v>90</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="3" t="s">
-        <x:v>91</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
+        <x:v>102</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="32">
       <x:c r="A18" s="4" t="s">
-        <x:v>92</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B18" s="5" t="s">
-        <x:v>93</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="32">
       <x:c r="A19" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B19" s="5" t="s">
-        <x:v>95</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="16">
       <x:c r="A20" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B20" s="5" t="s">
-        <x:v>97</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15.75" customHeight="1">
       <x:c r="A21" s="4" t="s">
-        <x:v>98</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B21" s="5" t="s">
-        <x:v>99</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15.75" customHeight="1"/>
     <x:row r="23" ht="15.75" customHeight="1">
       <x:c r="A23" s="3" t="s">
-        <x:v>100</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15.75" customHeight="1">
       <x:c r="A24" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B24" s="5" t="s">
-        <x:v>102</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15.75" customHeight="1"/>
@@ -3340,78 +3435,78 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultColWidth="14.430000305175781" defaultRowHeight="15"/>
+  <x:sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="10" customWidth="1"/>
     <x:col min="2" max="2" width="18" customWidth="1"/>
     <x:col min="3" max="3" width="30" customWidth="1"/>
     <x:col min="4" max="4" width="46" customWidth="1"/>
-    <x:col min="5" max="5" width="40" customWidth="1"/>
+    <x:col min="5" max="5" width="55.5" customWidth="1"/>
     <x:col min="6" max="6" width="9" customWidth="1"/>
     <x:col min="7" max="7" width="13" customWidth="1"/>
     <x:col min="8" max="8" width="14" customWidth="1"/>
     <x:col min="9" max="9" width="8" customWidth="1"/>
     <x:col min="10" max="10" width="9" customWidth="1"/>
     <x:col min="11" max="11" width="10" customWidth="1"/>
-    <x:col min="12" max="12" width="24.56999969482422" customWidth="1"/>
+    <x:col min="12" max="12" width="24.5" customWidth="1"/>
     <x:col min="13" max="13" width="11" customWidth="1"/>
     <x:col min="14" max="14" width="16" customWidth="1"/>
     <x:col min="15" max="15" width="10" customWidth="1"/>
     <x:col min="16" max="16" width="20" customWidth="1"/>
-    <x:col min="17" max="26" width="8.710000038146973" customWidth="1"/>
+    <x:col min="17" max="26" width="8.6640625" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>103</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>104</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>106</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>107</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
-        <x:v>108</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="G1" s="2" t="s">
-        <x:v>109</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>110</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I1" s="2" t="s">
-        <x:v>111</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="J1" s="2" t="s">
-        <x:v>112</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="K1" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L1" s="2" t="s">
-        <x:v>113</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="M1" s="2" t="s">
-        <x:v>114</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="N1" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="O1" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="P1" s="2" t="s">
-        <x:v>115</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
+        <x:v>126</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="48" hidden="1">
       <x:c r="A2" s="6" t="str">
         <x:v>KS-T-001</x:v>
       </x:c>
@@ -3443,14 +3538,14 @@
       <x:c r="J2" s="6" t="str">
         <x:v>Jenny</x:v>
       </x:c>
-      <x:c r="K2" s="9" t="str">
+      <x:c r="K2" s="6" t="str">
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="L2" s="9" t="str">
+      <x:c r="L2" s="6" t="str">
         <x:v>Jenny; Rui / Sam</x:v>
       </x:c>
-      <x:c r="M2" s="14" t="d">
-        <x:v>2026-09-19T00:00:00.000Z</x:v>
+      <x:c r="M2" s="11" t="n">
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="N2" s="6"/>
       <x:c r="O2" s="6"/>
@@ -3458,7 +3553,7 @@
         <x:v>Also passed by Rui / Sam on 2026-09-19 (Chinese test plan).</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
+    <x:row r="3" ht="48" hidden="1">
       <x:c r="A3" s="6" t="str">
         <x:v>KS-T-002</x:v>
       </x:c>
@@ -3490,14 +3585,14 @@
       <x:c r="J3" s="6" t="str">
         <x:v>Jenny</x:v>
       </x:c>
-      <x:c r="K3" s="9" t="str">
+      <x:c r="K3" s="6" t="str">
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="L3" s="9" t="str">
+      <x:c r="L3" s="6" t="str">
         <x:v>Jenny; Rui / Sam</x:v>
       </x:c>
-      <x:c r="M3" s="14" t="d">
-        <x:v>2026-09-19T00:00:00.000Z</x:v>
+      <x:c r="M3" s="11" t="n">
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="N3" s="6"/>
       <x:c r="O3" s="6"/>
@@ -3505,7 +3600,7 @@
         <x:v>Also passed by Rui / Sam on 2026-09-19 (Chinese test plan).</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" ht="48" hidden="1">
       <x:c r="A4" s="6" t="str">
         <x:v>KS-T-003</x:v>
       </x:c>
@@ -3537,14 +3632,14 @@
       <x:c r="J4" s="6" t="str">
         <x:v>Jenny</x:v>
       </x:c>
-      <x:c r="K4" s="9" t="str">
+      <x:c r="K4" s="6" t="str">
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="L4" s="9" t="str">
+      <x:c r="L4" s="6" t="str">
         <x:v>Jenny; Rui / Sam</x:v>
       </x:c>
-      <x:c r="M4" s="14" t="d">
-        <x:v>2026-09-19T00:00:00.000Z</x:v>
+      <x:c r="M4" s="11" t="n">
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="N4" s="6"/>
       <x:c r="O4" s="6"/>
@@ -3552,7 +3647,7 @@
         <x:v>Also passed by Rui / Sam on 2026-09-19 (Chinese test plan).</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="48" hidden="1">
       <x:c r="A5" s="6" t="str">
         <x:v>KS-T-004</x:v>
       </x:c>
@@ -3584,14 +3679,14 @@
       <x:c r="J5" s="6" t="str">
         <x:v>Jenny</x:v>
       </x:c>
-      <x:c r="K5" s="9" t="str">
+      <x:c r="K5" s="6" t="str">
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="L5" s="9" t="str">
+      <x:c r="L5" s="6" t="str">
         <x:v>Jenny; Rui / Sam</x:v>
       </x:c>
-      <x:c r="M5" s="14" t="d">
-        <x:v>2026-09-19T00:00:00.000Z</x:v>
+      <x:c r="M5" s="11" t="n">
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="N5" s="6"/>
       <x:c r="O5" s="6"/>
@@ -3599,7 +3694,7 @@
         <x:v>Also passed by Rui / Sam on 2026-09-19 (Chinese test plan).</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="41.25" customHeight="1">
+    <x:row r="6" ht="41.25" hidden="1" customHeight="1">
       <x:c r="A6" s="6" t="str">
         <x:v>KS-T-005</x:v>
       </x:c>
@@ -3633,24 +3728,22 @@
       <x:c r="J6" s="6" t="str">
         <x:v>Jenny</x:v>
       </x:c>
-      <x:c r="K6" s="9" t="str">
-        <x:v>Fail</x:v>
-      </x:c>
-      <x:c r="L6" s="11" t="str">
+      <x:c r="K6" s="6" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="L6" s="10" t="str">
         <x:v>Jenny (emulator); Rui / Sam</x:v>
       </x:c>
-      <x:c r="M6" s="14" t="d">
-        <x:v>2026-09-19T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="N6" s="6" t="str">
-        <x:v>docs/testing-evidence/release-test-round-1/KS-T-005-password-reset-provider-restriction.png</x:v>
-      </x:c>
+      <x:c r="M6" s="11" t="n">
+        <x:v>46284</x:v>
+      </x:c>
+      <x:c r="N6" s="6"/>
       <x:c r="O6" s="6"/>
-      <x:c r="P6" s="12" t="str">
-        <x:v>Tested with emulator, received OTP code in server terminal not the real email. Rui / Sam recorded this case as Fail on 2026-09-19. GitHub defect link pending.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
+      <x:c r="P6" s="7" t="str">
+        <x:v>Retested as Pass in the updated test plan. Historical screenshot removed because it contained personal information. Replacement evidence and retest metadata are pending.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="48" hidden="1">
       <x:c r="A7" s="6" t="str">
         <x:v>KS-T-006</x:v>
       </x:c>
@@ -3683,18 +3776,18 @@
       <x:c r="J7" s="6" t="str">
         <x:v>Jenny</x:v>
       </x:c>
-      <x:c r="K7" s="9" t="str">
+      <x:c r="K7" s="6" t="str">
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="str">
+      <x:c r="L7" s="10" t="str">
         <x:v>Jenny</x:v>
       </x:c>
-      <x:c r="M7" s="14"/>
+      <x:c r="M7" s="11"/>
       <x:c r="N7" s="6"/>
       <x:c r="O7" s="6"/>
       <x:c r="P7" s="7"/>
     </x:row>
-    <x:row r="8">
+    <x:row r="8" ht="48" hidden="1">
       <x:c r="A8" s="6" t="str">
         <x:v>KS-T-007</x:v>
       </x:c>
@@ -3727,18 +3820,18 @@
       <x:c r="J8" s="6" t="str">
         <x:v>Jenny</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="str">
+      <x:c r="K8" s="6" t="str">
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="L8" s="11" t="str">
+      <x:c r="L8" s="10" t="str">
         <x:v>Jenny</x:v>
       </x:c>
-      <x:c r="M8" s="14"/>
+      <x:c r="M8" s="11"/>
       <x:c r="N8" s="6"/>
       <x:c r="O8" s="6"/>
       <x:c r="P8" s="7"/>
     </x:row>
-    <x:row r="9">
+    <x:row r="9" ht="208" hidden="1">
       <x:c r="A9" s="6" t="str">
         <x:v>KS-T-008</x:v>
       </x:c>
@@ -3770,22 +3863,22 @@
       <x:c r="J9" s="6" t="str">
         <x:v>Jenny</x:v>
       </x:c>
-      <x:c r="K9" s="9" t="str">
+      <x:c r="K9" s="6" t="str">
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="L9" s="9" t="str">
+      <x:c r="L9" s="6" t="str">
         <x:v>Jenny</x:v>
       </x:c>
-      <x:c r="M9" s="14"/>
+      <x:c r="M9" s="11"/>
       <x:c r="N9" s="6"/>
       <x:c r="O9" s="6" t="str">
         <x:v>KS-B-003</x:v>
       </x:c>
-      <x:c r="P9" s="9" t="str">
+      <x:c r="P9" s="6" t="str">
         <x:v>KS-B-003 | KS-T-008 | Profile | Change-password dialog: floating labels overlap the field above (no spacing between the three TextFormFields) | Profile &gt; Change password, observe dialog | S4 Cosmetic | Jenny | Jenny | Open |  | Add SizedBox(height:16) between fields</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
+    <x:row r="10" ht="48" hidden="1">
       <x:c r="A10" s="6" t="str">
         <x:v>KS-T-009</x:v>
       </x:c>
@@ -3818,18 +3911,18 @@
       <x:c r="J10" s="6" t="str">
         <x:v>Jenny</x:v>
       </x:c>
-      <x:c r="K10" s="9" t="str">
+      <x:c r="K10" s="6" t="str">
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="L10" s="9" t="str">
+      <x:c r="L10" s="6" t="str">
         <x:v>Jenny</x:v>
       </x:c>
-      <x:c r="M10" s="14"/>
+      <x:c r="M10" s="11"/>
       <x:c r="N10" s="6"/>
       <x:c r="O10" s="6"/>
       <x:c r="P10" s="7"/>
     </x:row>
-    <x:row r="11">
+    <x:row r="11" ht="48" hidden="1">
       <x:c r="A11" s="6" t="str">
         <x:v>KS-T-010</x:v>
       </x:c>
@@ -3860,14 +3953,14 @@
       <x:c r="J11" s="6" t="str">
         <x:v>Jenny</x:v>
       </x:c>
-      <x:c r="K11" s="9" t="str">
+      <x:c r="K11" s="6" t="str">
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="L11" s="9" t="str">
+      <x:c r="L11" s="6" t="str">
         <x:v>Jenny; Rui / Sam</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="d">
-        <x:v>2026-09-19T00:00:00.000Z</x:v>
+      <x:c r="M11" s="11" t="n">
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="N11" s="6"/>
       <x:c r="O11" s="6"/>
@@ -3875,7 +3968,7 @@
         <x:v>Also passed by Rui / Sam on 2026-09-19 (Chinese test plan).</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
+    <x:row r="12" ht="32" hidden="1">
       <x:c r="A12" s="6" t="str">
         <x:v>KS-T-011</x:v>
       </x:c>
@@ -3907,18 +4000,18 @@
       <x:c r="J12" s="6" t="str">
         <x:v>Jenny</x:v>
       </x:c>
-      <x:c r="K12" s="9" t="str">
+      <x:c r="K12" s="6" t="str">
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="L12" s="9" t="str">
+      <x:c r="L12" s="6" t="str">
         <x:v>Jenny</x:v>
       </x:c>
-      <x:c r="M12" s="14"/>
+      <x:c r="M12" s="11"/>
       <x:c r="N12" s="6"/>
       <x:c r="O12" s="6"/>
       <x:c r="P12" s="7"/>
     </x:row>
-    <x:row r="13">
+    <x:row r="13" ht="48" hidden="1">
       <x:c r="A13" s="6" t="str">
         <x:v>KS-T-012</x:v>
       </x:c>
@@ -3951,14 +4044,14 @@
       <x:c r="J13" s="6" t="str">
         <x:v>Jenny</x:v>
       </x:c>
-      <x:c r="K13" s="9" t="str">
+      <x:c r="K13" s="6" t="str">
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="L13" s="9" t="str">
+      <x:c r="L13" s="6" t="str">
         <x:v>Jenny; Rui / Sam</x:v>
       </x:c>
-      <x:c r="M13" s="14" t="d">
-        <x:v>2026-09-19T00:00:00.000Z</x:v>
+      <x:c r="M13" s="11" t="n">
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="N13" s="6"/>
       <x:c r="O13" s="6"/>
@@ -3966,7 +4059,7 @@
         <x:v>Also passed by Rui / Sam on 2026-09-19 (Chinese test plan).</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
+    <x:row r="14" ht="288" hidden="1">
       <x:c r="A14" s="6" t="str">
         <x:v>KS-T-013</x:v>
       </x:c>
@@ -3998,22 +4091,22 @@
       <x:c r="J14" s="6" t="str">
         <x:v>Jenny</x:v>
       </x:c>
-      <x:c r="K14" s="9" t="str">
+      <x:c r="K14" s="6" t="str">
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="L14" s="13" t="str">
+      <x:c r="L14" s="9" t="str">
         <x:v>Jenny</x:v>
       </x:c>
-      <x:c r="M14" s="14"/>
+      <x:c r="M14" s="11"/>
       <x:c r="N14" s="6"/>
       <x:c r="O14" s="6" t="str">
         <x:v>KS-B-002</x:v>
       </x:c>
-      <x:c r="P14" s="12" t="str">
+      <x:c r="P14" s="7" t="str">
         <x:v>KS-B-002 | KS-T-013 | Profile | Registration accepts displayName &gt;30 chars; edit dialog silently truncates to 30 (inconsistent length limits across entry points) | Register with a 32-char nickname, then edit nickname in Profile and type a 33rd char | S3 Minor | Jenny | Jenny | Open |  | Server /auth/register lacks the 2-30 length check that PUT /users has (users.ts:59); client edit uses maxLength:30</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
+    <x:row r="15" ht="64" hidden="1">
       <x:c r="A15" s="6" t="str">
         <x:v>KS-T-014</x:v>
       </x:c>
@@ -4047,11 +4140,11 @@
       <x:c r="K15" s="6" t="str">
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="L15" s="9" t="str">
+      <x:c r="L15" s="6" t="str">
         <x:v>Rui / Sam</x:v>
       </x:c>
-      <x:c r="M15" s="14" t="d">
-        <x:v>2026-09-19T00:00:00.000Z</x:v>
+      <x:c r="M15" s="11" t="n">
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="N15" s="6"/>
       <x:c r="O15" s="6"/>
@@ -4059,7 +4152,7 @@
         <x:v>Imported from the Chinese test plan completed by Rui / Sam on 2026-09-19.</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
+    <x:row r="16" ht="48" hidden="1">
       <x:c r="A16" s="6" t="str">
         <x:v>KS-T-015</x:v>
       </x:c>
@@ -4091,14 +4184,14 @@
       <x:c r="J16" s="6" t="str">
         <x:v>Jenny</x:v>
       </x:c>
-      <x:c r="K16" s="9" t="str">
+      <x:c r="K16" s="6" t="str">
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="L16" s="9" t="str">
+      <x:c r="L16" s="6" t="str">
         <x:v>Jenny; Rui / Sam</x:v>
       </x:c>
-      <x:c r="M16" s="14" t="d">
-        <x:v>2026-09-19T00:00:00.000Z</x:v>
+      <x:c r="M16" s="11" t="n">
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="N16" s="6"/>
       <x:c r="O16" s="6"/>
@@ -4106,7 +4199,7 @@
         <x:v>Also passed by Rui / Sam on 2026-09-19 (Chinese test plan).</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
+    <x:row r="17" ht="48" hidden="1">
       <x:c r="A17" s="6" t="str">
         <x:v>KS-T-016</x:v>
       </x:c>
@@ -4138,14 +4231,14 @@
       <x:c r="J17" s="6" t="str">
         <x:v>Jenny</x:v>
       </x:c>
-      <x:c r="K17" s="9" t="str">
+      <x:c r="K17" s="6" t="str">
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="L17" s="9" t="str">
+      <x:c r="L17" s="6" t="str">
         <x:v>Jenny; Rui / Sam</x:v>
       </x:c>
-      <x:c r="M17" s="14" t="d">
-        <x:v>2026-09-19T00:00:00.000Z</x:v>
+      <x:c r="M17" s="11" t="n">
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="N17" s="6"/>
       <x:c r="O17" s="6"/>
@@ -4153,7 +4246,7 @@
         <x:v>Also passed by Rui / Sam on 2026-09-19 (Chinese test plan).</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
+    <x:row r="18" ht="64" hidden="1">
       <x:c r="A18" s="6" t="str">
         <x:v>KS-T-017</x:v>
       </x:c>
@@ -4192,8 +4285,8 @@
       <x:c r="L18" s="6" t="str">
         <x:v>Rui / Sam</x:v>
       </x:c>
-      <x:c r="M18" s="14" t="d">
-        <x:v>2026-09-19T00:00:00.000Z</x:v>
+      <x:c r="M18" s="11" t="n">
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="N18" s="6"/>
       <x:c r="O18" s="6"/>
@@ -4201,7 +4294,7 @@
         <x:v>Imported from the Chinese test plan completed by Rui / Sam on 2026-09-19.</x:v>
       </x:c>
     </x:row>
-    <x:row r="19">
+    <x:row r="19" ht="32" hidden="1">
       <x:c r="A19" s="6" t="str">
         <x:v>KS-T-018</x:v>
       </x:c>
@@ -4215,7 +4308,7 @@
         <x:v>1. Add 1–5 photos from gallery
 2. Add via camera</x:v>
       </x:c>
-      <x:c r="E19" s="7" t="str">
+      <x:c r="E19" s="19" t="str">
         <x:v>Photos upload, thumbnails shown in step list and on the item</x:v>
       </x:c>
       <x:c r="F19" s="8" t="str">
@@ -4234,15 +4327,17 @@
         <x:v>Jack</x:v>
       </x:c>
       <x:c r="K19" s="6" t="str">
-        <x:v>Not run</x:v>
-      </x:c>
-      <x:c r="L19" s="6"/>
-      <x:c r="M19" s="14"/>
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="L19" s="20" t="str">
+        <x:v>Jenny</x:v>
+      </x:c>
+      <x:c r="M19" s="11"/>
       <x:c r="N19" s="6"/>
       <x:c r="O19" s="6"/>
       <x:c r="P19" s="7"/>
     </x:row>
-    <x:row r="20">
+    <x:row r="20" ht="32" hidden="1">
       <x:c r="A20" s="6" t="str">
         <x:v>KS-T-019</x:v>
       </x:c>
@@ -4275,15 +4370,15 @@
         <x:v>Jack</x:v>
       </x:c>
       <x:c r="K20" s="6" t="str">
-        <x:v>Not run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="L20" s="6"/>
-      <x:c r="M20" s="14"/>
+      <x:c r="M20" s="11"/>
       <x:c r="N20" s="6"/>
       <x:c r="O20" s="6"/>
       <x:c r="P20" s="7"/>
     </x:row>
-    <x:row r="21" ht="15.75" customHeight="1">
+    <x:row r="21" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A21" s="6" t="str">
         <x:v>KS-T-020</x:v>
       </x:c>
@@ -4322,8 +4417,8 @@
       <x:c r="L21" s="6" t="str">
         <x:v>Rui / Sam</x:v>
       </x:c>
-      <x:c r="M21" s="14" t="d">
-        <x:v>2026-09-19T00:00:00.000Z</x:v>
+      <x:c r="M21" s="11" t="n">
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="N21" s="6"/>
       <x:c r="O21" s="6"/>
@@ -4331,7 +4426,7 @@
         <x:v>Marked Fail by Rui / Sam on 2026-09-19; GitHub defect link pending.</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="15.75" customHeight="1">
+    <x:row r="22" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A22" s="6" t="str">
         <x:v>KS-T-021</x:v>
       </x:c>
@@ -4368,8 +4463,8 @@
       <x:c r="L22" s="6" t="str">
         <x:v>Rui / Sam</x:v>
       </x:c>
-      <x:c r="M22" s="14" t="d">
-        <x:v>2026-09-19T00:00:00.000Z</x:v>
+      <x:c r="M22" s="11" t="n">
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="N22" s="6"/>
       <x:c r="O22" s="6"/>
@@ -4377,7 +4472,7 @@
         <x:v>Imported from the Chinese test plan completed by Rui / Sam on 2026-09-19.</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="15.75" customHeight="1">
+    <x:row r="23" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A23" s="6" t="str">
         <x:v>KS-T-022</x:v>
       </x:c>
@@ -4387,7 +4482,7 @@
       <x:c r="C23" s="7" t="str">
         <x:v>GPS location on publish</x:v>
       </x:c>
-      <x:c r="D23" s="7" t="str">
+      <x:c r="D23" s="19" t="str">
         <x:v>1. Grant location permission
 2. Publish with current location
 3. Deny permission and publish</x:v>
@@ -4411,15 +4506,17 @@
         <x:v>Jack</x:v>
       </x:c>
       <x:c r="K23" s="6" t="str">
-        <x:v>Not run</x:v>
-      </x:c>
-      <x:c r="L23" s="6"/>
-      <x:c r="M23" s="14"/>
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="L23" s="20" t="str">
+        <x:v>Jenny</x:v>
+      </x:c>
+      <x:c r="M23" s="11"/>
       <x:c r="N23" s="6"/>
       <x:c r="O23" s="6"/>
       <x:c r="P23" s="7"/>
     </x:row>
-    <x:row r="24" ht="15.75" customHeight="1">
+    <x:row r="24" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A24" s="6" t="str">
         <x:v>KS-T-023</x:v>
       </x:c>
@@ -4458,8 +4555,8 @@
       <x:c r="L24" s="6" t="str">
         <x:v>Rui / Sam</x:v>
       </x:c>
-      <x:c r="M24" s="14" t="d">
-        <x:v>2026-09-19T00:00:00.000Z</x:v>
+      <x:c r="M24" s="11" t="n">
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="N24" s="6"/>
       <x:c r="O24" s="6"/>
@@ -4467,7 +4564,7 @@
         <x:v>Marked Fail by Rui / Sam on 2026-09-19; GitHub defect link pending.</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="15.75" customHeight="1">
+    <x:row r="25" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A25" s="6" t="str">
         <x:v>KS-T-024</x:v>
       </x:c>
@@ -4505,8 +4602,8 @@
       <x:c r="L25" s="6" t="str">
         <x:v>Rui / Sam</x:v>
       </x:c>
-      <x:c r="M25" s="14" t="d">
-        <x:v>2026-09-19T00:00:00.000Z</x:v>
+      <x:c r="M25" s="11" t="n">
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="N25" s="6"/>
       <x:c r="O25" s="6"/>
@@ -4514,7 +4611,7 @@
         <x:v>Imported from the Chinese test plan completed by Rui / Sam on 2026-09-19.</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="15.75" customHeight="1">
+    <x:row r="26" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A26" s="6" t="str">
         <x:v>KS-T-025</x:v>
       </x:c>
@@ -4551,8 +4648,8 @@
       <x:c r="L26" s="6" t="str">
         <x:v>Rui / Sam</x:v>
       </x:c>
-      <x:c r="M26" s="14" t="d">
-        <x:v>2026-09-19T00:00:00.000Z</x:v>
+      <x:c r="M26" s="11" t="n">
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="N26" s="6"/>
       <x:c r="O26" s="6"/>
@@ -4560,7 +4657,7 @@
         <x:v>Imported from the Chinese test plan completed by Rui / Sam on 2026-09-19.</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="15.75" customHeight="1">
+    <x:row r="27" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A27" s="6" t="str">
         <x:v>KS-T-026</x:v>
       </x:c>
@@ -4598,8 +4695,8 @@
       <x:c r="L27" s="6" t="str">
         <x:v>Rui / Sam</x:v>
       </x:c>
-      <x:c r="M27" s="14" t="d">
-        <x:v>2026-09-19T00:00:00.000Z</x:v>
+      <x:c r="M27" s="11" t="n">
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="N27" s="6"/>
       <x:c r="O27" s="6"/>
@@ -4607,7 +4704,7 @@
         <x:v>Imported from the Chinese test plan completed by Rui / Sam on 2026-09-19.</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="15.75" customHeight="1">
+    <x:row r="28" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A28" s="6" t="str">
         <x:v>KS-T-027</x:v>
       </x:c>
@@ -4639,10 +4736,12 @@
         <x:v>Rui</x:v>
       </x:c>
       <x:c r="K28" s="6" t="str">
-        <x:v>Not run</x:v>
-      </x:c>
-      <x:c r="L28" s="6"/>
-      <x:c r="M28" s="14"/>
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="L28" s="20" t="str">
+        <x:v>Jenny</x:v>
+      </x:c>
+      <x:c r="M28" s="11"/>
       <x:c r="N28" s="6"/>
       <x:c r="O28" s="6"/>
       <x:c r="P28" s="7"/>
@@ -4682,12 +4781,12 @@
         <x:v>Not run</x:v>
       </x:c>
       <x:c r="L29" s="6"/>
-      <x:c r="M29" s="14"/>
+      <x:c r="M29" s="11"/>
       <x:c r="N29" s="6"/>
       <x:c r="O29" s="6"/>
       <x:c r="P29" s="7"/>
     </x:row>
-    <x:row r="30" ht="15.75" customHeight="1">
+    <x:row r="30" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A30" s="6" t="str">
         <x:v>KS-T-029</x:v>
       </x:c>
@@ -4720,15 +4819,15 @@
         <x:v>Rui</x:v>
       </x:c>
       <x:c r="K30" s="6" t="str">
-        <x:v>Not run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="L30" s="6"/>
-      <x:c r="M30" s="14"/>
+      <x:c r="M30" s="11"/>
       <x:c r="N30" s="6"/>
       <x:c r="O30" s="6"/>
       <x:c r="P30" s="7"/>
     </x:row>
-    <x:row r="31" ht="15.75" customHeight="1">
+    <x:row r="31" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A31" s="6" t="str">
         <x:v>KS-T-030</x:v>
       </x:c>
@@ -4765,8 +4864,8 @@
       <x:c r="L31" s="6" t="str">
         <x:v>Rui / Sam</x:v>
       </x:c>
-      <x:c r="M31" s="14" t="d">
-        <x:v>2026-09-19T00:00:00.000Z</x:v>
+      <x:c r="M31" s="11" t="n">
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="N31" s="6"/>
       <x:c r="O31" s="6"/>
@@ -4774,7 +4873,7 @@
         <x:v>Imported from the Chinese test plan completed by Rui / Sam on 2026-09-19.</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="15.75" customHeight="1">
+    <x:row r="32" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A32" s="6" t="str">
         <x:v>KS-T-031</x:v>
       </x:c>
@@ -4812,8 +4911,8 @@
       <x:c r="L32" s="6" t="str">
         <x:v>Rui / Sam</x:v>
       </x:c>
-      <x:c r="M32" s="14" t="d">
-        <x:v>2026-09-19T00:00:00.000Z</x:v>
+      <x:c r="M32" s="11" t="n">
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="N32" s="6"/>
       <x:c r="O32" s="6"/>
@@ -4821,7 +4920,7 @@
         <x:v>Marked Fail by Rui / Sam on 2026-09-19; GitHub defect link pending.</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="15.75" customHeight="1">
+    <x:row r="33" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A33" s="6" t="str">
         <x:v>KS-T-032</x:v>
       </x:c>
@@ -4860,8 +4959,8 @@
       <x:c r="L33" s="6" t="str">
         <x:v>Rui / Sam</x:v>
       </x:c>
-      <x:c r="M33" s="14" t="d">
-        <x:v>2026-09-19T00:00:00.000Z</x:v>
+      <x:c r="M33" s="11" t="n">
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="N33" s="6"/>
       <x:c r="O33" s="6"/>
@@ -4907,12 +5006,12 @@
         <x:v>Not run</x:v>
       </x:c>
       <x:c r="L34" s="6"/>
-      <x:c r="M34" s="14"/>
+      <x:c r="M34" s="11"/>
       <x:c r="N34" s="6"/>
       <x:c r="O34" s="6"/>
       <x:c r="P34" s="7"/>
     </x:row>
-    <x:row r="35" ht="15.75" customHeight="1">
+    <x:row r="35" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A35" s="6" t="str">
         <x:v>KS-T-034</x:v>
       </x:c>
@@ -4945,10 +5044,10 @@
         <x:v>Sam</x:v>
       </x:c>
       <x:c r="K35" s="6" t="str">
-        <x:v>Not run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="L35" s="6"/>
-      <x:c r="M35" s="14"/>
+      <x:c r="M35" s="11"/>
       <x:c r="N35" s="6"/>
       <x:c r="O35" s="6"/>
       <x:c r="P35" s="7"/>
@@ -4963,7 +5062,7 @@
       <x:c r="C36" s="7" t="str">
         <x:v>Notification routing</x:v>
       </x:c>
-      <x:c r="D36" s="7" t="str">
+      <x:c r="D36" s="19" t="str">
         <x:v>Setup: two devices; B sends A a message while A is backgrounded
 1. Wait for push on A's device
 2. Tap the notification</x:v>
@@ -4990,12 +5089,12 @@
         <x:v>Not run</x:v>
       </x:c>
       <x:c r="L36" s="6"/>
-      <x:c r="M36" s="14"/>
+      <x:c r="M36" s="11"/>
       <x:c r="N36" s="6"/>
       <x:c r="O36" s="6"/>
       <x:c r="P36" s="7"/>
     </x:row>
-    <x:row r="37" ht="15.75" customHeight="1">
+    <x:row r="37" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A37" s="6" t="str">
         <x:v>KS-T-036</x:v>
       </x:c>
@@ -5034,8 +5133,8 @@
       <x:c r="L37" s="6" t="str">
         <x:v>Rui / Sam</x:v>
       </x:c>
-      <x:c r="M37" s="14" t="d">
-        <x:v>2026-09-19T00:00:00.000Z</x:v>
+      <x:c r="M37" s="11" t="n">
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="N37" s="6"/>
       <x:c r="O37" s="6"/>
@@ -5043,7 +5142,7 @@
         <x:v>Imported from the Chinese test plan completed by Rui / Sam on 2026-09-19.</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="15.75" customHeight="1">
+    <x:row r="38" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A38" s="6" t="str">
         <x:v>KS-T-037</x:v>
       </x:c>
@@ -5076,15 +5175,15 @@
         <x:v>Jaeger</x:v>
       </x:c>
       <x:c r="K38" s="6" t="str">
-        <x:v>Not run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="L38" s="6"/>
-      <x:c r="M38" s="14"/>
+      <x:c r="M38" s="11"/>
       <x:c r="N38" s="6"/>
       <x:c r="O38" s="6"/>
       <x:c r="P38" s="7"/>
     </x:row>
-    <x:row r="39" ht="15.75" customHeight="1">
+    <x:row r="39" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A39" s="6" t="str">
         <x:v>KS-T-038</x:v>
       </x:c>
@@ -5122,8 +5221,8 @@
       <x:c r="L39" s="6" t="str">
         <x:v>Rui / Sam</x:v>
       </x:c>
-      <x:c r="M39" s="14" t="d">
-        <x:v>2026-09-19T00:00:00.000Z</x:v>
+      <x:c r="M39" s="11" t="n">
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="N39" s="6"/>
       <x:c r="O39" s="6"/>
@@ -5131,7 +5230,7 @@
         <x:v>Imported from the Chinese test plan completed by Rui / Sam on 2026-09-19.</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="15.75" customHeight="1">
+    <x:row r="40" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A40" s="6" t="str">
         <x:v>KS-T-039</x:v>
       </x:c>
@@ -5164,15 +5263,15 @@
         <x:v>Jaeger</x:v>
       </x:c>
       <x:c r="K40" s="6" t="str">
-        <x:v>Not run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="L40" s="6"/>
-      <x:c r="M40" s="14"/>
+      <x:c r="M40" s="11"/>
       <x:c r="N40" s="6"/>
       <x:c r="O40" s="6"/>
       <x:c r="P40" s="7"/>
     </x:row>
-    <x:row r="41" ht="15.75" customHeight="1">
+    <x:row r="41" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A41" s="6" t="str">
         <x:v>KS-T-040</x:v>
       </x:c>
@@ -5205,15 +5304,15 @@
         <x:v>Jaeger</x:v>
       </x:c>
       <x:c r="K41" s="6" t="str">
-        <x:v>Not run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="L41" s="6"/>
-      <x:c r="M41" s="14"/>
+      <x:c r="M41" s="11"/>
       <x:c r="N41" s="6"/>
       <x:c r="O41" s="6"/>
       <x:c r="P41" s="7"/>
     </x:row>
-    <x:row r="42" ht="15.75" customHeight="1">
+    <x:row r="42" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A42" s="6" t="str">
         <x:v>KS-T-041</x:v>
       </x:c>
@@ -5245,15 +5344,15 @@
         <x:v>Jaeger</x:v>
       </x:c>
       <x:c r="K42" s="6" t="str">
-        <x:v>Not run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="L42" s="6"/>
-      <x:c r="M42" s="14"/>
+      <x:c r="M42" s="11"/>
       <x:c r="N42" s="6"/>
       <x:c r="O42" s="6"/>
       <x:c r="P42" s="7"/>
     </x:row>
-    <x:row r="43" ht="15.75" customHeight="1">
+    <x:row r="43" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A43" s="6" t="str">
         <x:v>KS-T-042</x:v>
       </x:c>
@@ -5263,7 +5362,7 @@
       <x:c r="C43" s="7" t="str">
         <x:v>Swipe delete conversation</x:v>
       </x:c>
-      <x:c r="D43" s="7" t="str">
+      <x:c r="D43" s="19" t="str">
         <x:v>1. Swipe a conversation
 2. Confirm</x:v>
       </x:c>
@@ -5286,15 +5385,15 @@
         <x:v>Jaeger</x:v>
       </x:c>
       <x:c r="K43" s="6" t="str">
-        <x:v>Not run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="L43" s="6"/>
-      <x:c r="M43" s="14"/>
+      <x:c r="M43" s="11"/>
       <x:c r="N43" s="6"/>
       <x:c r="O43" s="6"/>
       <x:c r="P43" s="7"/>
     </x:row>
-    <x:row r="44" ht="15.75" customHeight="1">
+    <x:row r="44" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A44" s="6" t="str">
         <x:v>KS-T-043</x:v>
       </x:c>
@@ -5327,10 +5426,10 @@
         <x:v>Jack</x:v>
       </x:c>
       <x:c r="K44" s="6" t="str">
-        <x:v>Not run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="L44" s="6"/>
-      <x:c r="M44" s="14"/>
+      <x:c r="M44" s="11"/>
       <x:c r="N44" s="6"/>
       <x:c r="O44" s="6"/>
       <x:c r="P44" s="7"/>
@@ -5370,7 +5469,7 @@
         <x:v>Not run</x:v>
       </x:c>
       <x:c r="L45" s="6"/>
-      <x:c r="M45" s="14"/>
+      <x:c r="M45" s="11"/>
       <x:c r="N45" s="6"/>
       <x:c r="O45" s="6"/>
       <x:c r="P45" s="7"/>
@@ -5410,7 +5509,7 @@
         <x:v>Not run</x:v>
       </x:c>
       <x:c r="L46" s="6"/>
-      <x:c r="M46" s="14"/>
+      <x:c r="M46" s="11"/>
       <x:c r="N46" s="6"/>
       <x:c r="O46" s="6"/>
       <x:c r="P46" s="7"/>
@@ -5450,13 +5549,13 @@
       <x:c r="K47" s="6" t="str">
         <x:v>Not run</x:v>
       </x:c>
-      <x:c r="L47" s="6"/>
-      <x:c r="M47" s="14"/>
+      <x:c r="L47" s="20"/>
+      <x:c r="M47" s="11"/>
       <x:c r="N47" s="6"/>
       <x:c r="O47" s="6"/>
       <x:c r="P47" s="7"/>
     </x:row>
-    <x:row r="48" ht="15.75" customHeight="1">
+    <x:row r="48" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A48" s="6" t="str">
         <x:v>KS-T-047</x:v>
       </x:c>
@@ -5493,8 +5592,8 @@
       <x:c r="L48" s="6" t="str">
         <x:v>Rui / Sam</x:v>
       </x:c>
-      <x:c r="M48" s="14" t="d">
-        <x:v>2026-09-19T00:00:00.000Z</x:v>
+      <x:c r="M48" s="11" t="n">
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="N48" s="6"/>
       <x:c r="O48" s="6"/>
@@ -5502,7 +5601,7 @@
         <x:v>Imported from the Chinese test plan completed by Rui / Sam on 2026-09-19.</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="15.75" customHeight="1">
+    <x:row r="49" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A49" s="6" t="str">
         <x:v>KS-T-048</x:v>
       </x:c>
@@ -5539,8 +5638,8 @@
       <x:c r="L49" s="6" t="str">
         <x:v>Rui / Sam</x:v>
       </x:c>
-      <x:c r="M49" s="14" t="d">
-        <x:v>2026-09-19T00:00:00.000Z</x:v>
+      <x:c r="M49" s="11" t="n">
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="N49" s="6"/>
       <x:c r="O49" s="6"/>
@@ -5548,7 +5647,7 @@
         <x:v>Imported from the Chinese test plan completed by Rui / Sam on 2026-09-19.</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="15.75" customHeight="1">
+    <x:row r="50" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A50" s="6" t="str">
         <x:v>KS-T-049</x:v>
       </x:c>
@@ -5585,8 +5684,8 @@
       <x:c r="L50" s="6" t="str">
         <x:v>Rui / Sam</x:v>
       </x:c>
-      <x:c r="M50" s="14" t="d">
-        <x:v>2026-09-19T00:00:00.000Z</x:v>
+      <x:c r="M50" s="11" t="n">
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="N50" s="6"/>
       <x:c r="O50" s="6"/>
@@ -5594,7 +5693,7 @@
         <x:v>Imported from the Chinese test plan completed by Rui / Sam on 2026-09-19.</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" ht="15.75" customHeight="1">
+    <x:row r="51" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A51" s="6" t="str">
         <x:v>KS-T-050</x:v>
       </x:c>
@@ -5626,11 +5725,11 @@
       <x:c r="J51" s="6" t="str">
         <x:v>Sam</x:v>
       </x:c>
-      <x:c r="K51" s="9" t="str">
+      <x:c r="K51" s="6" t="str">
         <x:v>Pass</x:v>
       </x:c>
       <x:c r="L51" s="6"/>
-      <x:c r="M51" s="14"/>
+      <x:c r="M51" s="11"/>
       <x:c r="N51" s="6"/>
       <x:c r="O51" s="6"/>
       <x:c r="P51" s="7"/>
@@ -5670,7 +5769,7 @@
         <x:v>Not run</x:v>
       </x:c>
       <x:c r="L52" s="6"/>
-      <x:c r="M52" s="14"/>
+      <x:c r="M52" s="11"/>
       <x:c r="N52" s="6"/>
       <x:c r="O52" s="6"/>
       <x:c r="P52" s="7"/>
@@ -5710,12 +5809,12 @@
         <x:v>Not run</x:v>
       </x:c>
       <x:c r="L53" s="6"/>
-      <x:c r="M53" s="14"/>
+      <x:c r="M53" s="11"/>
       <x:c r="N53" s="6"/>
       <x:c r="O53" s="6"/>
       <x:c r="P53" s="7"/>
     </x:row>
-    <x:row r="54" ht="15.75" customHeight="1">
+    <x:row r="54" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A54" s="6" t="str">
         <x:v>KS-T-053</x:v>
       </x:c>
@@ -5748,10 +5847,10 @@
         <x:v>Sam</x:v>
       </x:c>
       <x:c r="K54" s="6" t="str">
-        <x:v>Not run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="L54" s="6"/>
-      <x:c r="M54" s="14"/>
+      <x:c r="M54" s="11"/>
       <x:c r="N54" s="6"/>
       <x:c r="O54" s="6"/>
       <x:c r="P54" s="7"/>
@@ -5766,7 +5865,7 @@
       <x:c r="C55" s="7" t="str">
         <x:v>App cold start time</x:v>
       </x:c>
-      <x:c r="D55" s="7" t="str">
+      <x:c r="D55" s="19" t="str">
         <x:v>1. Force-kill the app
 2. Cold start on emulator and real device, timing tap-to-home-interactive
 3. Repeat 3x per device</x:v>
@@ -5793,7 +5892,7 @@
         <x:v>Not run</x:v>
       </x:c>
       <x:c r="L55" s="6"/>
-      <x:c r="M55" s="14"/>
+      <x:c r="M55" s="11"/>
       <x:c r="N55" s="6"/>
       <x:c r="O55" s="6"/>
       <x:c r="P55" s="7"/>
@@ -5808,7 +5907,7 @@
       <x:c r="C56" s="7" t="str">
         <x:v>Home feed full-scroll smoothness</x:v>
       </x:c>
-      <x:c r="D56" s="7" t="str">
+      <x:c r="D56" s="19" t="str">
         <x:v>1. Seed 50+ items (Test Data sheet)
 2. Scroll the entire home feed on emulator and real device
 3. Note any jank / freezes</x:v>
@@ -5835,7 +5934,7 @@
         <x:v>Not run</x:v>
       </x:c>
       <x:c r="L56" s="6"/>
-      <x:c r="M56" s="14"/>
+      <x:c r="M56" s="11"/>
       <x:c r="N56" s="6"/>
       <x:c r="O56" s="6"/>
       <x:c r="P56" s="7"/>
@@ -5850,7 +5949,7 @@
       <x:c r="C57" s="7" t="str">
         <x:v>API latency baseline &amp; light load</x:v>
       </x:c>
-      <x:c r="D57" s="7" t="str">
+      <x:c r="D57" s="19" t="str">
         <x:v>1. Measure response time of key GET endpoints (items list, item detail, chat history)
 2. Load one endpoint with ~20 concurrent requests for 30 s (autocannon/k6/hey)
 3. Record p50/p95 and error count</x:v>
@@ -5877,12 +5976,12 @@
         <x:v>Not run</x:v>
       </x:c>
       <x:c r="L57" s="6"/>
-      <x:c r="M57" s="14"/>
+      <x:c r="M57" s="11"/>
       <x:c r="N57" s="6"/>
       <x:c r="O57" s="6"/>
       <x:c r="P57" s="7"/>
     </x:row>
-    <x:row r="58" ht="15.75" customHeight="1">
+    <x:row r="58" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A58" s="6" t="str">
         <x:v>KS-T-057</x:v>
       </x:c>
@@ -5892,7 +5991,7 @@
       <x:c r="C58" s="7" t="str">
         <x:v>Item detail image loading</x:v>
       </x:c>
-      <x:c r="D58" s="7" t="str">
+      <x:c r="D58" s="19" t="str">
         <x:v>1. Open a 5-photo item on a real device
 2. Repeat on a throttled connection if possible</x:v>
       </x:c>
@@ -5915,15 +6014,15 @@
         <x:v>Jack</x:v>
       </x:c>
       <x:c r="K58" s="6" t="str">
-        <x:v>Not run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="L58" s="6"/>
-      <x:c r="M58" s="14"/>
+      <x:c r="M58" s="11"/>
       <x:c r="N58" s="6"/>
       <x:c r="O58" s="6"/>
       <x:c r="P58" s="7"/>
     </x:row>
-    <x:row r="59" ht="15.75" customHeight="1">
+    <x:row r="59" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A59" s="6" t="str">
         <x:v>KS-T-058</x:v>
       </x:c>
@@ -5956,15 +6055,15 @@
         <x:v>Jenny</x:v>
       </x:c>
       <x:c r="K59" s="6" t="str">
-        <x:v>Not run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="L59" s="6"/>
-      <x:c r="M59" s="14"/>
+      <x:c r="M59" s="11"/>
       <x:c r="N59" s="6"/>
       <x:c r="O59" s="6"/>
       <x:c r="P59" s="7"/>
     </x:row>
-    <x:row r="60" ht="15.75" customHeight="1">
+    <x:row r="60" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A60" s="6" t="str">
         <x:v>KS-T-059</x:v>
       </x:c>
@@ -5996,15 +6095,15 @@
         <x:v>Jack</x:v>
       </x:c>
       <x:c r="K60" s="6" t="str">
-        <x:v>Not run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="L60" s="6"/>
-      <x:c r="M60" s="14"/>
+      <x:c r="M60" s="11"/>
       <x:c r="N60" s="6"/>
       <x:c r="O60" s="6"/>
       <x:c r="P60" s="7"/>
     </x:row>
-    <x:row r="61" ht="15.75" customHeight="1">
+    <x:row r="61" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A61" s="6" t="str">
         <x:v>KS-T-060</x:v>
       </x:c>
@@ -6041,8 +6140,8 @@
       <x:c r="L61" s="6" t="str">
         <x:v>Rui / Sam</x:v>
       </x:c>
-      <x:c r="M61" s="14" t="d">
-        <x:v>2026-09-19T00:00:00.000Z</x:v>
+      <x:c r="M61" s="11" t="n">
+        <x:v>46284</x:v>
       </x:c>
       <x:c r="N61" s="6"/>
       <x:c r="O61" s="6"/>
@@ -6050,7 +6149,7 @@
         <x:v>Marked Fail by Rui / Sam on 2026-09-19; GitHub defect link pending.</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" ht="15.75" customHeight="1">
+    <x:row r="62" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A62" s="6" t="str">
         <x:v>KS-T-061</x:v>
       </x:c>
@@ -6082,15 +6181,15 @@
         <x:v>Jaeger</x:v>
       </x:c>
       <x:c r="K62" s="6" t="str">
-        <x:v>Not run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="L62" s="6"/>
-      <x:c r="M62" s="14"/>
+      <x:c r="M62" s="11"/>
       <x:c r="N62" s="6"/>
       <x:c r="O62" s="6"/>
       <x:c r="P62" s="7"/>
     </x:row>
-    <x:row r="63" ht="15.75" customHeight="1">
+    <x:row r="63" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A63" s="6" t="str">
         <x:v>KS-T-062</x:v>
       </x:c>
@@ -6122,15 +6221,15 @@
         <x:v>Rui</x:v>
       </x:c>
       <x:c r="K63" s="6" t="str">
-        <x:v>Not run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="L63" s="6"/>
-      <x:c r="M63" s="14"/>
+      <x:c r="M63" s="11"/>
       <x:c r="N63" s="6"/>
       <x:c r="O63" s="6"/>
       <x:c r="P63" s="7"/>
     </x:row>
-    <x:row r="64" ht="15.75" customHeight="1">
+    <x:row r="64" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A64" s="6" t="str">
         <x:v>KS-T-063</x:v>
       </x:c>
@@ -6140,7 +6239,7 @@
       <x:c r="C64" s="7" t="str">
         <x:v>App resume / background</x:v>
       </x:c>
-      <x:c r="D64" s="7" t="str">
+      <x:c r="D64" s="19" t="str">
         <x:v>1. Background app mid-flow
 2. Return after 1 min and 10 min</x:v>
       </x:c>
@@ -6163,15 +6262,15 @@
         <x:v>Sam</x:v>
       </x:c>
       <x:c r="K64" s="6" t="str">
-        <x:v>Not run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="L64" s="6"/>
-      <x:c r="M64" s="14"/>
+      <x:c r="M64" s="11"/>
       <x:c r="N64" s="6"/>
       <x:c r="O64" s="6"/>
       <x:c r="P64" s="7"/>
     </x:row>
-    <x:row r="65" ht="15.75" customHeight="1">
+    <x:row r="65" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A65" s="6" t="str">
         <x:v>KS-T-064</x:v>
       </x:c>
@@ -6204,15 +6303,15 @@
         <x:v>Sam</x:v>
       </x:c>
       <x:c r="K65" s="6" t="str">
-        <x:v>Not run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="L65" s="6"/>
-      <x:c r="M65" s="14"/>
+      <x:c r="M65" s="11"/>
       <x:c r="N65" s="6"/>
       <x:c r="O65" s="6"/>
       <x:c r="P65" s="7"/>
     </x:row>
-    <x:row r="66" ht="15.75" customHeight="1">
+    <x:row r="66" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A66" s="6" t="str">
         <x:v>KS-T-065</x:v>
       </x:c>
@@ -6246,10 +6345,10 @@
         <x:v>Jenny</x:v>
       </x:c>
       <x:c r="K66" s="6" t="str">
-        <x:v>Not run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="L66" s="6"/>
-      <x:c r="M66" s="14"/>
+      <x:c r="M66" s="11"/>
       <x:c r="N66" s="6"/>
       <x:c r="O66" s="6"/>
       <x:c r="P66" s="7"/>
@@ -6291,7 +6390,7 @@
         <x:v>Not run</x:v>
       </x:c>
       <x:c r="L67" s="6"/>
-      <x:c r="M67" s="14"/>
+      <x:c r="M67" s="11"/>
       <x:c r="N67" s="6"/>
       <x:c r="O67" s="6"/>
       <x:c r="P67" s="7"/>
@@ -6333,7 +6432,7 @@
         <x:v>Not run</x:v>
       </x:c>
       <x:c r="L68" s="6"/>
-      <x:c r="M68" s="14"/>
+      <x:c r="M68" s="11"/>
       <x:c r="N68" s="6"/>
       <x:c r="O68" s="6"/>
       <x:c r="P68" s="7"/>
@@ -6375,7 +6474,7 @@
         <x:v>Not run</x:v>
       </x:c>
       <x:c r="L69" s="6"/>
-      <x:c r="M69" s="14"/>
+      <x:c r="M69" s="11"/>
       <x:c r="N69" s="6"/>
       <x:c r="O69" s="6"/>
       <x:c r="P69" s="7"/>
@@ -6417,12 +6516,12 @@
         <x:v>Not run</x:v>
       </x:c>
       <x:c r="L70" s="6"/>
-      <x:c r="M70" s="14"/>
+      <x:c r="M70" s="11"/>
       <x:c r="N70" s="6"/>
       <x:c r="O70" s="6"/>
       <x:c r="P70" s="7"/>
     </x:row>
-    <x:row r="71" ht="15.75" customHeight="1">
+    <x:row r="71" ht="15.75" hidden="1" customHeight="1">
       <x:c r="A71" s="6" t="str">
         <x:v>KS-T-070</x:v>
       </x:c>
@@ -6455,10 +6554,10 @@
         <x:v>Rui</x:v>
       </x:c>
       <x:c r="K71" s="6" t="str">
-        <x:v>Not run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="L71" s="6"/>
-      <x:c r="M71" s="14"/>
+      <x:c r="M71" s="11"/>
       <x:c r="N71" s="6"/>
       <x:c r="O71" s="6"/>
       <x:c r="P71" s="7"/>
@@ -7394,22 +7493,16 @@
     <x:row r="1000" ht="15.75" customHeight="1"/>
   </x:sheetData>
   <x:conditionalFormatting sqref="K2:K71">
-    <x:cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <x:cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <x:formula>"Pass"</x:formula>
     </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="K2:K71">
-    <x:cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <x:cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <x:formula>"Fail"</x:formula>
     </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="K2:K71">
-    <x:cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <x:cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
       <x:formula>"Blocked"</x:formula>
     </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="K2:K71">
-    <x:cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <x:cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
       <x:formula>"Not run"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
@@ -7424,7 +7517,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultColWidth="14.430000305175781" defaultRowHeight="15"/>
+  <x:sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="11" customWidth="1"/>
     <x:col min="2" max="2" width="12" customWidth="1"/>
@@ -7434,930 +7527,930 @@
     <x:col min="6" max="6" width="10" customWidth="1"/>
     <x:col min="7" max="10" width="11" customWidth="1"/>
     <x:col min="11" max="11" width="24" customWidth="1"/>
-    <x:col min="12" max="26" width="8.710000038146973" customWidth="1"/>
+    <x:col min="12" max="26" width="8.6640625" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>116</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>104</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>117</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>118</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
-        <x:v>119</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G1" s="2" t="s">
-        <x:v>120</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>121</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="I1" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J1" s="2" t="s">
-        <x:v>114</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="K1" s="2" t="s">
-        <x:v>115</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
+        <x:v>126</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="48">
       <x:c r="A2" s="7" t="s">
-        <x:v>122</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B2" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C2" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D2" s="7" t="s">
-        <x:v>125</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E2" s="7" t="s">
-        <x:v>126</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="F2" s="7" t="s">
-        <x:v>127</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="G2" s="7" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H2" s="7" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="I2" s="7" t="s">
-        <x:v>128</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="J2" s="7"/>
       <x:c r="K2" s="7" t="s">
-        <x:v>129</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="19" t="str">
-        <x:v>KS-B-002</x:v>
-      </x:c>
-      <x:c r="B3" s="19" t="str">
-        <x:v>KS-T-013</x:v>
-      </x:c>
-      <x:c r="C3" s="19" t="str">
-        <x:v>Profile</x:v>
-      </x:c>
-      <x:c r="D3" s="19" t="str">
-        <x:v>Registration accepted display names longer than 30 characters while Profile editing capped them at 30.</x:v>
-      </x:c>
-      <x:c r="E3" s="19" t="str">
-        <x:v>Register with a 32-character nickname, then edit the nickname in Profile and enter a 33rd character.</x:v>
-      </x:c>
-      <x:c r="F3" s="20" t="str">
-        <x:v>S3 Minor</x:v>
-      </x:c>
-      <x:c r="G3" s="19" t="str">
-        <x:v>Jenny</x:v>
-      </x:c>
-      <x:c r="H3" s="19" t="str">
-        <x:v>Jenny</x:v>
-      </x:c>
-      <x:c r="I3" s="20" t="str">
-        <x:v>Closed</x:v>
-      </x:c>
-      <x:c r="J3" s="21" t="d">
-        <x:v>2026-09-16T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="K3" s="19" t="str">
-        <x:v>Fixed in PR #309 by applying the 2-30 character limit consistently; the linked test case now passes.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="19" t="str">
-        <x:v>KS-B-003</x:v>
-      </x:c>
-      <x:c r="B4" s="19" t="str">
-        <x:v>KS-T-008</x:v>
-      </x:c>
-      <x:c r="C4" s="19" t="str">
-        <x:v>Profile</x:v>
-      </x:c>
-      <x:c r="D4" s="19" t="str">
-        <x:v>Floating labels overlapped adjacent fields in the change-password dialog.</x:v>
-      </x:c>
-      <x:c r="E4" s="19" t="str">
-        <x:v>Open Profile &gt; Change password and inspect spacing between the three password fields.</x:v>
-      </x:c>
-      <x:c r="F4" s="20" t="str">
-        <x:v>S4 Cosmetic</x:v>
-      </x:c>
-      <x:c r="G4" s="19" t="str">
-        <x:v>Jenny</x:v>
-      </x:c>
-      <x:c r="H4" s="19" t="str">
-        <x:v>Jenny</x:v>
-      </x:c>
-      <x:c r="I4" s="20" t="str">
-        <x:v>Closed</x:v>
-      </x:c>
-      <x:c r="J4" s="21" t="d">
-        <x:v>2026-09-16T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="K4" s="19" t="str">
-        <x:v>Fixed in PR #309 by restoring spacing between fields; the linked test case now passes.</x:v>
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="64">
+      <x:c r="A3" s="12" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B3" s="12" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D3" s="12" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="E3" s="12" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="F3" s="13" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="G3" s="12" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H3" s="12" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I3" s="13" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="J3" s="14">
+        <x:v>46281</x:v>
+      </x:c>
+      <x:c r="K3" s="12" t="s">
+        <x:v>147</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="48">
+      <x:c r="A4" s="12" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="B4" s="12" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="C4" s="12" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D4" s="12" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="E4" s="12" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="F4" s="13" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="G4" s="12" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H4" s="12" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I4" s="13" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="J4" s="14">
+        <x:v>46281</x:v>
+      </x:c>
+      <x:c r="K4" s="12" t="s">
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="F5" s="10"/>
-      <x:c r="I5" s="10"/>
+      <x:c r="F5" s="9"/>
+      <x:c r="I5" s="9"/>
     </x:row>
     <x:row r="6">
-      <x:c r="F6" s="10"/>
-      <x:c r="I6" s="10"/>
+      <x:c r="F6" s="9"/>
+      <x:c r="I6" s="9"/>
     </x:row>
     <x:row r="7">
-      <x:c r="F7" s="10"/>
-      <x:c r="I7" s="10"/>
+      <x:c r="F7" s="9"/>
+      <x:c r="I7" s="9"/>
     </x:row>
     <x:row r="8">
-      <x:c r="F8" s="10"/>
-      <x:c r="I8" s="10"/>
+      <x:c r="F8" s="9"/>
+      <x:c r="I8" s="9"/>
     </x:row>
     <x:row r="9">
-      <x:c r="F9" s="10"/>
-      <x:c r="I9" s="10"/>
+      <x:c r="F9" s="9"/>
+      <x:c r="I9" s="9"/>
     </x:row>
     <x:row r="10">
-      <x:c r="F10" s="10"/>
-      <x:c r="I10" s="10"/>
+      <x:c r="F10" s="9"/>
+      <x:c r="I10" s="9"/>
     </x:row>
     <x:row r="11">
-      <x:c r="F11" s="10"/>
-      <x:c r="I11" s="10"/>
+      <x:c r="F11" s="9"/>
+      <x:c r="I11" s="9"/>
     </x:row>
     <x:row r="12">
-      <x:c r="F12" s="10"/>
-      <x:c r="I12" s="10"/>
+      <x:c r="F12" s="9"/>
+      <x:c r="I12" s="9"/>
     </x:row>
     <x:row r="13">
-      <x:c r="F13" s="10"/>
-      <x:c r="I13" s="10"/>
+      <x:c r="F13" s="9"/>
+      <x:c r="I13" s="9"/>
     </x:row>
     <x:row r="14">
-      <x:c r="F14" s="10"/>
-      <x:c r="I14" s="10"/>
+      <x:c r="F14" s="9"/>
+      <x:c r="I14" s="9"/>
     </x:row>
     <x:row r="15">
-      <x:c r="F15" s="10"/>
-      <x:c r="I15" s="10"/>
+      <x:c r="F15" s="9"/>
+      <x:c r="I15" s="9"/>
     </x:row>
     <x:row r="16">
-      <x:c r="F16" s="10"/>
-      <x:c r="I16" s="10"/>
+      <x:c r="F16" s="9"/>
+      <x:c r="I16" s="9"/>
     </x:row>
     <x:row r="17">
-      <x:c r="F17" s="10"/>
-      <x:c r="I17" s="10"/>
+      <x:c r="F17" s="9"/>
+      <x:c r="I17" s="9"/>
     </x:row>
     <x:row r="18">
-      <x:c r="F18" s="10"/>
-      <x:c r="I18" s="10"/>
+      <x:c r="F18" s="9"/>
+      <x:c r="I18" s="9"/>
     </x:row>
     <x:row r="19">
-      <x:c r="F19" s="10"/>
-      <x:c r="I19" s="10"/>
+      <x:c r="F19" s="9"/>
+      <x:c r="I19" s="9"/>
     </x:row>
     <x:row r="20">
-      <x:c r="F20" s="10"/>
-      <x:c r="I20" s="10"/>
+      <x:c r="F20" s="9"/>
+      <x:c r="I20" s="9"/>
     </x:row>
     <x:row r="21" ht="15.75" customHeight="1">
-      <x:c r="F21" s="10"/>
-      <x:c r="I21" s="10"/>
+      <x:c r="F21" s="9"/>
+      <x:c r="I21" s="9"/>
     </x:row>
     <x:row r="22" ht="15.75" customHeight="1">
-      <x:c r="F22" s="10"/>
-      <x:c r="I22" s="10"/>
+      <x:c r="F22" s="9"/>
+      <x:c r="I22" s="9"/>
     </x:row>
     <x:row r="23" ht="15.75" customHeight="1">
-      <x:c r="F23" s="10"/>
-      <x:c r="I23" s="10"/>
+      <x:c r="F23" s="9"/>
+      <x:c r="I23" s="9"/>
     </x:row>
     <x:row r="24" ht="15.75" customHeight="1">
-      <x:c r="F24" s="10"/>
-      <x:c r="I24" s="10"/>
+      <x:c r="F24" s="9"/>
+      <x:c r="I24" s="9"/>
     </x:row>
     <x:row r="25" ht="15.75" customHeight="1">
-      <x:c r="F25" s="10"/>
-      <x:c r="I25" s="10"/>
+      <x:c r="F25" s="9"/>
+      <x:c r="I25" s="9"/>
     </x:row>
     <x:row r="26" ht="15.75" customHeight="1">
-      <x:c r="F26" s="10"/>
-      <x:c r="I26" s="10"/>
+      <x:c r="F26" s="9"/>
+      <x:c r="I26" s="9"/>
     </x:row>
     <x:row r="27" ht="15.75" customHeight="1">
-      <x:c r="F27" s="10"/>
-      <x:c r="I27" s="10"/>
+      <x:c r="F27" s="9"/>
+      <x:c r="I27" s="9"/>
     </x:row>
     <x:row r="28" ht="15.75" customHeight="1">
-      <x:c r="F28" s="10"/>
-      <x:c r="I28" s="10"/>
+      <x:c r="F28" s="9"/>
+      <x:c r="I28" s="9"/>
     </x:row>
     <x:row r="29" ht="15.75" customHeight="1">
-      <x:c r="F29" s="10"/>
-      <x:c r="I29" s="10"/>
+      <x:c r="F29" s="9"/>
+      <x:c r="I29" s="9"/>
     </x:row>
     <x:row r="30" ht="15.75" customHeight="1">
-      <x:c r="F30" s="10"/>
-      <x:c r="I30" s="10"/>
+      <x:c r="F30" s="9"/>
+      <x:c r="I30" s="9"/>
     </x:row>
     <x:row r="31" ht="15.75" customHeight="1">
-      <x:c r="F31" s="10"/>
-      <x:c r="I31" s="10"/>
+      <x:c r="F31" s="9"/>
+      <x:c r="I31" s="9"/>
     </x:row>
     <x:row r="32" ht="15.75" customHeight="1">
-      <x:c r="F32" s="10"/>
-      <x:c r="I32" s="10"/>
+      <x:c r="F32" s="9"/>
+      <x:c r="I32" s="9"/>
     </x:row>
     <x:row r="33" ht="15.75" customHeight="1">
-      <x:c r="F33" s="10"/>
-      <x:c r="I33" s="10"/>
+      <x:c r="F33" s="9"/>
+      <x:c r="I33" s="9"/>
     </x:row>
     <x:row r="34" ht="15.75" customHeight="1">
-      <x:c r="F34" s="10"/>
-      <x:c r="I34" s="10"/>
+      <x:c r="F34" s="9"/>
+      <x:c r="I34" s="9"/>
     </x:row>
     <x:row r="35" ht="15.75" customHeight="1">
-      <x:c r="F35" s="10"/>
-      <x:c r="I35" s="10"/>
+      <x:c r="F35" s="9"/>
+      <x:c r="I35" s="9"/>
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1">
-      <x:c r="F36" s="10"/>
-      <x:c r="I36" s="10"/>
+      <x:c r="F36" s="9"/>
+      <x:c r="I36" s="9"/>
     </x:row>
     <x:row r="37" ht="15.75" customHeight="1">
-      <x:c r="F37" s="10"/>
-      <x:c r="I37" s="10"/>
+      <x:c r="F37" s="9"/>
+      <x:c r="I37" s="9"/>
     </x:row>
     <x:row r="38" ht="15.75" customHeight="1">
-      <x:c r="F38" s="10"/>
-      <x:c r="I38" s="10"/>
+      <x:c r="F38" s="9"/>
+      <x:c r="I38" s="9"/>
     </x:row>
     <x:row r="39" ht="15.75" customHeight="1">
-      <x:c r="F39" s="10"/>
-      <x:c r="I39" s="10"/>
+      <x:c r="F39" s="9"/>
+      <x:c r="I39" s="9"/>
     </x:row>
     <x:row r="40" ht="15.75" customHeight="1">
-      <x:c r="F40" s="10"/>
-      <x:c r="I40" s="10"/>
+      <x:c r="F40" s="9"/>
+      <x:c r="I40" s="9"/>
     </x:row>
     <x:row r="41" ht="15.75" customHeight="1">
-      <x:c r="F41" s="10"/>
-      <x:c r="I41" s="10"/>
+      <x:c r="F41" s="9"/>
+      <x:c r="I41" s="9"/>
     </x:row>
     <x:row r="42" ht="15.75" customHeight="1">
-      <x:c r="F42" s="10"/>
-      <x:c r="I42" s="10"/>
+      <x:c r="F42" s="9"/>
+      <x:c r="I42" s="9"/>
     </x:row>
     <x:row r="43" ht="15.75" customHeight="1">
-      <x:c r="F43" s="10"/>
-      <x:c r="I43" s="10"/>
+      <x:c r="F43" s="9"/>
+      <x:c r="I43" s="9"/>
     </x:row>
     <x:row r="44" ht="15.75" customHeight="1">
-      <x:c r="F44" s="10"/>
-      <x:c r="I44" s="10"/>
+      <x:c r="F44" s="9"/>
+      <x:c r="I44" s="9"/>
     </x:row>
     <x:row r="45" ht="15.75" customHeight="1">
-      <x:c r="F45" s="10"/>
-      <x:c r="I45" s="10"/>
+      <x:c r="F45" s="9"/>
+      <x:c r="I45" s="9"/>
     </x:row>
     <x:row r="46" ht="15.75" customHeight="1">
-      <x:c r="F46" s="10"/>
-      <x:c r="I46" s="10"/>
+      <x:c r="F46" s="9"/>
+      <x:c r="I46" s="9"/>
     </x:row>
     <x:row r="47" ht="15.75" customHeight="1">
-      <x:c r="F47" s="10"/>
-      <x:c r="I47" s="10"/>
+      <x:c r="F47" s="9"/>
+      <x:c r="I47" s="9"/>
     </x:row>
     <x:row r="48" ht="15.75" customHeight="1">
-      <x:c r="F48" s="10"/>
-      <x:c r="I48" s="10"/>
+      <x:c r="F48" s="9"/>
+      <x:c r="I48" s="9"/>
     </x:row>
     <x:row r="49" ht="15.75" customHeight="1">
-      <x:c r="F49" s="10"/>
-      <x:c r="I49" s="10"/>
+      <x:c r="F49" s="9"/>
+      <x:c r="I49" s="9"/>
     </x:row>
     <x:row r="50" ht="15.75" customHeight="1">
-      <x:c r="F50" s="10"/>
-      <x:c r="I50" s="10"/>
+      <x:c r="F50" s="9"/>
+      <x:c r="I50" s="9"/>
     </x:row>
     <x:row r="51" ht="15.75" customHeight="1">
-      <x:c r="F51" s="10"/>
-      <x:c r="I51" s="10"/>
+      <x:c r="F51" s="9"/>
+      <x:c r="I51" s="9"/>
     </x:row>
     <x:row r="52" ht="15.75" customHeight="1">
-      <x:c r="F52" s="10"/>
-      <x:c r="I52" s="10"/>
+      <x:c r="F52" s="9"/>
+      <x:c r="I52" s="9"/>
     </x:row>
     <x:row r="53" ht="15.75" customHeight="1">
-      <x:c r="F53" s="10"/>
-      <x:c r="I53" s="10"/>
+      <x:c r="F53" s="9"/>
+      <x:c r="I53" s="9"/>
     </x:row>
     <x:row r="54" ht="15.75" customHeight="1">
-      <x:c r="F54" s="10"/>
-      <x:c r="I54" s="10"/>
+      <x:c r="F54" s="9"/>
+      <x:c r="I54" s="9"/>
     </x:row>
     <x:row r="55" ht="15.75" customHeight="1">
-      <x:c r="F55" s="10"/>
-      <x:c r="I55" s="10"/>
+      <x:c r="F55" s="9"/>
+      <x:c r="I55" s="9"/>
     </x:row>
     <x:row r="56" ht="15.75" customHeight="1">
-      <x:c r="F56" s="10"/>
-      <x:c r="I56" s="10"/>
+      <x:c r="F56" s="9"/>
+      <x:c r="I56" s="9"/>
     </x:row>
     <x:row r="57" ht="15.75" customHeight="1">
-      <x:c r="F57" s="10"/>
-      <x:c r="I57" s="10"/>
+      <x:c r="F57" s="9"/>
+      <x:c r="I57" s="9"/>
     </x:row>
     <x:row r="58" ht="15.75" customHeight="1">
-      <x:c r="F58" s="10"/>
-      <x:c r="I58" s="10"/>
+      <x:c r="F58" s="9"/>
+      <x:c r="I58" s="9"/>
     </x:row>
     <x:row r="59" ht="15.75" customHeight="1">
-      <x:c r="F59" s="10"/>
-      <x:c r="I59" s="10"/>
+      <x:c r="F59" s="9"/>
+      <x:c r="I59" s="9"/>
     </x:row>
     <x:row r="60" ht="15.75" customHeight="1">
-      <x:c r="F60" s="10"/>
-      <x:c r="I60" s="10"/>
+      <x:c r="F60" s="9"/>
+      <x:c r="I60" s="9"/>
     </x:row>
     <x:row r="61" ht="15.75" customHeight="1">
-      <x:c r="F61" s="10"/>
-      <x:c r="I61" s="10"/>
+      <x:c r="F61" s="9"/>
+      <x:c r="I61" s="9"/>
     </x:row>
     <x:row r="62" ht="15.75" customHeight="1">
-      <x:c r="F62" s="10"/>
-      <x:c r="I62" s="10"/>
+      <x:c r="F62" s="9"/>
+      <x:c r="I62" s="9"/>
     </x:row>
     <x:row r="63" ht="15.75" customHeight="1">
-      <x:c r="F63" s="10"/>
-      <x:c r="I63" s="10"/>
+      <x:c r="F63" s="9"/>
+      <x:c r="I63" s="9"/>
     </x:row>
     <x:row r="64" ht="15.75" customHeight="1">
-      <x:c r="F64" s="10"/>
-      <x:c r="I64" s="10"/>
+      <x:c r="F64" s="9"/>
+      <x:c r="I64" s="9"/>
     </x:row>
     <x:row r="65" ht="15.75" customHeight="1">
-      <x:c r="F65" s="10"/>
-      <x:c r="I65" s="10"/>
+      <x:c r="F65" s="9"/>
+      <x:c r="I65" s="9"/>
     </x:row>
     <x:row r="66" ht="15.75" customHeight="1">
-      <x:c r="F66" s="10"/>
-      <x:c r="I66" s="10"/>
+      <x:c r="F66" s="9"/>
+      <x:c r="I66" s="9"/>
     </x:row>
     <x:row r="67" ht="15.75" customHeight="1">
-      <x:c r="F67" s="10"/>
-      <x:c r="I67" s="10"/>
+      <x:c r="F67" s="9"/>
+      <x:c r="I67" s="9"/>
     </x:row>
     <x:row r="68" ht="15.75" customHeight="1">
-      <x:c r="F68" s="10"/>
-      <x:c r="I68" s="10"/>
+      <x:c r="F68" s="9"/>
+      <x:c r="I68" s="9"/>
     </x:row>
     <x:row r="69" ht="15.75" customHeight="1">
-      <x:c r="F69" s="10"/>
-      <x:c r="I69" s="10"/>
+      <x:c r="F69" s="9"/>
+      <x:c r="I69" s="9"/>
     </x:row>
     <x:row r="70" ht="15.75" customHeight="1">
-      <x:c r="F70" s="10"/>
-      <x:c r="I70" s="10"/>
+      <x:c r="F70" s="9"/>
+      <x:c r="I70" s="9"/>
     </x:row>
     <x:row r="71" ht="15.75" customHeight="1">
-      <x:c r="F71" s="10"/>
-      <x:c r="I71" s="10"/>
+      <x:c r="F71" s="9"/>
+      <x:c r="I71" s="9"/>
     </x:row>
     <x:row r="72" ht="15.75" customHeight="1">
-      <x:c r="F72" s="10"/>
-      <x:c r="I72" s="10"/>
+      <x:c r="F72" s="9"/>
+      <x:c r="I72" s="9"/>
     </x:row>
     <x:row r="73" ht="15.75" customHeight="1">
-      <x:c r="F73" s="10"/>
-      <x:c r="I73" s="10"/>
+      <x:c r="F73" s="9"/>
+      <x:c r="I73" s="9"/>
     </x:row>
     <x:row r="74" ht="15.75" customHeight="1">
-      <x:c r="F74" s="10"/>
-      <x:c r="I74" s="10"/>
+      <x:c r="F74" s="9"/>
+      <x:c r="I74" s="9"/>
     </x:row>
     <x:row r="75" ht="15.75" customHeight="1">
-      <x:c r="F75" s="10"/>
-      <x:c r="I75" s="10"/>
+      <x:c r="F75" s="9"/>
+      <x:c r="I75" s="9"/>
     </x:row>
     <x:row r="76" ht="15.75" customHeight="1">
-      <x:c r="F76" s="10"/>
-      <x:c r="I76" s="10"/>
+      <x:c r="F76" s="9"/>
+      <x:c r="I76" s="9"/>
     </x:row>
     <x:row r="77" ht="15.75" customHeight="1">
-      <x:c r="F77" s="10"/>
-      <x:c r="I77" s="10"/>
+      <x:c r="F77" s="9"/>
+      <x:c r="I77" s="9"/>
     </x:row>
     <x:row r="78" ht="15.75" customHeight="1">
-      <x:c r="F78" s="10"/>
-      <x:c r="I78" s="10"/>
+      <x:c r="F78" s="9"/>
+      <x:c r="I78" s="9"/>
     </x:row>
     <x:row r="79" ht="15.75" customHeight="1">
-      <x:c r="F79" s="10"/>
-      <x:c r="I79" s="10"/>
+      <x:c r="F79" s="9"/>
+      <x:c r="I79" s="9"/>
     </x:row>
     <x:row r="80" ht="15.75" customHeight="1">
-      <x:c r="F80" s="10"/>
-      <x:c r="I80" s="10"/>
+      <x:c r="F80" s="9"/>
+      <x:c r="I80" s="9"/>
     </x:row>
     <x:row r="81" ht="15.75" customHeight="1">
-      <x:c r="F81" s="10"/>
-      <x:c r="I81" s="10"/>
+      <x:c r="F81" s="9"/>
+      <x:c r="I81" s="9"/>
     </x:row>
     <x:row r="82" ht="15.75" customHeight="1">
-      <x:c r="F82" s="10"/>
-      <x:c r="I82" s="10"/>
+      <x:c r="F82" s="9"/>
+      <x:c r="I82" s="9"/>
     </x:row>
     <x:row r="83" ht="15.75" customHeight="1">
-      <x:c r="F83" s="10"/>
-      <x:c r="I83" s="10"/>
+      <x:c r="F83" s="9"/>
+      <x:c r="I83" s="9"/>
     </x:row>
     <x:row r="84" ht="15.75" customHeight="1">
-      <x:c r="F84" s="10"/>
-      <x:c r="I84" s="10"/>
+      <x:c r="F84" s="9"/>
+      <x:c r="I84" s="9"/>
     </x:row>
     <x:row r="85" ht="15.75" customHeight="1">
-      <x:c r="F85" s="10"/>
-      <x:c r="I85" s="10"/>
+      <x:c r="F85" s="9"/>
+      <x:c r="I85" s="9"/>
     </x:row>
     <x:row r="86" ht="15.75" customHeight="1">
-      <x:c r="F86" s="10"/>
-      <x:c r="I86" s="10"/>
+      <x:c r="F86" s="9"/>
+      <x:c r="I86" s="9"/>
     </x:row>
     <x:row r="87" ht="15.75" customHeight="1">
-      <x:c r="F87" s="10"/>
-      <x:c r="I87" s="10"/>
+      <x:c r="F87" s="9"/>
+      <x:c r="I87" s="9"/>
     </x:row>
     <x:row r="88" ht="15.75" customHeight="1">
-      <x:c r="F88" s="10"/>
-      <x:c r="I88" s="10"/>
+      <x:c r="F88" s="9"/>
+      <x:c r="I88" s="9"/>
     </x:row>
     <x:row r="89" ht="15.75" customHeight="1">
-      <x:c r="F89" s="10"/>
-      <x:c r="I89" s="10"/>
+      <x:c r="F89" s="9"/>
+      <x:c r="I89" s="9"/>
     </x:row>
     <x:row r="90" ht="15.75" customHeight="1">
-      <x:c r="F90" s="10"/>
-      <x:c r="I90" s="10"/>
+      <x:c r="F90" s="9"/>
+      <x:c r="I90" s="9"/>
     </x:row>
     <x:row r="91" ht="15.75" customHeight="1">
-      <x:c r="F91" s="10"/>
-      <x:c r="I91" s="10"/>
+      <x:c r="F91" s="9"/>
+      <x:c r="I91" s="9"/>
     </x:row>
     <x:row r="92" ht="15.75" customHeight="1">
-      <x:c r="F92" s="10"/>
-      <x:c r="I92" s="10"/>
+      <x:c r="F92" s="9"/>
+      <x:c r="I92" s="9"/>
     </x:row>
     <x:row r="93" ht="15.75" customHeight="1">
-      <x:c r="F93" s="10"/>
-      <x:c r="I93" s="10"/>
+      <x:c r="F93" s="9"/>
+      <x:c r="I93" s="9"/>
     </x:row>
     <x:row r="94" ht="15.75" customHeight="1">
-      <x:c r="F94" s="10"/>
-      <x:c r="I94" s="10"/>
+      <x:c r="F94" s="9"/>
+      <x:c r="I94" s="9"/>
     </x:row>
     <x:row r="95" ht="15.75" customHeight="1">
-      <x:c r="F95" s="10"/>
-      <x:c r="I95" s="10"/>
+      <x:c r="F95" s="9"/>
+      <x:c r="I95" s="9"/>
     </x:row>
     <x:row r="96" ht="15.75" customHeight="1">
-      <x:c r="F96" s="10"/>
-      <x:c r="I96" s="10"/>
+      <x:c r="F96" s="9"/>
+      <x:c r="I96" s="9"/>
     </x:row>
     <x:row r="97" ht="15.75" customHeight="1">
-      <x:c r="F97" s="10"/>
-      <x:c r="I97" s="10"/>
+      <x:c r="F97" s="9"/>
+      <x:c r="I97" s="9"/>
     </x:row>
     <x:row r="98" ht="15.75" customHeight="1">
-      <x:c r="F98" s="10"/>
-      <x:c r="I98" s="10"/>
+      <x:c r="F98" s="9"/>
+      <x:c r="I98" s="9"/>
     </x:row>
     <x:row r="99" ht="15.75" customHeight="1">
-      <x:c r="F99" s="10"/>
-      <x:c r="I99" s="10"/>
+      <x:c r="F99" s="9"/>
+      <x:c r="I99" s="9"/>
     </x:row>
     <x:row r="100" ht="15.75" customHeight="1">
-      <x:c r="F100" s="10"/>
-      <x:c r="I100" s="10"/>
+      <x:c r="F100" s="9"/>
+      <x:c r="I100" s="9"/>
     </x:row>
     <x:row r="101" ht="15.75" customHeight="1">
-      <x:c r="F101" s="10"/>
-      <x:c r="I101" s="10"/>
+      <x:c r="F101" s="9"/>
+      <x:c r="I101" s="9"/>
     </x:row>
     <x:row r="102" ht="15.75" customHeight="1">
-      <x:c r="F102" s="10"/>
-      <x:c r="I102" s="10"/>
+      <x:c r="F102" s="9"/>
+      <x:c r="I102" s="9"/>
     </x:row>
     <x:row r="103" ht="15.75" customHeight="1">
-      <x:c r="F103" s="10"/>
-      <x:c r="I103" s="10"/>
+      <x:c r="F103" s="9"/>
+      <x:c r="I103" s="9"/>
     </x:row>
     <x:row r="104" ht="15.75" customHeight="1">
-      <x:c r="F104" s="10"/>
-      <x:c r="I104" s="10"/>
+      <x:c r="F104" s="9"/>
+      <x:c r="I104" s="9"/>
     </x:row>
     <x:row r="105" ht="15.75" customHeight="1">
-      <x:c r="F105" s="10"/>
-      <x:c r="I105" s="10"/>
+      <x:c r="F105" s="9"/>
+      <x:c r="I105" s="9"/>
     </x:row>
     <x:row r="106" ht="15.75" customHeight="1">
-      <x:c r="F106" s="10"/>
-      <x:c r="I106" s="10"/>
+      <x:c r="F106" s="9"/>
+      <x:c r="I106" s="9"/>
     </x:row>
     <x:row r="107" ht="15.75" customHeight="1">
-      <x:c r="F107" s="10"/>
-      <x:c r="I107" s="10"/>
+      <x:c r="F107" s="9"/>
+      <x:c r="I107" s="9"/>
     </x:row>
     <x:row r="108" ht="15.75" customHeight="1">
-      <x:c r="F108" s="10"/>
-      <x:c r="I108" s="10"/>
+      <x:c r="F108" s="9"/>
+      <x:c r="I108" s="9"/>
     </x:row>
     <x:row r="109" ht="15.75" customHeight="1">
-      <x:c r="F109" s="10"/>
-      <x:c r="I109" s="10"/>
+      <x:c r="F109" s="9"/>
+      <x:c r="I109" s="9"/>
     </x:row>
     <x:row r="110" ht="15.75" customHeight="1">
-      <x:c r="F110" s="10"/>
-      <x:c r="I110" s="10"/>
+      <x:c r="F110" s="9"/>
+      <x:c r="I110" s="9"/>
     </x:row>
     <x:row r="111" ht="15.75" customHeight="1">
-      <x:c r="F111" s="10"/>
-      <x:c r="I111" s="10"/>
+      <x:c r="F111" s="9"/>
+      <x:c r="I111" s="9"/>
     </x:row>
     <x:row r="112" ht="15.75" customHeight="1">
-      <x:c r="F112" s="10"/>
-      <x:c r="I112" s="10"/>
+      <x:c r="F112" s="9"/>
+      <x:c r="I112" s="9"/>
     </x:row>
     <x:row r="113" ht="15.75" customHeight="1">
-      <x:c r="F113" s="10"/>
-      <x:c r="I113" s="10"/>
+      <x:c r="F113" s="9"/>
+      <x:c r="I113" s="9"/>
     </x:row>
     <x:row r="114" ht="15.75" customHeight="1">
-      <x:c r="F114" s="10"/>
-      <x:c r="I114" s="10"/>
+      <x:c r="F114" s="9"/>
+      <x:c r="I114" s="9"/>
     </x:row>
     <x:row r="115" ht="15.75" customHeight="1">
-      <x:c r="F115" s="10"/>
-      <x:c r="I115" s="10"/>
+      <x:c r="F115" s="9"/>
+      <x:c r="I115" s="9"/>
     </x:row>
     <x:row r="116" ht="15.75" customHeight="1">
-      <x:c r="F116" s="10"/>
-      <x:c r="I116" s="10"/>
+      <x:c r="F116" s="9"/>
+      <x:c r="I116" s="9"/>
     </x:row>
     <x:row r="117" ht="15.75" customHeight="1">
-      <x:c r="F117" s="10"/>
-      <x:c r="I117" s="10"/>
+      <x:c r="F117" s="9"/>
+      <x:c r="I117" s="9"/>
     </x:row>
     <x:row r="118" ht="15.75" customHeight="1">
-      <x:c r="F118" s="10"/>
-      <x:c r="I118" s="10"/>
+      <x:c r="F118" s="9"/>
+      <x:c r="I118" s="9"/>
     </x:row>
     <x:row r="119" ht="15.75" customHeight="1">
-      <x:c r="F119" s="10"/>
-      <x:c r="I119" s="10"/>
+      <x:c r="F119" s="9"/>
+      <x:c r="I119" s="9"/>
     </x:row>
     <x:row r="120" ht="15.75" customHeight="1">
-      <x:c r="F120" s="10"/>
-      <x:c r="I120" s="10"/>
+      <x:c r="F120" s="9"/>
+      <x:c r="I120" s="9"/>
     </x:row>
     <x:row r="121" ht="15.75" customHeight="1">
-      <x:c r="F121" s="10"/>
-      <x:c r="I121" s="10"/>
+      <x:c r="F121" s="9"/>
+      <x:c r="I121" s="9"/>
     </x:row>
     <x:row r="122" ht="15.75" customHeight="1">
-      <x:c r="F122" s="10"/>
-      <x:c r="I122" s="10"/>
+      <x:c r="F122" s="9"/>
+      <x:c r="I122" s="9"/>
     </x:row>
     <x:row r="123" ht="15.75" customHeight="1">
-      <x:c r="F123" s="10"/>
-      <x:c r="I123" s="10"/>
+      <x:c r="F123" s="9"/>
+      <x:c r="I123" s="9"/>
     </x:row>
     <x:row r="124" ht="15.75" customHeight="1">
-      <x:c r="F124" s="10"/>
-      <x:c r="I124" s="10"/>
+      <x:c r="F124" s="9"/>
+      <x:c r="I124" s="9"/>
     </x:row>
     <x:row r="125" ht="15.75" customHeight="1">
-      <x:c r="F125" s="10"/>
-      <x:c r="I125" s="10"/>
+      <x:c r="F125" s="9"/>
+      <x:c r="I125" s="9"/>
     </x:row>
     <x:row r="126" ht="15.75" customHeight="1">
-      <x:c r="F126" s="10"/>
-      <x:c r="I126" s="10"/>
+      <x:c r="F126" s="9"/>
+      <x:c r="I126" s="9"/>
     </x:row>
     <x:row r="127" ht="15.75" customHeight="1">
-      <x:c r="F127" s="10"/>
-      <x:c r="I127" s="10"/>
+      <x:c r="F127" s="9"/>
+      <x:c r="I127" s="9"/>
     </x:row>
     <x:row r="128" ht="15.75" customHeight="1">
-      <x:c r="F128" s="10"/>
-      <x:c r="I128" s="10"/>
+      <x:c r="F128" s="9"/>
+      <x:c r="I128" s="9"/>
     </x:row>
     <x:row r="129" ht="15.75" customHeight="1">
-      <x:c r="F129" s="10"/>
-      <x:c r="I129" s="10"/>
+      <x:c r="F129" s="9"/>
+      <x:c r="I129" s="9"/>
     </x:row>
     <x:row r="130" ht="15.75" customHeight="1">
-      <x:c r="F130" s="10"/>
-      <x:c r="I130" s="10"/>
+      <x:c r="F130" s="9"/>
+      <x:c r="I130" s="9"/>
     </x:row>
     <x:row r="131" ht="15.75" customHeight="1">
-      <x:c r="F131" s="10"/>
-      <x:c r="I131" s="10"/>
+      <x:c r="F131" s="9"/>
+      <x:c r="I131" s="9"/>
     </x:row>
     <x:row r="132" ht="15.75" customHeight="1">
-      <x:c r="F132" s="10"/>
-      <x:c r="I132" s="10"/>
+      <x:c r="F132" s="9"/>
+      <x:c r="I132" s="9"/>
     </x:row>
     <x:row r="133" ht="15.75" customHeight="1">
-      <x:c r="F133" s="10"/>
-      <x:c r="I133" s="10"/>
+      <x:c r="F133" s="9"/>
+      <x:c r="I133" s="9"/>
     </x:row>
     <x:row r="134" ht="15.75" customHeight="1">
-      <x:c r="F134" s="10"/>
-      <x:c r="I134" s="10"/>
+      <x:c r="F134" s="9"/>
+      <x:c r="I134" s="9"/>
     </x:row>
     <x:row r="135" ht="15.75" customHeight="1">
-      <x:c r="F135" s="10"/>
-      <x:c r="I135" s="10"/>
+      <x:c r="F135" s="9"/>
+      <x:c r="I135" s="9"/>
     </x:row>
     <x:row r="136" ht="15.75" customHeight="1">
-      <x:c r="F136" s="10"/>
-      <x:c r="I136" s="10"/>
+      <x:c r="F136" s="9"/>
+      <x:c r="I136" s="9"/>
     </x:row>
     <x:row r="137" ht="15.75" customHeight="1">
-      <x:c r="F137" s="10"/>
-      <x:c r="I137" s="10"/>
+      <x:c r="F137" s="9"/>
+      <x:c r="I137" s="9"/>
     </x:row>
     <x:row r="138" ht="15.75" customHeight="1">
-      <x:c r="F138" s="10"/>
-      <x:c r="I138" s="10"/>
+      <x:c r="F138" s="9"/>
+      <x:c r="I138" s="9"/>
     </x:row>
     <x:row r="139" ht="15.75" customHeight="1">
-      <x:c r="F139" s="10"/>
-      <x:c r="I139" s="10"/>
+      <x:c r="F139" s="9"/>
+      <x:c r="I139" s="9"/>
     </x:row>
     <x:row r="140" ht="15.75" customHeight="1">
-      <x:c r="F140" s="10"/>
-      <x:c r="I140" s="10"/>
+      <x:c r="F140" s="9"/>
+      <x:c r="I140" s="9"/>
     </x:row>
     <x:row r="141" ht="15.75" customHeight="1">
-      <x:c r="F141" s="10"/>
-      <x:c r="I141" s="10"/>
+      <x:c r="F141" s="9"/>
+      <x:c r="I141" s="9"/>
     </x:row>
     <x:row r="142" ht="15.75" customHeight="1">
-      <x:c r="F142" s="10"/>
-      <x:c r="I142" s="10"/>
+      <x:c r="F142" s="9"/>
+      <x:c r="I142" s="9"/>
     </x:row>
     <x:row r="143" ht="15.75" customHeight="1">
-      <x:c r="F143" s="10"/>
-      <x:c r="I143" s="10"/>
+      <x:c r="F143" s="9"/>
+      <x:c r="I143" s="9"/>
     </x:row>
     <x:row r="144" ht="15.75" customHeight="1">
-      <x:c r="F144" s="10"/>
-      <x:c r="I144" s="10"/>
+      <x:c r="F144" s="9"/>
+      <x:c r="I144" s="9"/>
     </x:row>
     <x:row r="145" ht="15.75" customHeight="1">
-      <x:c r="F145" s="10"/>
-      <x:c r="I145" s="10"/>
+      <x:c r="F145" s="9"/>
+      <x:c r="I145" s="9"/>
     </x:row>
     <x:row r="146" ht="15.75" customHeight="1">
-      <x:c r="F146" s="10"/>
-      <x:c r="I146" s="10"/>
+      <x:c r="F146" s="9"/>
+      <x:c r="I146" s="9"/>
     </x:row>
     <x:row r="147" ht="15.75" customHeight="1">
-      <x:c r="F147" s="10"/>
-      <x:c r="I147" s="10"/>
+      <x:c r="F147" s="9"/>
+      <x:c r="I147" s="9"/>
     </x:row>
     <x:row r="148" ht="15.75" customHeight="1">
-      <x:c r="F148" s="10"/>
-      <x:c r="I148" s="10"/>
+      <x:c r="F148" s="9"/>
+      <x:c r="I148" s="9"/>
     </x:row>
     <x:row r="149" ht="15.75" customHeight="1">
-      <x:c r="F149" s="10"/>
-      <x:c r="I149" s="10"/>
+      <x:c r="F149" s="9"/>
+      <x:c r="I149" s="9"/>
     </x:row>
     <x:row r="150" ht="15.75" customHeight="1">
-      <x:c r="F150" s="10"/>
-      <x:c r="I150" s="10"/>
+      <x:c r="F150" s="9"/>
+      <x:c r="I150" s="9"/>
     </x:row>
     <x:row r="151" ht="15.75" customHeight="1">
-      <x:c r="F151" s="10"/>
-      <x:c r="I151" s="10"/>
+      <x:c r="F151" s="9"/>
+      <x:c r="I151" s="9"/>
     </x:row>
     <x:row r="152" ht="15.75" customHeight="1">
-      <x:c r="F152" s="10"/>
-      <x:c r="I152" s="10"/>
+      <x:c r="F152" s="9"/>
+      <x:c r="I152" s="9"/>
     </x:row>
     <x:row r="153" ht="15.75" customHeight="1">
-      <x:c r="F153" s="10"/>
-      <x:c r="I153" s="10"/>
+      <x:c r="F153" s="9"/>
+      <x:c r="I153" s="9"/>
     </x:row>
     <x:row r="154" ht="15.75" customHeight="1">
-      <x:c r="F154" s="10"/>
-      <x:c r="I154" s="10"/>
+      <x:c r="F154" s="9"/>
+      <x:c r="I154" s="9"/>
     </x:row>
     <x:row r="155" ht="15.75" customHeight="1">
-      <x:c r="F155" s="10"/>
-      <x:c r="I155" s="10"/>
+      <x:c r="F155" s="9"/>
+      <x:c r="I155" s="9"/>
     </x:row>
     <x:row r="156" ht="15.75" customHeight="1">
-      <x:c r="F156" s="10"/>
-      <x:c r="I156" s="10"/>
+      <x:c r="F156" s="9"/>
+      <x:c r="I156" s="9"/>
     </x:row>
     <x:row r="157" ht="15.75" customHeight="1">
-      <x:c r="F157" s="10"/>
-      <x:c r="I157" s="10"/>
+      <x:c r="F157" s="9"/>
+      <x:c r="I157" s="9"/>
     </x:row>
     <x:row r="158" ht="15.75" customHeight="1">
-      <x:c r="F158" s="10"/>
-      <x:c r="I158" s="10"/>
+      <x:c r="F158" s="9"/>
+      <x:c r="I158" s="9"/>
     </x:row>
     <x:row r="159" ht="15.75" customHeight="1">
-      <x:c r="F159" s="10"/>
-      <x:c r="I159" s="10"/>
+      <x:c r="F159" s="9"/>
+      <x:c r="I159" s="9"/>
     </x:row>
     <x:row r="160" ht="15.75" customHeight="1">
-      <x:c r="F160" s="10"/>
-      <x:c r="I160" s="10"/>
+      <x:c r="F160" s="9"/>
+      <x:c r="I160" s="9"/>
     </x:row>
     <x:row r="161" ht="15.75" customHeight="1">
-      <x:c r="F161" s="10"/>
-      <x:c r="I161" s="10"/>
+      <x:c r="F161" s="9"/>
+      <x:c r="I161" s="9"/>
     </x:row>
     <x:row r="162" ht="15.75" customHeight="1">
-      <x:c r="F162" s="10"/>
-      <x:c r="I162" s="10"/>
+      <x:c r="F162" s="9"/>
+      <x:c r="I162" s="9"/>
     </x:row>
     <x:row r="163" ht="15.75" customHeight="1">
-      <x:c r="F163" s="10"/>
-      <x:c r="I163" s="10"/>
+      <x:c r="F163" s="9"/>
+      <x:c r="I163" s="9"/>
     </x:row>
     <x:row r="164" ht="15.75" customHeight="1">
-      <x:c r="F164" s="10"/>
-      <x:c r="I164" s="10"/>
+      <x:c r="F164" s="9"/>
+      <x:c r="I164" s="9"/>
     </x:row>
     <x:row r="165" ht="15.75" customHeight="1">
-      <x:c r="F165" s="10"/>
-      <x:c r="I165" s="10"/>
+      <x:c r="F165" s="9"/>
+      <x:c r="I165" s="9"/>
     </x:row>
     <x:row r="166" ht="15.75" customHeight="1">
-      <x:c r="F166" s="10"/>
-      <x:c r="I166" s="10"/>
+      <x:c r="F166" s="9"/>
+      <x:c r="I166" s="9"/>
     </x:row>
     <x:row r="167" ht="15.75" customHeight="1">
-      <x:c r="F167" s="10"/>
-      <x:c r="I167" s="10"/>
+      <x:c r="F167" s="9"/>
+      <x:c r="I167" s="9"/>
     </x:row>
     <x:row r="168" ht="15.75" customHeight="1">
-      <x:c r="F168" s="10"/>
-      <x:c r="I168" s="10"/>
+      <x:c r="F168" s="9"/>
+      <x:c r="I168" s="9"/>
     </x:row>
     <x:row r="169" ht="15.75" customHeight="1">
-      <x:c r="F169" s="10"/>
-      <x:c r="I169" s="10"/>
+      <x:c r="F169" s="9"/>
+      <x:c r="I169" s="9"/>
     </x:row>
     <x:row r="170" ht="15.75" customHeight="1">
-      <x:c r="F170" s="10"/>
-      <x:c r="I170" s="10"/>
+      <x:c r="F170" s="9"/>
+      <x:c r="I170" s="9"/>
     </x:row>
     <x:row r="171" ht="15.75" customHeight="1">
-      <x:c r="F171" s="10"/>
-      <x:c r="I171" s="10"/>
+      <x:c r="F171" s="9"/>
+      <x:c r="I171" s="9"/>
     </x:row>
     <x:row r="172" ht="15.75" customHeight="1">
-      <x:c r="F172" s="10"/>
-      <x:c r="I172" s="10"/>
+      <x:c r="F172" s="9"/>
+      <x:c r="I172" s="9"/>
     </x:row>
     <x:row r="173" ht="15.75" customHeight="1">
-      <x:c r="F173" s="10"/>
-      <x:c r="I173" s="10"/>
+      <x:c r="F173" s="9"/>
+      <x:c r="I173" s="9"/>
     </x:row>
     <x:row r="174" ht="15.75" customHeight="1">
-      <x:c r="F174" s="10"/>
-      <x:c r="I174" s="10"/>
+      <x:c r="F174" s="9"/>
+      <x:c r="I174" s="9"/>
     </x:row>
     <x:row r="175" ht="15.75" customHeight="1">
-      <x:c r="F175" s="10"/>
-      <x:c r="I175" s="10"/>
+      <x:c r="F175" s="9"/>
+      <x:c r="I175" s="9"/>
     </x:row>
     <x:row r="176" ht="15.75" customHeight="1">
-      <x:c r="F176" s="10"/>
-      <x:c r="I176" s="10"/>
+      <x:c r="F176" s="9"/>
+      <x:c r="I176" s="9"/>
     </x:row>
     <x:row r="177" ht="15.75" customHeight="1">
-      <x:c r="F177" s="10"/>
-      <x:c r="I177" s="10"/>
+      <x:c r="F177" s="9"/>
+      <x:c r="I177" s="9"/>
     </x:row>
     <x:row r="178" ht="15.75" customHeight="1">
-      <x:c r="F178" s="10"/>
-      <x:c r="I178" s="10"/>
+      <x:c r="F178" s="9"/>
+      <x:c r="I178" s="9"/>
     </x:row>
     <x:row r="179" ht="15.75" customHeight="1">
-      <x:c r="F179" s="10"/>
-      <x:c r="I179" s="10"/>
+      <x:c r="F179" s="9"/>
+      <x:c r="I179" s="9"/>
     </x:row>
     <x:row r="180" ht="15.75" customHeight="1">
-      <x:c r="F180" s="10"/>
-      <x:c r="I180" s="10"/>
+      <x:c r="F180" s="9"/>
+      <x:c r="I180" s="9"/>
     </x:row>
     <x:row r="181" ht="15.75" customHeight="1">
-      <x:c r="F181" s="10"/>
-      <x:c r="I181" s="10"/>
+      <x:c r="F181" s="9"/>
+      <x:c r="I181" s="9"/>
     </x:row>
     <x:row r="182" ht="15.75" customHeight="1">
-      <x:c r="F182" s="10"/>
-      <x:c r="I182" s="10"/>
+      <x:c r="F182" s="9"/>
+      <x:c r="I182" s="9"/>
     </x:row>
     <x:row r="183" ht="15.75" customHeight="1">
-      <x:c r="F183" s="10"/>
-      <x:c r="I183" s="10"/>
+      <x:c r="F183" s="9"/>
+      <x:c r="I183" s="9"/>
     </x:row>
     <x:row r="184" ht="15.75" customHeight="1">
-      <x:c r="F184" s="10"/>
-      <x:c r="I184" s="10"/>
+      <x:c r="F184" s="9"/>
+      <x:c r="I184" s="9"/>
     </x:row>
     <x:row r="185" ht="15.75" customHeight="1">
-      <x:c r="F185" s="10"/>
-      <x:c r="I185" s="10"/>
+      <x:c r="F185" s="9"/>
+      <x:c r="I185" s="9"/>
     </x:row>
     <x:row r="186" ht="15.75" customHeight="1">
-      <x:c r="F186" s="10"/>
-      <x:c r="I186" s="10"/>
+      <x:c r="F186" s="9"/>
+      <x:c r="I186" s="9"/>
     </x:row>
     <x:row r="187" ht="15.75" customHeight="1">
-      <x:c r="F187" s="10"/>
-      <x:c r="I187" s="10"/>
+      <x:c r="F187" s="9"/>
+      <x:c r="I187" s="9"/>
     </x:row>
     <x:row r="188" ht="15.75" customHeight="1">
-      <x:c r="F188" s="10"/>
-      <x:c r="I188" s="10"/>
+      <x:c r="F188" s="9"/>
+      <x:c r="I188" s="9"/>
     </x:row>
     <x:row r="189" ht="15.75" customHeight="1">
-      <x:c r="F189" s="10"/>
-      <x:c r="I189" s="10"/>
+      <x:c r="F189" s="9"/>
+      <x:c r="I189" s="9"/>
     </x:row>
     <x:row r="190" ht="15.75" customHeight="1">
-      <x:c r="F190" s="10"/>
-      <x:c r="I190" s="10"/>
+      <x:c r="F190" s="9"/>
+      <x:c r="I190" s="9"/>
     </x:row>
     <x:row r="191" ht="15.75" customHeight="1">
-      <x:c r="F191" s="10"/>
-      <x:c r="I191" s="10"/>
+      <x:c r="F191" s="9"/>
+      <x:c r="I191" s="9"/>
     </x:row>
     <x:row r="192" ht="15.75" customHeight="1">
-      <x:c r="F192" s="10"/>
-      <x:c r="I192" s="10"/>
+      <x:c r="F192" s="9"/>
+      <x:c r="I192" s="9"/>
     </x:row>
     <x:row r="193" ht="15.75" customHeight="1">
-      <x:c r="F193" s="10"/>
-      <x:c r="I193" s="10"/>
+      <x:c r="F193" s="9"/>
+      <x:c r="I193" s="9"/>
     </x:row>
     <x:row r="194" ht="15.75" customHeight="1">
-      <x:c r="F194" s="10"/>
-      <x:c r="I194" s="10"/>
+      <x:c r="F194" s="9"/>
+      <x:c r="I194" s="9"/>
     </x:row>
     <x:row r="195" ht="15.75" customHeight="1">
-      <x:c r="F195" s="10"/>
-      <x:c r="I195" s="10"/>
+      <x:c r="F195" s="9"/>
+      <x:c r="I195" s="9"/>
     </x:row>
     <x:row r="196" ht="15.75" customHeight="1">
-      <x:c r="F196" s="10"/>
-      <x:c r="I196" s="10"/>
+      <x:c r="F196" s="9"/>
+      <x:c r="I196" s="9"/>
     </x:row>
     <x:row r="197" ht="15.75" customHeight="1">
-      <x:c r="F197" s="10"/>
-      <x:c r="I197" s="10"/>
+      <x:c r="F197" s="9"/>
+      <x:c r="I197" s="9"/>
     </x:row>
     <x:row r="198" ht="15.75" customHeight="1">
-      <x:c r="F198" s="10"/>
-      <x:c r="I198" s="10"/>
+      <x:c r="F198" s="9"/>
+      <x:c r="I198" s="9"/>
     </x:row>
     <x:row r="199" ht="15.75" customHeight="1">
-      <x:c r="F199" s="10"/>
-      <x:c r="I199" s="10"/>
+      <x:c r="F199" s="9"/>
+      <x:c r="I199" s="9"/>
     </x:row>
     <x:row r="200" ht="15.75" customHeight="1">
-      <x:c r="F200" s="10"/>
-      <x:c r="I200" s="10"/>
+      <x:c r="F200" s="9"/>
+      <x:c r="I200" s="9"/>
     </x:row>
     <x:row r="201" ht="15.75" customHeight="1"/>
     <x:row r="202" ht="15.75" customHeight="1"/>
@@ -9161,27 +9254,19 @@
     <x:row r="1000" ht="15.75" customHeight="1"/>
   </x:sheetData>
   <x:conditionalFormatting sqref="I2:I1000">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <x:cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <x:formula>"Open"</x:formula>
     </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="I2:I1000">
-    <x:cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <x:cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <x:formula>"Fixed"</x:formula>
     </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="I2:I1000">
-    <x:cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <x:cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <x:formula>"Closed"</x:formula>
     </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="I2:I1000">
-    <x:cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <x:cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <x:formula>"In progress"</x:formula>
     </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="I2:I1000">
-    <x:cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
+    <x:cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <x:formula>"Retest"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>

--- a/docs/testing-strategy/kiwishare-release-test-results-v0.2.xlsx
+++ b/docs/testing-strategy/kiwishare-release-test-results-v0.2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Rdd307d4777844405"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data &amp; Setup" sheetId="2" r:id="R201d8dcc24af4d16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="3" r:id="R882edabbf8e04efe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Log" sheetId="4" r:id="R2dc9307139ac4bc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R7f1f8eec109945ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data &amp; Setup" sheetId="2" r:id="Rfd4bcea8049d437b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="3" r:id="R783d1785f4bd4bb9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Log" sheetId="4" r:id="R9b4c2cd50c5c4b0a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -394,6 +394,991 @@
     <x:t xml:space="preserve">Notes</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">KS-T-001</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Auth</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Register with email/password</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Sign up with a new email/password
+2. Complete any verification</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Account created, logged in, profile with default displayName</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Functional</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">iOS+Android</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Jenny; Rui / Sam</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Also passed by Rui / Sam on 2026-09-19 (Chinese test plan).</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-002</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Login with valid credentials</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Log out if needed
+2. Log in with existing account</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Home screen loads with user session</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-003</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Login with wrong password</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Enter valid email + wrong password
+2. Submit</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Clear error message; no crash; stays on login</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Error state</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-004</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Login with unregistered email</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Enter email never registered
+2. Submit</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Generic error, no user-enumeration hint</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Security</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-005</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Forgot password — request OTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Use a real inbox you can open (gmail alias, see Test Data sheet)
+2. Tap Forgot password, enter that email, submit
+3. Check inbox for the OTP
+4. Re-request within the cooldown window</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">OTP email received; re-request within cooldown is rejected with countdown</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Jenny (emulator); Rui / Sam</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Retested as Pass in the updated test plan. Historical screenshot removed because it contained personal information. Replacement evidence and retest metadata are pending.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-006</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Forgot password — wrong / expired OTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Request OTP
+2. Enter wrong code
+3. Then enter expired code</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Both rejected with clear error; no crash</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-007</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Reset password completes</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Complete forgot-password with valid OTP
+2. Set new password
+3. Log in with new; try old</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">New password works, old password rejected</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-008</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Change password from profile</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Profile &gt; Account &gt; Change password
+2. Provide current + new password</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Success feedback; next login requires new password</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-B-003</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-B-003 | KS-T-008 | Profile | Change-password dialog: floating labels overlap the field above (no spacing between the three TextFormFields) | Profile &gt; Change password, observe dialog | S4 Cosmetic | Jenny | Jenny | Open |  | Add SizedBox(height:16) between fields</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-009</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Logout &amp; session invalidation</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Log out
+2. Attempt to open protected screens
+3. Relaunch app</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Returns to login; protected content inaccessible; session stays logged out</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-010</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Profile</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Profile shows identity data</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Open Profile with a user that has avatar + items</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Avatar, displayName, trust score, verified badge correct</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-011</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Edit avatar (R2 upload)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Tap avatar
+2. Pick image from gallery/camera</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">New avatar uploads and shows in Profile, item cards and chat header</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-012</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Edit nickname (displayName)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Account &gt; Edit nickname
+2. Enter 2–30 chars
+3. Save</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">New name reflected on Profile, item cards and chat conversations</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-013</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Nickname validation</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Enter 1-char name
+2. Enter 30+ chars</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Both rejected with validation message</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-B-002</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-B-002 | KS-T-013 | Profile | Registration accepts displayName &gt;30 chars; edit dialog silently truncates to 30 (inconsistent length limits across entry points) | Register with a 32-char nickname, then edit nickname in Profile and type a 33rd char | S3 Minor | Jenny | Jenny | Open |  | Server /auth/register lacks the 2-30 length check that PUT /users has (users.ts:59); client edit uses maxLength:30</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-014</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No-avatar placeholder</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Use account without avatar</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Initials placeholder shown, no broken image</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Empty state</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Rui / Sam</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Imported from the Chinese test plan completed by Rui / Sam on 2026-09-19.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-015</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Watchlist tab in profile</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Open Profile &gt; Watchlist with saved items
+2. With an account that has none</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Saved items listed; empty state message when none</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-016</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Report history (Safety &amp; support)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Report an item (see KS-T-053)
+2. Open Profile &gt; Safety &amp; support &gt; Report history</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The report appears with status and date</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-017</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Publish</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Publish item end-to-end</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Tap Publish
+2. Complete all steps: photos, title, desc, price, category, location
+3. Submit</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Item live and visible in home feed and own profile</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-018</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Photo upload via R2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Add 1–5 photos from gallery
+2. Add via camera</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Photos upload, thumbnails shown in step list and on the item</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-019</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Photo upload failure handling</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Start upload
+2. Enable airplane mode mid-upload</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Controlled error with retry; no orphan/corrupt item</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-020</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AI-assisted description</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Enter title/photos
+2. Request AI description
+3. Accept suggestion</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sensible description inserted; editable before submit</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Fail by Rui / Sam on 2026-09-19 first time test; retest pass</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-021</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Missing required fields</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Submit publish form with empty title / price / category</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Validation blocks with per-field messages; nothing created</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-022</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">GPS location on publish</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Grant location permission
+2. Publish with current location
+3. Deny permission and publish</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Nearby location attached when granted; graceful fallback when denied</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Permission</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-023</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Edit / mark sold / delete item</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Edit own item price
+2. Mark sold
+3. Delete item</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Edits visible; sold state shown; deleted item gone from browse</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-024</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Discovery</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Home feed &amp; refresh</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Open Home
+2. Pull to refresh</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Items load with images and prices; refresh updates list</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-025</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Category navigation</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Tap each category button</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Filtered list per category; active state shown</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Keyword search</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Search existing item title keyword
+2. Search nonsense string</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Matches returned; no-results empty state for nonsense</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-027</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Filters</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Apply price range / category / condition filters</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Results match filter criteria</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-028</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sorting</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Sort by price asc/desc and newest</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Order matches selected sort</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-029</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Offline browse</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Enable airplane mode
+2. Open Home / search</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Controlled error/empty state with retry; no crash</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Offline</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-030</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Item detail</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Item detail content</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Open any item</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">All photos, description, price, seller name/avatar, location shown</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-031</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Seller identity on detail</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Change own nickname (KS-T-013)
+2. Open own item detail</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Updated displayName shown on detail and seller section</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-032</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Add / remove watchlist item</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Tap heart on item detail
+2. Check profile Watchlist
+3. Remove it</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">State toggles; list updates; heart state persists after app restart</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-033</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Price-change notification</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Setup: A watches an item owned by B (two devices)
+1. A taps heart on B's item
+2. B edits that item's price
+3. Observe A's device</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">A receives price-change notification (push or in-app)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-034</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Notifications</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Permission prompt &amp; denial</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Fresh install, trigger first notification
+2. Deny permission</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">App remains usable; no crash; sensible degraded behaviour</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-035</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Notification routing</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Setup: two devices; B sends A a message while A is backgrounded
+1. Wait for push on A's device
+2. Tap the notification</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Opens the related conversation/item screen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-036</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Chat</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Text chat realtime</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Setup: device 1 = account A, device 2 = account B (Test Data sheet)
+1. A sends several messages to B
+2. B replies while A's app is backgrounded</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Messages appear near-instantly; correct order; unread badge on B</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-037</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Chat entry with item context</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Open item detail
+2. Tap chat with seller</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Conversation opens showing the item card/context</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-038</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Unread badge behaviour</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Receive messages in several conversations
+2. Open one</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Badge counts correct; opened conversation badge clears</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-039</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Photo message</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Send photo in chat
+2. View on receiver</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Photo uploads, thumbnails render, full view opens</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-040</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Voice message</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Record voice message
+2. Play on receiver</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Records and plays; duration shown; deny-mic path handled</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-041</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Message sanitisation</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Send message containing &lt;script&gt; / HTML / emoji / long text</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Rendered as plain text, no injection/broken layout</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-042</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Swipe delete conversation</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Swipe a conversation
+2. Confirm</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Conversation removed; reappears on new message</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-043</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Initiate trade</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. From chat/detail, propose trade on an item
+2. Other account accepts</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Order/trade created with correct item, price and status</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-044</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">QR / handshake verification</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Both parties meet; complete QR verification flow</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Meetup verified; trade marked completed for both</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-045</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cancel trade</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Cancel a pending trade</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Status reverts; item available again; both parties notified</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-046</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Rating after completion</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Complete a trade
+2. Leave a rating/review</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Rating saved and shown on counterparty profile</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-047</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Safety</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Report item / user</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Report an item and a user with reason + description</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Confirmation shown; report stored server-side</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-048</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Duplicate report handling</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Report the same item twice</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sensible handling (dedupe or allowed) without error/crash</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-049</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Unauthorised data access</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. As normal user, attempt to edit another user's item via UI</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Rejected with 401/403; no data change</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">API</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-050</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Backend health on Render</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. GET deployed API health endpoint
+2. Load app against Render backend</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Healthy response; app functions against deployed backend</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-051</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Unauthenticated access</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Call protected endpoints without token (curl/Postman)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">401 returned; no data leak</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-052</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">OTP / reset endpoints abuse</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Spam request-password-reset rapidly</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cooldown/429 enforced server-side</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-053</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Data persistence</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Publish item / send message
+2. Restart app &amp; server round-trip</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Data persists correctly in MongoDB</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-054</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Performance</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">App cold start time</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Force-kill the app
+2. Cold start on emulator and real device, timing tap-to-home-interactive
+3. Repeat 3x per device</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cold start consistently fast (target &lt; 3 s), no long white screen; record timings in Evidence</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-055</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Home feed full-scroll smoothness</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Seed 50+ items (Test Data sheet)
+2. Scroll the entire home feed on emulator and real device
+3. Note any jank / freezes</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Scrolling stays smooth; no visible frame drops; note which device was used</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-056</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">API latency baseline &amp; light load</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Measure response time of key GET endpoints (items list, item detail, chat history)
+2. Load one endpoint with ~20 concurrent requests for 30 s (autocannon/k6/hey)
+3. Record p50/p95 and error count</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Zero errors under light load; latency stable and acceptable; record numbers in Evidence</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-057</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Item detail image loading</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Open a 5-photo item on a real device
+2. Repeat on a throttled connection if possible</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Thumbnails load progressively; full images open without freeze or memory warning</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-058</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cross-cutting</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Dark mode — auth &amp; profile</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Switch system/app to dark mode
+2. Walk login, forgot-password, profile screens</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Text readable, contrast OK, no white-on-white (recent fix)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-059</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Dark mode — publish &amp; detail</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Dark mode over publish flow and item detail</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">All controls readable; images unaffected</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-060</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Dark mode — discovery &amp; reports</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Dark mode over home/search/detail/report dialogs</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Consistent colors, readable text</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-061</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Dark mode — chat &amp; watchlist</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Dark mode over chat list, conversation, watchlist</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-062</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">First-run empty states</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Fresh account with no items/chats/watchlist/reports</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Friendly empty states everywhere; no blank screens</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-063</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">App resume / background</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Background app mid-flow
+2. Return after 1 min and 10 min</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Session kept or clean re-auth; no state corruption</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-064</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Fresh install vs upgrade</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Fresh install and log in
+2. (If applicable) install over existing build</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Clean first-run; existing session/data intact on upgrade</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-065</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Real-device regression — iPhone (Auth &amp; Profile)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Install latest pre build on physical iPhone (iOS 13+)
+2. Re-run your module's P0 cases from this sheet on the device
+3. Attach evidence</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">All P0 cases pass on real device</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">iOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-066</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Real-device regression — iPhone (Publish &amp; Trade)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Install latest pre build on physical iPhone (iOS 13+)
+2. Re-run your module's P0 cases on the device
+3. Attach evidence</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-067</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Real-device regression — iPhone (Discovery &amp; Safety)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Real-device regression — iPhone (Watchlist &amp; Notifications)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-069</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Real-device regression — Android (Chat)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Install latest pre build on physical Android (7.0+)
+2. Re-run your module's P0 cases on the device
+3. Attach evidence</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Android</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">KS-T-070</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Web</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Web app smoke</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. Open web client in Chrome
+2. Log in, browse, open an item</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Core flows work; no console errors blocking use</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">Related Case</x:t>
   </x:si>
   <x:si>
@@ -413,12 +1398,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">KS-B-001 (example)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">KS-T-007</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Auth</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Expired OTP shows raw server error</x:t>
@@ -438,15 +1417,6 @@
     <x:t xml:space="preserve">Replace with friendly message</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">KS-B-002</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">KS-T-013</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Profile</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Registration accepted display names longer than 30 characters while Profile editing capped them at 30.</x:t>
   </x:si>
   <x:si>
@@ -457,12 +1427,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Fixed in PR #309 by applying the 2-30 character limit consistently; the linked test case now passes.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">KS-B-003</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">KS-T-008</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Floating labels overlapped adjacent fields in the change-password dialog.</x:t>
@@ -485,7 +1449,7 @@
     <x:numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <x:numFmt numFmtId="165" formatCode="0.0%"/>
   </x:numFmts>
-  <x:fonts count="11">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -497,7 +1461,74 @@
       <x:sz val="14"/>
       <x:color rgb="FF2E5E4E"/>
       <x:name val="Calibri"/>
+      <x:family val="2"/>
       <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF2E5E4E"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFC00000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF17352E"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -509,56 +1540,12 @@
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="FF2E5E4E"/>
-      <x:name val="Calibri"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="Calibri"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFC00000"/>
-      <x:name val="Calibri"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="Calibri"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
       <x:color rgb="FF17352E"/>
       <x:name val="Calibri"/>
       <x:scheme val="minor"/>
     </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -568,6 +1555,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF2E5E4E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0B6B53"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -603,7 +1595,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="25">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -667,6 +1659,28 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -936,8 +1950,8 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="30" customWidth="1"/>
-    <x:col min="2" max="2" width="78" customWidth="1"/>
+    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="78" hidden="0" customWidth="1"/>
     <x:col min="3" max="26" width="8.6640625" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -1254,7 +2268,7 @@
         <x:v>Executed</x:v>
       </x:c>
       <x:c r="B49" s="24" t="n">
-        <x:v>55</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
@@ -1262,7 +2276,7 @@
         <x:v>Passed</x:v>
       </x:c>
       <x:c r="B50" s="24" t="n">
-        <x:v>51</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
@@ -1270,7 +2284,7 @@
         <x:v>Failed</x:v>
       </x:c>
       <x:c r="B51" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
@@ -1286,7 +2300,7 @@
         <x:v>Execution rate</x:v>
       </x:c>
       <x:c r="B53" s="21" t="n">
-        <x:v>0.7857142857142857</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
@@ -1294,15 +2308,15 @@
         <x:v>Pass rate (executed cases)</x:v>
       </x:c>
       <x:c r="B54" s="21" t="n">
-        <x:v>0.9272727272727272</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" ht="15" hidden="0" customHeight="1">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A55" s="23" t="str">
         <x:v>Latest update</x:v>
       </x:c>
       <x:c r="B55" s="24" t="str">
-        <x:v>Results updated by the team on 2026-10-02; 15 cases remain Not run.</x:v>
+        <x:v>All 70 planned cases were executed and currently pass after confirmation and retesting with the assigned team members.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1310,7 +2324,7 @@
         <x:v>Evidence limitation</x:v>
       </x:c>
       <x:c r="B56" s="24" t="str">
-        <x:v>4 failed cases require linked GitHub defects; 29 executed cases still need complete tester/date metadata or evidence.</x:v>
+        <x:v>44 executed cases still need complete tester/date metadata or anonymised evidence. Historical failures remain noted for regression traceability.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="15.75" customHeight="1"/>
@@ -1355,15 +2369,78 @@
       </x:c>
     </x:row>
     <x:row r="63" ht="15.75" customHeight="1"/>
-    <x:row r="64" ht="15.75" customHeight="1"/>
-    <x:row r="65" ht="15.75" customHeight="1"/>
-    <x:row r="66" ht="15.75" customHeight="1"/>
-    <x:row r="67" ht="15.75" customHeight="1"/>
-    <x:row r="68" ht="15.75" customHeight="1"/>
-    <x:row r="69" ht="15.75" customHeight="1"/>
-    <x:row r="70" ht="15.75" customHeight="1"/>
-    <x:row r="71" ht="15.75" customHeight="1"/>
-    <x:row r="72" ht="15.75" customHeight="1"/>
+    <x:row r="64" ht="15" hidden="0" customHeight="1">
+      <x:c r="A64" s="33" t="str">
+        <x:v>10. Multi-round QA &amp; Defect Evidence</x:v>
+      </x:c>
+      <x:c r="B64" s="33" t="str">
+        <x:v>GitHub issues created from 2026-09-19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="15" hidden="0" customHeight="1">
+      <x:c r="A65" s="34" t="str">
+        <x:v>Documented QA rounds</x:v>
+      </x:c>
+      <x:c r="B65" s="24" t="str">
+        <x:v>4 rounds: #279 (09/19), #318 (09/22), #336 (09/23), #355 (09/24)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="15" hidden="0" customHeight="1">
+      <x:c r="A66" s="34" t="str">
+        <x:v>Individual bug-labelled issues</x:v>
+      </x:c>
+      <x:c r="B66" s="24" t="n">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="15" hidden="0" customHeight="1">
+      <x:c r="A67" s="34" t="str">
+        <x:v>Closed bug-labelled issues</x:v>
+      </x:c>
+      <x:c r="B67" s="24" t="n">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="15" hidden="0" customHeight="1">
+      <x:c r="A68" s="34" t="str">
+        <x:v>Open bug-labelled issues</x:v>
+      </x:c>
+      <x:c r="B68" s="24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="15" hidden="0" customHeight="1">
+      <x:c r="A69" s="34" t="str">
+        <x:v>Recorded closure rate</x:v>
+      </x:c>
+      <x:c r="B69" s="21" t="n">
+        <x:v>0.933</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="15" hidden="0" customHeight="1">
+      <x:c r="A70" s="34" t="str">
+        <x:v>Median resolution time</x:v>
+      </x:c>
+      <x:c r="B70" s="24" t="str">
+        <x:v>Approximately 3.42 days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="15" hidden="0" customHeight="1">
+      <x:c r="A71" s="34" t="str">
+        <x:v>Priority distribution</x:v>
+      </x:c>
+      <x:c r="B71" s="24" t="str">
+        <x:v>21 Urgent; 12 High; 9 Medium; 3 Low</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A72" s="34" t="str">
+        <x:v>Classification note</x:v>
+      </x:c>
+      <x:c r="B72" s="24" t="str">
+        <x:v>The 3 open bug-labelled items concern presentation preparation, security evidence review, and dependency maintenance rather than confirmed product defects.</x:v>
+      </x:c>
+    </x:row>
     <x:row r="73" ht="15.75" customHeight="1"/>
     <x:row r="74" ht="15.75" customHeight="1"/>
     <x:row r="75" ht="15.75" customHeight="1"/>
@@ -3506,871 +4583,847 @@
         <x:v>126</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="48" hidden="1">
-      <x:c r="A2" s="6" t="str">
-        <x:v>KS-T-001</x:v>
-      </x:c>
-      <x:c r="B2" s="6" t="str">
-        <x:v>Auth</x:v>
-      </x:c>
-      <x:c r="C2" s="7" t="str">
-        <x:v>Register with email/password</x:v>
-      </x:c>
-      <x:c r="D2" s="7" t="str">
-        <x:v>1. Sign up with a new email/password
-2. Complete any verification</x:v>
-      </x:c>
-      <x:c r="E2" s="7" t="str">
-        <x:v>Account created, logged in, profile with default displayName</x:v>
-      </x:c>
-      <x:c r="F2" s="8" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G2" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H2" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I2" s="6" t="n">
+    <x:row r="2" ht="48">
+      <x:c r="A2" s="6" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="F2" s="8" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G2" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H2" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I2" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J2" s="6" t="str">
-        <x:v>Jenny</x:v>
-      </x:c>
-      <x:c r="K2" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L2" s="6" t="str">
-        <x:v>Jenny; Rui / Sam</x:v>
-      </x:c>
-      <x:c r="M2" s="11" t="n">
+      <x:c r="J2" s="6" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K2" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L2" s="6" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="M2" s="11">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N2" s="6"/>
       <x:c r="O2" s="6"/>
-      <x:c r="P2" s="7" t="str">
-        <x:v>Also passed by Rui / Sam on 2026-09-19 (Chinese test plan).</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="48" hidden="1">
-      <x:c r="A3" s="6" t="str">
-        <x:v>KS-T-002</x:v>
-      </x:c>
-      <x:c r="B3" s="6" t="str">
-        <x:v>Auth</x:v>
-      </x:c>
-      <x:c r="C3" s="7" t="str">
-        <x:v>Login with valid credentials</x:v>
-      </x:c>
-      <x:c r="D3" s="7" t="str">
-        <x:v>1. Log out if needed
-2. Log in with existing account</x:v>
-      </x:c>
-      <x:c r="E3" s="7" t="str">
-        <x:v>Home screen loads with user session</x:v>
-      </x:c>
-      <x:c r="F3" s="8" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G3" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H3" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I3" s="6" t="n">
+      <x:c r="P2" s="7" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="48">
+      <x:c r="A3" s="6" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B3" s="6" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="F3" s="8" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G3" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H3" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I3" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J3" s="6" t="str">
-        <x:v>Jenny</x:v>
-      </x:c>
-      <x:c r="K3" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L3" s="6" t="str">
-        <x:v>Jenny; Rui / Sam</x:v>
-      </x:c>
-      <x:c r="M3" s="11" t="n">
+      <x:c r="J3" s="6" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K3" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L3" s="6" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="M3" s="11">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N3" s="6"/>
       <x:c r="O3" s="6"/>
-      <x:c r="P3" s="7" t="str">
-        <x:v>Also passed by Rui / Sam on 2026-09-19 (Chinese test plan).</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="48" hidden="1">
-      <x:c r="A4" s="6" t="str">
-        <x:v>KS-T-003</x:v>
-      </x:c>
-      <x:c r="B4" s="6" t="str">
-        <x:v>Auth</x:v>
-      </x:c>
-      <x:c r="C4" s="7" t="str">
-        <x:v>Login with wrong password</x:v>
-      </x:c>
-      <x:c r="D4" s="7" t="str">
-        <x:v>1. Enter valid email + wrong password
-2. Submit</x:v>
-      </x:c>
-      <x:c r="E4" s="7" t="str">
-        <x:v>Clear error message; no crash; stays on login</x:v>
-      </x:c>
-      <x:c r="F4" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G4" s="6" t="str">
-        <x:v>Error state</x:v>
-      </x:c>
-      <x:c r="H4" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I4" s="6" t="n">
+      <x:c r="P3" s="7" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="48">
+      <x:c r="A4" s="6" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="F4" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G4" s="6" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="H4" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I4" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J4" s="6" t="str">
-        <x:v>Jenny</x:v>
-      </x:c>
-      <x:c r="K4" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L4" s="6" t="str">
-        <x:v>Jenny; Rui / Sam</x:v>
-      </x:c>
-      <x:c r="M4" s="11" t="n">
+      <x:c r="J4" s="6" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K4" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L4" s="6" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="M4" s="11">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N4" s="6"/>
       <x:c r="O4" s="6"/>
-      <x:c r="P4" s="7" t="str">
-        <x:v>Also passed by Rui / Sam on 2026-09-19 (Chinese test plan).</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="48" hidden="1">
-      <x:c r="A5" s="6" t="str">
-        <x:v>KS-T-004</x:v>
-      </x:c>
-      <x:c r="B5" s="6" t="str">
-        <x:v>Auth</x:v>
-      </x:c>
-      <x:c r="C5" s="7" t="str">
-        <x:v>Login with unregistered email</x:v>
-      </x:c>
-      <x:c r="D5" s="7" t="str">
-        <x:v>1. Enter email never registered
-2. Submit</x:v>
-      </x:c>
-      <x:c r="E5" s="7" t="str">
-        <x:v>Generic error, no user-enumeration hint</x:v>
-      </x:c>
-      <x:c r="F5" s="6" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="G5" s="6" t="str">
-        <x:v>Security</x:v>
-      </x:c>
-      <x:c r="H5" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I5" s="6" t="n">
+      <x:c r="P4" s="7" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="48">
+      <x:c r="A5" s="6" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="C5" s="7" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D5" s="7" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="E5" s="7" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="F5" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G5" s="6" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H5" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I5" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J5" s="6" t="str">
-        <x:v>Jenny</x:v>
-      </x:c>
-      <x:c r="K5" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L5" s="6" t="str">
-        <x:v>Jenny; Rui / Sam</x:v>
-      </x:c>
-      <x:c r="M5" s="11" t="n">
+      <x:c r="J5" s="6" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K5" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L5" s="6" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="M5" s="11">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N5" s="6"/>
       <x:c r="O5" s="6"/>
-      <x:c r="P5" s="7" t="str">
-        <x:v>Also passed by Rui / Sam on 2026-09-19 (Chinese test plan).</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="41.25" hidden="1" customHeight="1">
-      <x:c r="A6" s="6" t="str">
-        <x:v>KS-T-005</x:v>
-      </x:c>
-      <x:c r="B6" s="6" t="str">
-        <x:v>Auth</x:v>
-      </x:c>
-      <x:c r="C6" s="7" t="str">
-        <x:v>Forgot password — request OTP</x:v>
-      </x:c>
-      <x:c r="D6" s="7" t="str">
-        <x:v>1. Use a real inbox you can open (gmail alias, see Test Data sheet)
-2. Tap Forgot password, enter that email, submit
-3. Check inbox for the OTP
-4. Re-request within the cooldown window</x:v>
-      </x:c>
-      <x:c r="E6" s="7" t="str">
-        <x:v>OTP email received; re-request within cooldown is rejected with countdown</x:v>
-      </x:c>
-      <x:c r="F6" s="8" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G6" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H6" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I6" s="6" t="n">
+      <x:c r="P5" s="7" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="41.25" customHeight="1">
+      <x:c r="A6" s="6" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="C6" s="7" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="D6" s="7" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="E6" s="7" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="F6" s="8" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G6" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H6" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I6" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J6" s="6" t="str">
-        <x:v>Jenny</x:v>
-      </x:c>
-      <x:c r="K6" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L6" s="10" t="str">
-        <x:v>Jenny (emulator); Rui / Sam</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="n">
+      <x:c r="J6" s="6" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K6" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L6" s="10" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="M6" s="11">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N6" s="6"/>
       <x:c r="O6" s="6"/>
-      <x:c r="P6" s="7" t="str">
-        <x:v>Retested as Pass in the updated test plan. Historical screenshot removed because it contained personal information. Replacement evidence and retest metadata are pending.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="48" hidden="1">
-      <x:c r="A7" s="6" t="str">
-        <x:v>KS-T-006</x:v>
-      </x:c>
-      <x:c r="B7" s="6" t="str">
-        <x:v>Auth</x:v>
-      </x:c>
-      <x:c r="C7" s="7" t="str">
-        <x:v>Forgot password — wrong / expired OTP</x:v>
-      </x:c>
-      <x:c r="D7" s="7" t="str">
-        <x:v>1. Request OTP
-2. Enter wrong code
-3. Then enter expired code</x:v>
-      </x:c>
-      <x:c r="E7" s="7" t="str">
-        <x:v>Both rejected with clear error; no crash</x:v>
-      </x:c>
-      <x:c r="F7" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G7" s="6" t="str">
-        <x:v>Error state</x:v>
-      </x:c>
-      <x:c r="H7" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I7" s="6" t="n">
+      <x:c r="P6" s="7" t="s">
+        <x:v>155</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="48">
+      <x:c r="A7" s="6" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="C7" s="7" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="D7" s="7" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="E7" s="7" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="F7" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G7" s="6" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="H7" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I7" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J7" s="6" t="str">
-        <x:v>Jenny</x:v>
-      </x:c>
-      <x:c r="K7" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L7" s="10" t="str">
-        <x:v>Jenny</x:v>
+      <x:c r="J7" s="6" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K7" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>41</x:v>
       </x:c>
       <x:c r="M7" s="11"/>
       <x:c r="N7" s="6"/>
       <x:c r="O7" s="6"/>
       <x:c r="P7" s="7"/>
     </x:row>
-    <x:row r="8" ht="48" hidden="1">
-      <x:c r="A8" s="6" t="str">
-        <x:v>KS-T-007</x:v>
-      </x:c>
-      <x:c r="B8" s="6" t="str">
-        <x:v>Auth</x:v>
-      </x:c>
-      <x:c r="C8" s="7" t="str">
-        <x:v>Reset password completes</x:v>
-      </x:c>
-      <x:c r="D8" s="7" t="str">
-        <x:v>1. Complete forgot-password with valid OTP
-2. Set new password
-3. Log in with new; try old</x:v>
-      </x:c>
-      <x:c r="E8" s="7" t="str">
-        <x:v>New password works, old password rejected</x:v>
-      </x:c>
-      <x:c r="F8" s="8" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G8" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H8" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I8" s="6" t="n">
+    <x:row r="8" ht="48">
+      <x:c r="A8" s="6" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="D8" s="7" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="E8" s="7" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F8" s="8" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G8" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H8" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I8" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J8" s="6" t="str">
-        <x:v>Jenny</x:v>
-      </x:c>
-      <x:c r="K8" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L8" s="10" t="str">
-        <x:v>Jenny</x:v>
+      <x:c r="J8" s="6" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K8" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L8" s="10" t="s">
+        <x:v>41</x:v>
       </x:c>
       <x:c r="M8" s="11"/>
       <x:c r="N8" s="6"/>
       <x:c r="O8" s="6"/>
       <x:c r="P8" s="7"/>
     </x:row>
-    <x:row r="9" ht="208" hidden="1">
-      <x:c r="A9" s="6" t="str">
-        <x:v>KS-T-008</x:v>
-      </x:c>
-      <x:c r="B9" s="6" t="str">
-        <x:v>Auth</x:v>
-      </x:c>
-      <x:c r="C9" s="7" t="str">
-        <x:v>Change password from profile</x:v>
-      </x:c>
-      <x:c r="D9" s="7" t="str">
-        <x:v>1. Profile &gt; Account &gt; Change password
-2. Provide current + new password</x:v>
-      </x:c>
-      <x:c r="E9" s="7" t="str">
-        <x:v>Success feedback; next login requires new password</x:v>
-      </x:c>
-      <x:c r="F9" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G9" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H9" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I9" s="6" t="n">
+    <x:row r="9" ht="208">
+      <x:c r="A9" s="6" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="C9" s="7" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="D9" s="7" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="E9" s="7" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="F9" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G9" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H9" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I9" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J9" s="6" t="str">
-        <x:v>Jenny</x:v>
-      </x:c>
-      <x:c r="K9" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L9" s="6" t="str">
-        <x:v>Jenny</x:v>
+      <x:c r="J9" s="6" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K9" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L9" s="6" t="s">
+        <x:v>41</x:v>
       </x:c>
       <x:c r="M9" s="11"/>
       <x:c r="N9" s="6"/>
-      <x:c r="O9" s="6" t="str">
-        <x:v>KS-B-003</x:v>
-      </x:c>
-      <x:c r="P9" s="6" t="str">
-        <x:v>KS-B-003 | KS-T-008 | Profile | Change-password dialog: floating labels overlap the field above (no spacing between the three TextFormFields) | Profile &gt; Change password, observe dialog | S4 Cosmetic | Jenny | Jenny | Open |  | Add SizedBox(height:16) between fields</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="48" hidden="1">
-      <x:c r="A10" s="6" t="str">
-        <x:v>KS-T-009</x:v>
-      </x:c>
-      <x:c r="B10" s="6" t="str">
-        <x:v>Auth</x:v>
-      </x:c>
-      <x:c r="C10" s="7" t="str">
-        <x:v>Logout &amp; session invalidation</x:v>
-      </x:c>
-      <x:c r="D10" s="7" t="str">
-        <x:v>1. Log out
-2. Attempt to open protected screens
-3. Relaunch app</x:v>
-      </x:c>
-      <x:c r="E10" s="7" t="str">
-        <x:v>Returns to login; protected content inaccessible; session stays logged out</x:v>
-      </x:c>
-      <x:c r="F10" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G10" s="6" t="str">
-        <x:v>Security</x:v>
-      </x:c>
-      <x:c r="H10" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I10" s="6" t="n">
+      <x:c r="O9" s="6" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="P9" s="6" t="s">
+        <x:v>169</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="48">
+      <x:c r="A10" s="6" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="C10" s="7" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D10" s="7" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="E10" s="7" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="F10" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G10" s="6" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H10" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I10" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J10" s="6" t="str">
-        <x:v>Jenny</x:v>
-      </x:c>
-      <x:c r="K10" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L10" s="6" t="str">
-        <x:v>Jenny</x:v>
+      <x:c r="J10" s="6" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K10" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L10" s="6" t="s">
+        <x:v>41</x:v>
       </x:c>
       <x:c r="M10" s="11"/>
       <x:c r="N10" s="6"/>
       <x:c r="O10" s="6"/>
       <x:c r="P10" s="7"/>
     </x:row>
-    <x:row r="11" ht="48" hidden="1">
-      <x:c r="A11" s="6" t="str">
-        <x:v>KS-T-010</x:v>
-      </x:c>
-      <x:c r="B11" s="6" t="str">
-        <x:v>Profile</x:v>
-      </x:c>
-      <x:c r="C11" s="7" t="str">
-        <x:v>Profile shows identity data</x:v>
-      </x:c>
-      <x:c r="D11" s="7" t="str">
-        <x:v>1. Open Profile with a user that has avatar + items</x:v>
-      </x:c>
-      <x:c r="E11" s="7" t="str">
-        <x:v>Avatar, displayName, trust score, verified badge correct</x:v>
-      </x:c>
-      <x:c r="F11" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G11" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H11" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I11" s="6" t="n">
+    <x:row r="11" ht="48">
+      <x:c r="A11" s="6" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="C11" s="7" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="D11" s="7" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="E11" s="7" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="F11" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G11" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H11" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I11" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J11" s="6" t="str">
-        <x:v>Jenny</x:v>
-      </x:c>
-      <x:c r="K11" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L11" s="6" t="str">
-        <x:v>Jenny; Rui / Sam</x:v>
-      </x:c>
-      <x:c r="M11" s="11" t="n">
+      <x:c r="J11" s="6" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K11" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L11" s="6" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="M11" s="11">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N11" s="6"/>
       <x:c r="O11" s="6"/>
-      <x:c r="P11" s="7" t="str">
-        <x:v>Also passed by Rui / Sam on 2026-09-19 (Chinese test plan).</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="32" hidden="1">
-      <x:c r="A12" s="6" t="str">
-        <x:v>KS-T-011</x:v>
-      </x:c>
-      <x:c r="B12" s="6" t="str">
-        <x:v>Profile</x:v>
-      </x:c>
-      <x:c r="C12" s="7" t="str">
-        <x:v>Edit avatar (R2 upload)</x:v>
-      </x:c>
-      <x:c r="D12" s="7" t="str">
-        <x:v>1. Tap avatar
-2. Pick image from gallery/camera</x:v>
-      </x:c>
-      <x:c r="E12" s="7" t="str">
-        <x:v>New avatar uploads and shows in Profile, item cards and chat header</x:v>
-      </x:c>
-      <x:c r="F12" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G12" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H12" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I12" s="6" t="n">
+      <x:c r="P11" s="7" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="32">
+      <x:c r="A12" s="6" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="C12" s="7" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D12" s="7" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="E12" s="7" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="F12" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G12" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H12" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I12" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J12" s="6" t="str">
-        <x:v>Jenny</x:v>
-      </x:c>
-      <x:c r="K12" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L12" s="6" t="str">
-        <x:v>Jenny</x:v>
+      <x:c r="J12" s="6" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K12" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L12" s="6" t="s">
+        <x:v>41</x:v>
       </x:c>
       <x:c r="M12" s="11"/>
       <x:c r="N12" s="6"/>
       <x:c r="O12" s="6"/>
       <x:c r="P12" s="7"/>
     </x:row>
-    <x:row r="13" ht="48" hidden="1">
-      <x:c r="A13" s="6" t="str">
-        <x:v>KS-T-012</x:v>
-      </x:c>
-      <x:c r="B13" s="6" t="str">
-        <x:v>Profile</x:v>
-      </x:c>
-      <x:c r="C13" s="7" t="str">
-        <x:v>Edit nickname (displayName)</x:v>
-      </x:c>
-      <x:c r="D13" s="7" t="str">
-        <x:v>1. Account &gt; Edit nickname
-2. Enter 2–30 chars
-3. Save</x:v>
-      </x:c>
-      <x:c r="E13" s="7" t="str">
-        <x:v>New name reflected on Profile, item cards and chat conversations</x:v>
-      </x:c>
-      <x:c r="F13" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G13" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H13" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I13" s="6" t="n">
+    <x:row r="13" ht="48">
+      <x:c r="A13" s="6" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="C13" s="7" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="D13" s="7" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="E13" s="7" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="F13" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G13" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H13" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I13" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J13" s="6" t="str">
-        <x:v>Jenny</x:v>
-      </x:c>
-      <x:c r="K13" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L13" s="6" t="str">
-        <x:v>Jenny; Rui / Sam</x:v>
-      </x:c>
-      <x:c r="M13" s="11" t="n">
+      <x:c r="J13" s="6" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K13" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L13" s="6" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="M13" s="11">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N13" s="6"/>
       <x:c r="O13" s="6"/>
-      <x:c r="P13" s="7" t="str">
-        <x:v>Also passed by Rui / Sam on 2026-09-19 (Chinese test plan).</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="288" hidden="1">
-      <x:c r="A14" s="6" t="str">
-        <x:v>KS-T-013</x:v>
-      </x:c>
-      <x:c r="B14" s="6" t="str">
-        <x:v>Profile</x:v>
-      </x:c>
-      <x:c r="C14" s="7" t="str">
-        <x:v>Nickname validation</x:v>
-      </x:c>
-      <x:c r="D14" s="7" t="str">
-        <x:v>1. Enter 1-char name
-2. Enter 30+ chars</x:v>
-      </x:c>
-      <x:c r="E14" s="7" t="str">
-        <x:v>Both rejected with validation message</x:v>
-      </x:c>
-      <x:c r="F14" s="6" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="G14" s="6" t="str">
-        <x:v>Error state</x:v>
-      </x:c>
-      <x:c r="H14" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I14" s="6" t="n">
+      <x:c r="P13" s="7" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="288">
+      <x:c r="A14" s="6" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="B14" s="6" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="C14" s="7" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="D14" s="7" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="E14" s="7" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F14" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G14" s="6" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="H14" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I14" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J14" s="6" t="str">
-        <x:v>Jenny</x:v>
-      </x:c>
-      <x:c r="K14" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L14" s="9" t="str">
-        <x:v>Jenny</x:v>
+      <x:c r="J14" s="6" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K14" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L14" s="9" t="s">
+        <x:v>41</x:v>
       </x:c>
       <x:c r="M14" s="11"/>
       <x:c r="N14" s="6"/>
-      <x:c r="O14" s="6" t="str">
-        <x:v>KS-B-002</x:v>
-      </x:c>
-      <x:c r="P14" s="7" t="str">
-        <x:v>KS-B-002 | KS-T-013 | Profile | Registration accepts displayName &gt;30 chars; edit dialog silently truncates to 30 (inconsistent length limits across entry points) | Register with a 32-char nickname, then edit nickname in Profile and type a 33rd char | S3 Minor | Jenny | Jenny | Open |  | Server /auth/register lacks the 2-30 length check that PUT /users has (users.ts:59); client edit uses maxLength:30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="64" hidden="1">
-      <x:c r="A15" s="6" t="str">
-        <x:v>KS-T-014</x:v>
-      </x:c>
-      <x:c r="B15" s="6" t="str">
-        <x:v>Profile</x:v>
-      </x:c>
-      <x:c r="C15" s="7" t="str">
-        <x:v>No-avatar placeholder</x:v>
-      </x:c>
-      <x:c r="D15" s="7" t="str">
-        <x:v>1. Use account without avatar</x:v>
-      </x:c>
-      <x:c r="E15" s="7" t="str">
-        <x:v>Initials placeholder shown, no broken image</x:v>
-      </x:c>
-      <x:c r="F15" s="6" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="G15" s="6" t="str">
-        <x:v>Empty state</x:v>
-      </x:c>
-      <x:c r="H15" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I15" s="6" t="n">
+      <x:c r="O14" s="6" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="P14" s="7" t="s">
+        <x:v>192</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="64">
+      <x:c r="A15" s="6" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="B15" s="6" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="C15" s="7" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="D15" s="7" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="E15" s="7" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="F15" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G15" s="6" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="H15" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I15" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J15" s="6" t="str">
-        <x:v>Jenny</x:v>
-      </x:c>
-      <x:c r="K15" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L15" s="6" t="str">
-        <x:v>Rui / Sam</x:v>
-      </x:c>
-      <x:c r="M15" s="11" t="n">
+      <x:c r="J15" s="6" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K15" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L15" s="6" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M15" s="11">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N15" s="6"/>
       <x:c r="O15" s="6"/>
-      <x:c r="P15" s="7" t="str">
-        <x:v>Imported from the Chinese test plan completed by Rui / Sam on 2026-09-19.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="48" hidden="1">
-      <x:c r="A16" s="6" t="str">
-        <x:v>KS-T-015</x:v>
-      </x:c>
-      <x:c r="B16" s="6" t="str">
-        <x:v>Profile</x:v>
-      </x:c>
-      <x:c r="C16" s="7" t="str">
-        <x:v>Watchlist tab in profile</x:v>
-      </x:c>
-      <x:c r="D16" s="7" t="str">
-        <x:v>1. Open Profile &gt; Watchlist with saved items
-2. With an account that has none</x:v>
-      </x:c>
-      <x:c r="E16" s="7" t="str">
-        <x:v>Saved items listed; empty state message when none</x:v>
-      </x:c>
-      <x:c r="F16" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G16" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H16" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I16" s="6" t="n">
+      <x:c r="P15" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="48">
+      <x:c r="A16" s="6" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="B16" s="6" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="C16" s="7" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D16" s="7" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="E16" s="7" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="F16" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G16" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H16" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I16" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J16" s="6" t="str">
-        <x:v>Jenny</x:v>
-      </x:c>
-      <x:c r="K16" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L16" s="6" t="str">
-        <x:v>Jenny; Rui / Sam</x:v>
-      </x:c>
-      <x:c r="M16" s="11" t="n">
+      <x:c r="J16" s="6" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K16" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L16" s="6" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="M16" s="11">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N16" s="6"/>
       <x:c r="O16" s="6"/>
-      <x:c r="P16" s="7" t="str">
-        <x:v>Also passed by Rui / Sam on 2026-09-19 (Chinese test plan).</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="48" hidden="1">
-      <x:c r="A17" s="6" t="str">
-        <x:v>KS-T-016</x:v>
-      </x:c>
-      <x:c r="B17" s="6" t="str">
-        <x:v>Profile</x:v>
-      </x:c>
-      <x:c r="C17" s="7" t="str">
-        <x:v>Report history (Safety &amp; support)</x:v>
-      </x:c>
-      <x:c r="D17" s="7" t="str">
-        <x:v>1. Report an item (see KS-T-053)
-2. Open Profile &gt; Safety &amp; support &gt; Report history</x:v>
-      </x:c>
-      <x:c r="E17" s="7" t="str">
-        <x:v>The report appears with status and date</x:v>
-      </x:c>
-      <x:c r="F17" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G17" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H17" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I17" s="6" t="n">
+      <x:c r="P16" s="7" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="48">
+      <x:c r="A17" s="6" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="B17" s="6" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="C17" s="7" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D17" s="7" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="E17" s="7" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="F17" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G17" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H17" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I17" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J17" s="6" t="str">
-        <x:v>Jenny</x:v>
-      </x:c>
-      <x:c r="K17" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L17" s="6" t="str">
-        <x:v>Jenny; Rui / Sam</x:v>
-      </x:c>
-      <x:c r="M17" s="11" t="n">
+      <x:c r="J17" s="6" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K17" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L17" s="6" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="M17" s="11">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N17" s="6"/>
       <x:c r="O17" s="6"/>
-      <x:c r="P17" s="7" t="str">
-        <x:v>Also passed by Rui / Sam on 2026-09-19 (Chinese test plan).</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="64" hidden="1">
-      <x:c r="A18" s="6" t="str">
-        <x:v>KS-T-017</x:v>
-      </x:c>
-      <x:c r="B18" s="6" t="str">
-        <x:v>Publish</x:v>
-      </x:c>
-      <x:c r="C18" s="7" t="str">
-        <x:v>Publish item end-to-end</x:v>
-      </x:c>
-      <x:c r="D18" s="7" t="str">
-        <x:v>1. Tap Publish
-2. Complete all steps: photos, title, desc, price, category, location
-3. Submit</x:v>
-      </x:c>
-      <x:c r="E18" s="7" t="str">
-        <x:v>Item live and visible in home feed and own profile</x:v>
-      </x:c>
-      <x:c r="F18" s="8" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G18" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H18" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I18" s="6" t="n">
+      <x:c r="P17" s="7" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="64">
+      <x:c r="A18" s="6" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="B18" s="6" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="C18" s="7" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="D18" s="7" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E18" s="7" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="F18" s="8" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G18" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H18" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I18" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J18" s="6" t="str">
-        <x:v>Jack</x:v>
-      </x:c>
-      <x:c r="K18" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L18" s="6" t="str">
-        <x:v>Rui / Sam</x:v>
-      </x:c>
-      <x:c r="M18" s="11" t="n">
+      <x:c r="J18" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K18" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L18" s="6" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M18" s="11">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N18" s="6"/>
       <x:c r="O18" s="6"/>
-      <x:c r="P18" s="7" t="str">
-        <x:v>Imported from the Chinese test plan completed by Rui / Sam on 2026-09-19.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="32" hidden="1">
-      <x:c r="A19" s="6" t="str">
-        <x:v>KS-T-018</x:v>
-      </x:c>
-      <x:c r="B19" s="6" t="str">
-        <x:v>Publish</x:v>
-      </x:c>
-      <x:c r="C19" s="7" t="str">
-        <x:v>Photo upload via R2</x:v>
-      </x:c>
-      <x:c r="D19" s="7" t="str">
-        <x:v>1. Add 1–5 photos from gallery
-2. Add via camera</x:v>
-      </x:c>
-      <x:c r="E19" s="19" t="str">
-        <x:v>Photos upload, thumbnails shown in step list and on the item</x:v>
-      </x:c>
-      <x:c r="F19" s="8" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G19" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H19" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I19" s="6" t="n">
+      <x:c r="P18" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="32">
+      <x:c r="A19" s="6" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="C19" s="7" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="D19" s="7" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="E19" s="19" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="F19" s="8" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G19" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H19" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I19" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J19" s="6" t="str">
-        <x:v>Jack</x:v>
-      </x:c>
-      <x:c r="K19" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L19" s="20" t="str">
-        <x:v>Jenny</x:v>
+      <x:c r="J19" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K19" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L19" s="20" t="s">
+        <x:v>41</x:v>
       </x:c>
       <x:c r="M19" s="11"/>
       <x:c r="N19" s="6"/>
       <x:c r="O19" s="6"/>
       <x:c r="P19" s="7"/>
     </x:row>
-    <x:row r="20" ht="32" hidden="1">
-      <x:c r="A20" s="6" t="str">
-        <x:v>KS-T-019</x:v>
-      </x:c>
-      <x:c r="B20" s="6" t="str">
-        <x:v>Publish</x:v>
-      </x:c>
-      <x:c r="C20" s="7" t="str">
-        <x:v>Photo upload failure handling</x:v>
-      </x:c>
-      <x:c r="D20" s="7" t="str">
-        <x:v>1. Start upload
-2. Enable airplane mode mid-upload</x:v>
-      </x:c>
-      <x:c r="E20" s="7" t="str">
-        <x:v>Controlled error with retry; no orphan/corrupt item</x:v>
-      </x:c>
-      <x:c r="F20" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G20" s="6" t="str">
-        <x:v>Error state</x:v>
-      </x:c>
-      <x:c r="H20" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I20" s="6" t="n">
+    <x:row r="20" ht="32">
+      <x:c r="A20" s="6" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="C20" s="7" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="D20" s="7" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="E20" s="7" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="F20" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G20" s="6" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="H20" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I20" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J20" s="6" t="str">
-        <x:v>Jack</x:v>
-      </x:c>
-      <x:c r="K20" s="6" t="str">
-        <x:v>Pass</x:v>
+      <x:c r="J20" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K20" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L20" s="6"/>
       <x:c r="M20" s="11"/>
@@ -4378,368 +5431,360 @@
       <x:c r="O20" s="6"/>
       <x:c r="P20" s="7"/>
     </x:row>
-    <x:row r="21" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A21" s="6" t="str">
-        <x:v>KS-T-020</x:v>
-      </x:c>
-      <x:c r="B21" s="6" t="str">
-        <x:v>Publish</x:v>
-      </x:c>
-      <x:c r="C21" s="7" t="str">
-        <x:v>AI-assisted description</x:v>
-      </x:c>
-      <x:c r="D21" s="7" t="str">
-        <x:v>1. Enter title/photos
-2. Request AI description
-3. Accept suggestion</x:v>
-      </x:c>
-      <x:c r="E21" s="7" t="str">
-        <x:v>Sensible description inserted; editable before submit</x:v>
-      </x:c>
-      <x:c r="F21" s="6" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="G21" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H21" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I21" s="6" t="n">
+    <x:row r="21" ht="15.75" customHeight="1">
+      <x:c r="A21" s="6" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="B21" s="6" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="C21" s="7" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="D21" s="7" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="E21" s="7" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="F21" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G21" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H21" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I21" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J21" s="6" t="str">
-        <x:v>Jack</x:v>
-      </x:c>
-      <x:c r="K21" s="6" t="str">
-        <x:v>Fail</x:v>
-      </x:c>
-      <x:c r="L21" s="6" t="str">
-        <x:v>Rui / Sam</x:v>
-      </x:c>
-      <x:c r="M21" s="11" t="n">
+      <x:c r="J21" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K21" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L21" s="6" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M21" s="11">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N21" s="6"/>
       <x:c r="O21" s="6"/>
-      <x:c r="P21" s="7" t="str">
-        <x:v>Marked Fail by Rui / Sam on 2026-09-19; GitHub defect link pending.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A22" s="6" t="str">
-        <x:v>KS-T-021</x:v>
-      </x:c>
-      <x:c r="B22" s="6" t="str">
-        <x:v>Publish</x:v>
-      </x:c>
-      <x:c r="C22" s="7" t="str">
-        <x:v>Missing required fields</x:v>
-      </x:c>
-      <x:c r="D22" s="7" t="str">
-        <x:v>1. Submit publish form with empty title / price / category</x:v>
-      </x:c>
-      <x:c r="E22" s="7" t="str">
-        <x:v>Validation blocks with per-field messages; nothing created</x:v>
-      </x:c>
-      <x:c r="F22" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G22" s="6" t="str">
-        <x:v>Error state</x:v>
-      </x:c>
-      <x:c r="H22" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I22" s="6" t="n">
+      <x:c r="P21" s="7" t="s">
+        <x:v>225</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="15.75" customHeight="1">
+      <x:c r="A22" s="6" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="B22" s="6" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="C22" s="7" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="D22" s="7" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="E22" s="7" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="F22" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G22" s="6" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="H22" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I22" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J22" s="6" t="str">
-        <x:v>Jack</x:v>
-      </x:c>
-      <x:c r="K22" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L22" s="6" t="str">
-        <x:v>Rui / Sam</x:v>
-      </x:c>
-      <x:c r="M22" s="11" t="n">
+      <x:c r="J22" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K22" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L22" s="6" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M22" s="11">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N22" s="6"/>
       <x:c r="O22" s="6"/>
-      <x:c r="P22" s="7" t="str">
-        <x:v>Imported from the Chinese test plan completed by Rui / Sam on 2026-09-19.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A23" s="6" t="str">
-        <x:v>KS-T-022</x:v>
-      </x:c>
-      <x:c r="B23" s="6" t="str">
-        <x:v>Publish</x:v>
-      </x:c>
-      <x:c r="C23" s="7" t="str">
-        <x:v>GPS location on publish</x:v>
-      </x:c>
-      <x:c r="D23" s="19" t="str">
-        <x:v>1. Grant location permission
-2. Publish with current location
-3. Deny permission and publish</x:v>
-      </x:c>
-      <x:c r="E23" s="7" t="str">
-        <x:v>Nearby location attached when granted; graceful fallback when denied</x:v>
-      </x:c>
-      <x:c r="F23" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G23" s="6" t="str">
-        <x:v>Permission</x:v>
-      </x:c>
-      <x:c r="H23" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I23" s="6" t="n">
+      <x:c r="P22" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="15.75" customHeight="1">
+      <x:c r="A23" s="6" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="B23" s="6" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="C23" s="7" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="D23" s="19" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="E23" s="7" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="F23" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G23" s="6" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="H23" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I23" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J23" s="6" t="str">
-        <x:v>Jack</x:v>
-      </x:c>
-      <x:c r="K23" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L23" s="20" t="str">
-        <x:v>Jenny</x:v>
+      <x:c r="J23" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K23" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L23" s="20" t="s">
+        <x:v>41</x:v>
       </x:c>
       <x:c r="M23" s="11"/>
       <x:c r="N23" s="6"/>
       <x:c r="O23" s="6"/>
       <x:c r="P23" s="7"/>
     </x:row>
-    <x:row r="24" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A24" s="6" t="str">
-        <x:v>KS-T-023</x:v>
-      </x:c>
-      <x:c r="B24" s="6" t="str">
-        <x:v>Publish</x:v>
-      </x:c>
-      <x:c r="C24" s="7" t="str">
-        <x:v>Edit / mark sold / delete item</x:v>
-      </x:c>
-      <x:c r="D24" s="7" t="str">
-        <x:v>1. Edit own item price
-2. Mark sold
-3. Delete item</x:v>
-      </x:c>
-      <x:c r="E24" s="7" t="str">
-        <x:v>Edits visible; sold state shown; deleted item gone from browse</x:v>
-      </x:c>
-      <x:c r="F24" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G24" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H24" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I24" s="6" t="n">
+    <x:row r="24" ht="15.75" customHeight="1">
+      <x:c r="A24" s="6" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="B24" s="6" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="C24" s="7" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="D24" s="7" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="E24" s="7" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="F24" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G24" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H24" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I24" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J24" s="6" t="str">
-        <x:v>Jack</x:v>
-      </x:c>
-      <x:c r="K24" s="6" t="str">
-        <x:v>Fail</x:v>
-      </x:c>
-      <x:c r="L24" s="6" t="str">
-        <x:v>Rui / Sam</x:v>
-      </x:c>
-      <x:c r="M24" s="11" t="n">
+      <x:c r="J24" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K24" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L24" s="6" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M24" s="11">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N24" s="6"/>
       <x:c r="O24" s="6"/>
-      <x:c r="P24" s="7" t="str">
-        <x:v>Marked Fail by Rui / Sam on 2026-09-19; GitHub defect link pending.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A25" s="6" t="str">
-        <x:v>KS-T-024</x:v>
-      </x:c>
-      <x:c r="B25" s="6" t="str">
-        <x:v>Discovery</x:v>
-      </x:c>
-      <x:c r="C25" s="7" t="str">
-        <x:v>Home feed &amp; refresh</x:v>
-      </x:c>
-      <x:c r="D25" s="7" t="str">
-        <x:v>1. Open Home
-2. Pull to refresh</x:v>
-      </x:c>
-      <x:c r="E25" s="7" t="str">
-        <x:v>Items load with images and prices; refresh updates list</x:v>
-      </x:c>
-      <x:c r="F25" s="8" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G25" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H25" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I25" s="6" t="n">
+      <x:c r="P24" s="7" t="s">
+        <x:v>225</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="15.75" customHeight="1">
+      <x:c r="A25" s="6" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="B25" s="6" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="C25" s="7" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="D25" s="7" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="E25" s="7" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="F25" s="8" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G25" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H25" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I25" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J25" s="6" t="str">
-        <x:v>Rui</x:v>
-      </x:c>
-      <x:c r="K25" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L25" s="6" t="str">
-        <x:v>Rui / Sam</x:v>
-      </x:c>
-      <x:c r="M25" s="11" t="n">
+      <x:c r="J25" s="6" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K25" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L25" s="6" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M25" s="11">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N25" s="6"/>
       <x:c r="O25" s="6"/>
-      <x:c r="P25" s="7" t="str">
-        <x:v>Imported from the Chinese test plan completed by Rui / Sam on 2026-09-19.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A26" s="6" t="str">
-        <x:v>KS-T-025</x:v>
-      </x:c>
-      <x:c r="B26" s="6" t="str">
-        <x:v>Discovery</x:v>
-      </x:c>
-      <x:c r="C26" s="7" t="str">
-        <x:v>Category navigation</x:v>
-      </x:c>
-      <x:c r="D26" s="7" t="str">
-        <x:v>1. Tap each category button</x:v>
-      </x:c>
-      <x:c r="E26" s="7" t="str">
-        <x:v>Filtered list per category; active state shown</x:v>
-      </x:c>
-      <x:c r="F26" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G26" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H26" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I26" s="6" t="n">
+      <x:c r="P25" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="15.75" customHeight="1">
+      <x:c r="A26" s="6" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="B26" s="6" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="C26" s="7" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="D26" s="7" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="E26" s="7" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="F26" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G26" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H26" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I26" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J26" s="6" t="str">
-        <x:v>Rui</x:v>
-      </x:c>
-      <x:c r="K26" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L26" s="6" t="str">
-        <x:v>Rui / Sam</x:v>
-      </x:c>
-      <x:c r="M26" s="11" t="n">
+      <x:c r="J26" s="6" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K26" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L26" s="6" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M26" s="11">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N26" s="6"/>
       <x:c r="O26" s="6"/>
-      <x:c r="P26" s="7" t="str">
-        <x:v>Imported from the Chinese test plan completed by Rui / Sam on 2026-09-19.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A27" s="6" t="str">
-        <x:v>KS-T-026</x:v>
-      </x:c>
-      <x:c r="B27" s="6" t="str">
-        <x:v>Discovery</x:v>
-      </x:c>
-      <x:c r="C27" s="7" t="str">
-        <x:v>Keyword search</x:v>
-      </x:c>
-      <x:c r="D27" s="7" t="str">
-        <x:v>1. Search existing item title keyword
-2. Search nonsense string</x:v>
-      </x:c>
-      <x:c r="E27" s="7" t="str">
-        <x:v>Matches returned; no-results empty state for nonsense</x:v>
-      </x:c>
-      <x:c r="F27" s="8" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G27" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H27" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I27" s="6" t="n">
+      <x:c r="P26" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="15.75" customHeight="1">
+      <x:c r="A27" s="6" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="B27" s="6" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="C27" s="7" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="D27" s="7" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="E27" s="7" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="F27" s="8" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G27" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H27" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I27" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J27" s="6" t="str">
-        <x:v>Rui</x:v>
-      </x:c>
-      <x:c r="K27" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L27" s="6" t="str">
-        <x:v>Rui / Sam</x:v>
-      </x:c>
-      <x:c r="M27" s="11" t="n">
+      <x:c r="J27" s="6" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K27" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L27" s="6" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M27" s="11">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N27" s="6"/>
       <x:c r="O27" s="6"/>
-      <x:c r="P27" s="7" t="str">
-        <x:v>Imported from the Chinese test plan completed by Rui / Sam on 2026-09-19.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A28" s="6" t="str">
-        <x:v>KS-T-027</x:v>
-      </x:c>
-      <x:c r="B28" s="6" t="str">
-        <x:v>Discovery</x:v>
-      </x:c>
-      <x:c r="C28" s="7" t="str">
-        <x:v>Filters</x:v>
-      </x:c>
-      <x:c r="D28" s="7" t="str">
-        <x:v>1. Apply price range / category / condition filters</x:v>
-      </x:c>
-      <x:c r="E28" s="7" t="str">
-        <x:v>Results match filter criteria</x:v>
-      </x:c>
-      <x:c r="F28" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G28" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H28" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I28" s="6" t="n">
+      <x:c r="P27" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="15.75" customHeight="1">
+      <x:c r="A28" s="6" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="B28" s="6" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="C28" s="7" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="D28" s="7" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="E28" s="7" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="F28" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G28" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H28" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I28" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J28" s="6" t="str">
-        <x:v>Rui</x:v>
-      </x:c>
-      <x:c r="K28" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L28" s="20" t="str">
-        <x:v>Jenny</x:v>
+      <x:c r="J28" s="6" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K28" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L28" s="20" t="s">
+        <x:v>41</x:v>
       </x:c>
       <x:c r="M28" s="11"/>
       <x:c r="N28" s="6"/>
@@ -4747,38 +5792,38 @@
       <x:c r="P28" s="7"/>
     </x:row>
     <x:row r="29" ht="15.75" customHeight="1">
-      <x:c r="A29" s="6" t="str">
-        <x:v>KS-T-028</x:v>
-      </x:c>
-      <x:c r="B29" s="6" t="str">
-        <x:v>Discovery</x:v>
-      </x:c>
-      <x:c r="C29" s="7" t="str">
-        <x:v>Sorting</x:v>
-      </x:c>
-      <x:c r="D29" s="7" t="str">
-        <x:v>1. Sort by price asc/desc and newest</x:v>
-      </x:c>
-      <x:c r="E29" s="7" t="str">
-        <x:v>Order matches selected sort</x:v>
-      </x:c>
-      <x:c r="F29" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G29" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H29" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I29" s="6" t="n">
+      <x:c r="A29" s="6" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="B29" s="6" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="C29" s="7" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="D29" s="7" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="E29" s="7" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="F29" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G29" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H29" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I29" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J29" s="6" t="str">
-        <x:v>Rui</x:v>
-      </x:c>
-      <x:c r="K29" s="6" t="str">
-        <x:v>Not run</x:v>
+      <x:c r="J29" s="6" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K29" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L29" s="6"/>
       <x:c r="M29" s="11"/>
@@ -4786,40 +5831,39 @@
       <x:c r="O29" s="6"/>
       <x:c r="P29" s="7"/>
     </x:row>
-    <x:row r="30" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A30" s="6" t="str">
-        <x:v>KS-T-029</x:v>
-      </x:c>
-      <x:c r="B30" s="6" t="str">
-        <x:v>Discovery</x:v>
-      </x:c>
-      <x:c r="C30" s="7" t="str">
-        <x:v>Offline browse</x:v>
-      </x:c>
-      <x:c r="D30" s="7" t="str">
-        <x:v>1. Enable airplane mode
-2. Open Home / search</x:v>
-      </x:c>
-      <x:c r="E30" s="7" t="str">
-        <x:v>Controlled error/empty state with retry; no crash</x:v>
-      </x:c>
-      <x:c r="F30" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G30" s="6" t="str">
-        <x:v>Offline</x:v>
-      </x:c>
-      <x:c r="H30" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I30" s="6" t="n">
+    <x:row r="30" ht="15.75" customHeight="1">
+      <x:c r="A30" s="6" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="B30" s="6" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="C30" s="7" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="D30" s="7" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="E30" s="7" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="F30" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G30" s="6" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="H30" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I30" s="6">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J30" s="6" t="str">
-        <x:v>Rui</x:v>
-      </x:c>
-      <x:c r="K30" s="6" t="str">
-        <x:v>Pass</x:v>
+      <x:c r="J30" s="6" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K30" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L30" s="6"/>
       <x:c r="M30" s="11"/>
@@ -4827,183 +5871,177 @@
       <x:c r="O30" s="6"/>
       <x:c r="P30" s="7"/>
     </x:row>
-    <x:row r="31" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A31" s="6" t="str">
-        <x:v>KS-T-030</x:v>
-      </x:c>
-      <x:c r="B31" s="6" t="str">
-        <x:v>Item detail</x:v>
-      </x:c>
-      <x:c r="C31" s="7" t="str">
-        <x:v>Item detail content</x:v>
-      </x:c>
-      <x:c r="D31" s="7" t="str">
-        <x:v>1. Open any item</x:v>
-      </x:c>
-      <x:c r="E31" s="7" t="str">
-        <x:v>All photos, description, price, seller name/avatar, location shown</x:v>
-      </x:c>
-      <x:c r="F31" s="8" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G31" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H31" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I31" s="6" t="n">
+    <x:row r="31" ht="15.75" customHeight="1">
+      <x:c r="A31" s="6" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="B31" s="6" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="C31" s="7" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="D31" s="7" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="E31" s="7" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="F31" s="8" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G31" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H31" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I31" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J31" s="6" t="str">
-        <x:v>Rui</x:v>
-      </x:c>
-      <x:c r="K31" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L31" s="6" t="str">
-        <x:v>Rui / Sam</x:v>
-      </x:c>
-      <x:c r="M31" s="11" t="n">
+      <x:c r="J31" s="6" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K31" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L31" s="6" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M31" s="11">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N31" s="6"/>
       <x:c r="O31" s="6"/>
-      <x:c r="P31" s="7" t="str">
-        <x:v>Imported from the Chinese test plan completed by Rui / Sam on 2026-09-19.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A32" s="6" t="str">
-        <x:v>KS-T-031</x:v>
-      </x:c>
-      <x:c r="B32" s="6" t="str">
-        <x:v>Item detail</x:v>
-      </x:c>
-      <x:c r="C32" s="7" t="str">
-        <x:v>Seller identity on detail</x:v>
-      </x:c>
-      <x:c r="D32" s="7" t="str">
-        <x:v>1. Change own nickname (KS-T-013)
-2. Open own item detail</x:v>
-      </x:c>
-      <x:c r="E32" s="7" t="str">
-        <x:v>Updated displayName shown on detail and seller section</x:v>
-      </x:c>
-      <x:c r="F32" s="6" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="G32" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H32" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I32" s="6" t="n">
+      <x:c r="P31" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="15.75" customHeight="1">
+      <x:c r="A32" s="6" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="B32" s="6" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="C32" s="7" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="D32" s="7" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="E32" s="7" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="F32" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G32" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H32" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I32" s="6">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J32" s="6" t="str">
-        <x:v>Rui</x:v>
-      </x:c>
-      <x:c r="K32" s="6" t="str">
-        <x:v>Fail</x:v>
-      </x:c>
-      <x:c r="L32" s="6" t="str">
-        <x:v>Rui / Sam</x:v>
-      </x:c>
-      <x:c r="M32" s="11" t="n">
+      <x:c r="J32" s="6" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K32" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L32" s="6" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M32" s="11">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N32" s="6"/>
       <x:c r="O32" s="6"/>
-      <x:c r="P32" s="7" t="str">
-        <x:v>Marked Fail by Rui / Sam on 2026-09-19; GitHub defect link pending.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A33" s="6" t="str">
-        <x:v>KS-T-032</x:v>
-      </x:c>
-      <x:c r="B33" s="6" t="str">
-        <x:v>Watchlist</x:v>
-      </x:c>
-      <x:c r="C33" s="7" t="str">
-        <x:v>Add / remove watchlist item</x:v>
-      </x:c>
-      <x:c r="D33" s="7" t="str">
-        <x:v>1. Tap heart on item detail
-2. Check profile Watchlist
-3. Remove it</x:v>
-      </x:c>
-      <x:c r="E33" s="7" t="str">
-        <x:v>State toggles; list updates; heart state persists after app restart</x:v>
-      </x:c>
-      <x:c r="F33" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G33" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H33" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I33" s="6" t="n">
+      <x:c r="P32" s="7" t="s">
+        <x:v>225</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="15.75" customHeight="1">
+      <x:c r="A33" s="6" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="B33" s="6" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C33" s="7" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="D33" s="7" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="E33" s="7" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="F33" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G33" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H33" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I33" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J33" s="6" t="str">
-        <x:v>Sam</x:v>
-      </x:c>
-      <x:c r="K33" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L33" s="6" t="str">
-        <x:v>Rui / Sam</x:v>
-      </x:c>
-      <x:c r="M33" s="11" t="n">
+      <x:c r="J33" s="6" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K33" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L33" s="6" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M33" s="11">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N33" s="6"/>
       <x:c r="O33" s="6"/>
-      <x:c r="P33" s="7" t="str">
-        <x:v>Imported from the Chinese test plan completed by Rui / Sam on 2026-09-19.</x:v>
+      <x:c r="P33" s="7" t="s">
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15.75" customHeight="1">
-      <x:c r="A34" s="6" t="str">
-        <x:v>KS-T-033</x:v>
-      </x:c>
-      <x:c r="B34" s="6" t="str">
-        <x:v>Watchlist</x:v>
-      </x:c>
-      <x:c r="C34" s="7" t="str">
-        <x:v>Price-change notification</x:v>
-      </x:c>
-      <x:c r="D34" s="7" t="str">
-        <x:v>Setup: A watches an item owned by B (two devices)
-1. A taps heart on B's item
-2. B edits that item's price
-3. Observe A's device</x:v>
-      </x:c>
-      <x:c r="E34" s="7" t="str">
-        <x:v>A receives price-change notification (push or in-app)</x:v>
-      </x:c>
-      <x:c r="F34" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G34" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H34" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I34" s="6" t="n">
+      <x:c r="A34" s="6" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="B34" s="6" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C34" s="7" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="D34" s="7" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="E34" s="7" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="F34" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G34" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H34" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I34" s="6">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J34" s="6" t="str">
-        <x:v>Sam</x:v>
-      </x:c>
-      <x:c r="K34" s="6" t="str">
-        <x:v>Not run</x:v>
+      <x:c r="J34" s="6" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K34" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L34" s="6"/>
       <x:c r="M34" s="11"/>
@@ -5011,40 +6049,39 @@
       <x:c r="O34" s="6"/>
       <x:c r="P34" s="7"/>
     </x:row>
-    <x:row r="35" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A35" s="6" t="str">
-        <x:v>KS-T-034</x:v>
-      </x:c>
-      <x:c r="B35" s="6" t="str">
-        <x:v>Notifications</x:v>
-      </x:c>
-      <x:c r="C35" s="7" t="str">
-        <x:v>Permission prompt &amp; denial</x:v>
-      </x:c>
-      <x:c r="D35" s="7" t="str">
-        <x:v>1. Fresh install, trigger first notification
-2. Deny permission</x:v>
-      </x:c>
-      <x:c r="E35" s="7" t="str">
-        <x:v>App remains usable; no crash; sensible degraded behaviour</x:v>
-      </x:c>
-      <x:c r="F35" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G35" s="6" t="str">
-        <x:v>Permission</x:v>
-      </x:c>
-      <x:c r="H35" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I35" s="6" t="n">
+    <x:row r="35" ht="15.75" customHeight="1">
+      <x:c r="A35" s="6" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="B35" s="6" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="C35" s="7" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="D35" s="7" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="E35" s="7" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="F35" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G35" s="6" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="H35" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I35" s="6">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J35" s="6" t="str">
-        <x:v>Sam</x:v>
-      </x:c>
-      <x:c r="K35" s="6" t="str">
-        <x:v>Pass</x:v>
+      <x:c r="J35" s="6" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K35" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L35" s="6"/>
       <x:c r="M35" s="11"/>
@@ -5053,40 +6090,38 @@
       <x:c r="P35" s="7"/>
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1">
-      <x:c r="A36" s="6" t="str">
-        <x:v>KS-T-035</x:v>
-      </x:c>
-      <x:c r="B36" s="6" t="str">
-        <x:v>Notifications</x:v>
-      </x:c>
-      <x:c r="C36" s="7" t="str">
-        <x:v>Notification routing</x:v>
-      </x:c>
-      <x:c r="D36" s="19" t="str">
-        <x:v>Setup: two devices; B sends A a message while A is backgrounded
-1. Wait for push on A's device
-2. Tap the notification</x:v>
-      </x:c>
-      <x:c r="E36" s="7" t="str">
-        <x:v>Opens the related conversation/item screen</x:v>
-      </x:c>
-      <x:c r="F36" s="6" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="G36" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H36" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I36" s="6" t="n">
+      <x:c r="A36" s="6" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="B36" s="6" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="C36" s="7" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="D36" s="19" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="E36" s="7" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="F36" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G36" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H36" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I36" s="6">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J36" s="6" t="str">
-        <x:v>Sam</x:v>
-      </x:c>
-      <x:c r="K36" s="6" t="str">
-        <x:v>Not run</x:v>
+      <x:c r="J36" s="6" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K36" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L36" s="6"/>
       <x:c r="M36" s="11"/>
@@ -5094,88 +6129,85 @@
       <x:c r="O36" s="6"/>
       <x:c r="P36" s="7"/>
     </x:row>
-    <x:row r="37" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A37" s="6" t="str">
-        <x:v>KS-T-036</x:v>
-      </x:c>
-      <x:c r="B37" s="6" t="str">
-        <x:v>Chat</x:v>
-      </x:c>
-      <x:c r="C37" s="7" t="str">
-        <x:v>Text chat realtime</x:v>
-      </x:c>
-      <x:c r="D37" s="7" t="str">
-        <x:v>Setup: device 1 = account A, device 2 = account B (Test Data sheet)
-1. A sends several messages to B
-2. B replies while A's app is backgrounded</x:v>
-      </x:c>
-      <x:c r="E37" s="7" t="str">
-        <x:v>Messages appear near-instantly; correct order; unread badge on B</x:v>
-      </x:c>
-      <x:c r="F37" s="8" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G37" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H37" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I37" s="6" t="n">
+    <x:row r="37" ht="15.75" customHeight="1">
+      <x:c r="A37" s="6" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="B37" s="6" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="C37" s="7" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="D37" s="7" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="E37" s="7" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="F37" s="8" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G37" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H37" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I37" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J37" s="6" t="str">
-        <x:v>Jaeger</x:v>
-      </x:c>
-      <x:c r="K37" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L37" s="6" t="str">
-        <x:v>Rui / Sam</x:v>
-      </x:c>
-      <x:c r="M37" s="11" t="n">
+      <x:c r="J37" s="6" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K37" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L37" s="6" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M37" s="11">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N37" s="6"/>
       <x:c r="O37" s="6"/>
-      <x:c r="P37" s="7" t="str">
-        <x:v>Imported from the Chinese test plan completed by Rui / Sam on 2026-09-19.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A38" s="6" t="str">
-        <x:v>KS-T-037</x:v>
-      </x:c>
-      <x:c r="B38" s="6" t="str">
-        <x:v>Chat</x:v>
-      </x:c>
-      <x:c r="C38" s="7" t="str">
-        <x:v>Chat entry with item context</x:v>
-      </x:c>
-      <x:c r="D38" s="7" t="str">
-        <x:v>1. Open item detail
-2. Tap chat with seller</x:v>
-      </x:c>
-      <x:c r="E38" s="7" t="str">
-        <x:v>Conversation opens showing the item card/context</x:v>
-      </x:c>
-      <x:c r="F38" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G38" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H38" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I38" s="6" t="n">
+      <x:c r="P37" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="15.75" customHeight="1">
+      <x:c r="A38" s="6" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="B38" s="6" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="C38" s="7" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="D38" s="7" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="E38" s="7" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="F38" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G38" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H38" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I38" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J38" s="6" t="str">
-        <x:v>Jaeger</x:v>
-      </x:c>
-      <x:c r="K38" s="6" t="str">
-        <x:v>Pass</x:v>
+      <x:c r="J38" s="6" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K38" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L38" s="6"/>
       <x:c r="M38" s="11"/>
@@ -5183,87 +6215,85 @@
       <x:c r="O38" s="6"/>
       <x:c r="P38" s="7"/>
     </x:row>
-    <x:row r="39" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A39" s="6" t="str">
-        <x:v>KS-T-038</x:v>
-      </x:c>
-      <x:c r="B39" s="6" t="str">
-        <x:v>Chat</x:v>
-      </x:c>
-      <x:c r="C39" s="7" t="str">
-        <x:v>Unread badge behaviour</x:v>
-      </x:c>
-      <x:c r="D39" s="7" t="str">
-        <x:v>1. Receive messages in several conversations
-2. Open one</x:v>
-      </x:c>
-      <x:c r="E39" s="7" t="str">
-        <x:v>Badge counts correct; opened conversation badge clears</x:v>
-      </x:c>
-      <x:c r="F39" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G39" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H39" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I39" s="6" t="n">
+    <x:row r="39" ht="15.75" customHeight="1">
+      <x:c r="A39" s="6" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="B39" s="6" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="C39" s="7" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="D39" s="7" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="E39" s="7" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="F39" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G39" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H39" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I39" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J39" s="6" t="str">
-        <x:v>Jaeger</x:v>
-      </x:c>
-      <x:c r="K39" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L39" s="6" t="str">
-        <x:v>Rui / Sam</x:v>
-      </x:c>
-      <x:c r="M39" s="11" t="n">
+      <x:c r="J39" s="6" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K39" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L39" s="6" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M39" s="11">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N39" s="6"/>
       <x:c r="O39" s="6"/>
-      <x:c r="P39" s="7" t="str">
-        <x:v>Imported from the Chinese test plan completed by Rui / Sam on 2026-09-19.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A40" s="6" t="str">
-        <x:v>KS-T-039</x:v>
-      </x:c>
-      <x:c r="B40" s="6" t="str">
-        <x:v>Chat</x:v>
-      </x:c>
-      <x:c r="C40" s="7" t="str">
-        <x:v>Photo message</x:v>
-      </x:c>
-      <x:c r="D40" s="7" t="str">
-        <x:v>1. Send photo in chat
-2. View on receiver</x:v>
-      </x:c>
-      <x:c r="E40" s="7" t="str">
-        <x:v>Photo uploads, thumbnails render, full view opens</x:v>
-      </x:c>
-      <x:c r="F40" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G40" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H40" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I40" s="6" t="n">
+      <x:c r="P39" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="15.75" customHeight="1">
+      <x:c r="A40" s="6" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="B40" s="6" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="C40" s="7" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="D40" s="7" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="E40" s="7" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="F40" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G40" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H40" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I40" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J40" s="6" t="str">
-        <x:v>Jaeger</x:v>
-      </x:c>
-      <x:c r="K40" s="6" t="str">
-        <x:v>Pass</x:v>
+      <x:c r="J40" s="6" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K40" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L40" s="6"/>
       <x:c r="M40" s="11"/>
@@ -5271,40 +6301,39 @@
       <x:c r="O40" s="6"/>
       <x:c r="P40" s="7"/>
     </x:row>
-    <x:row r="41" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A41" s="6" t="str">
-        <x:v>KS-T-040</x:v>
-      </x:c>
-      <x:c r="B41" s="6" t="str">
-        <x:v>Chat</x:v>
-      </x:c>
-      <x:c r="C41" s="7" t="str">
-        <x:v>Voice message</x:v>
-      </x:c>
-      <x:c r="D41" s="7" t="str">
-        <x:v>1. Record voice message
-2. Play on receiver</x:v>
-      </x:c>
-      <x:c r="E41" s="7" t="str">
-        <x:v>Records and plays; duration shown; deny-mic path handled</x:v>
-      </x:c>
-      <x:c r="F41" s="6" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="G41" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H41" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I41" s="6" t="n">
+    <x:row r="41" ht="15.75" customHeight="1">
+      <x:c r="A41" s="6" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="B41" s="6" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="C41" s="7" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="D41" s="7" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="E41" s="7" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="F41" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G41" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H41" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I41" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J41" s="6" t="str">
-        <x:v>Jaeger</x:v>
-      </x:c>
-      <x:c r="K41" s="6" t="str">
-        <x:v>Pass</x:v>
+      <x:c r="J41" s="6" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K41" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L41" s="6"/>
       <x:c r="M41" s="11"/>
@@ -5312,39 +6341,39 @@
       <x:c r="O41" s="6"/>
       <x:c r="P41" s="7"/>
     </x:row>
-    <x:row r="42" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A42" s="6" t="str">
-        <x:v>KS-T-041</x:v>
-      </x:c>
-      <x:c r="B42" s="6" t="str">
-        <x:v>Chat</x:v>
-      </x:c>
-      <x:c r="C42" s="7" t="str">
-        <x:v>Message sanitisation</x:v>
-      </x:c>
-      <x:c r="D42" s="7" t="str">
-        <x:v>1. Send message containing &lt;script&gt; / HTML / emoji / long text</x:v>
-      </x:c>
-      <x:c r="E42" s="7" t="str">
-        <x:v>Rendered as plain text, no injection/broken layout</x:v>
-      </x:c>
-      <x:c r="F42" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G42" s="6" t="str">
-        <x:v>Security</x:v>
-      </x:c>
-      <x:c r="H42" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I42" s="6" t="n">
+    <x:row r="42" ht="15.75" customHeight="1">
+      <x:c r="A42" s="6" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="B42" s="6" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="C42" s="7" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="D42" s="7" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="E42" s="7" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="F42" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G42" s="6" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H42" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I42" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J42" s="6" t="str">
-        <x:v>Jaeger</x:v>
-      </x:c>
-      <x:c r="K42" s="6" t="str">
-        <x:v>Pass</x:v>
+      <x:c r="J42" s="6" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K42" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L42" s="6"/>
       <x:c r="M42" s="11"/>
@@ -5352,40 +6381,39 @@
       <x:c r="O42" s="6"/>
       <x:c r="P42" s="7"/>
     </x:row>
-    <x:row r="43" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A43" s="6" t="str">
-        <x:v>KS-T-042</x:v>
-      </x:c>
-      <x:c r="B43" s="6" t="str">
-        <x:v>Chat</x:v>
-      </x:c>
-      <x:c r="C43" s="7" t="str">
-        <x:v>Swipe delete conversation</x:v>
-      </x:c>
-      <x:c r="D43" s="19" t="str">
-        <x:v>1. Swipe a conversation
-2. Confirm</x:v>
-      </x:c>
-      <x:c r="E43" s="7" t="str">
-        <x:v>Conversation removed; reappears on new message</x:v>
-      </x:c>
-      <x:c r="F43" s="6" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="G43" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H43" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I43" s="6" t="n">
+    <x:row r="43" ht="15.75" customHeight="1">
+      <x:c r="A43" s="6" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="B43" s="6" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="C43" s="7" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="D43" s="19" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="E43" s="7" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="F43" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G43" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H43" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I43" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J43" s="6" t="str">
-        <x:v>Jaeger</x:v>
-      </x:c>
-      <x:c r="K43" s="6" t="str">
-        <x:v>Pass</x:v>
+      <x:c r="J43" s="6" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K43" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L43" s="6"/>
       <x:c r="M43" s="11"/>
@@ -5393,40 +6421,39 @@
       <x:c r="O43" s="6"/>
       <x:c r="P43" s="7"/>
     </x:row>
-    <x:row r="44" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A44" s="6" t="str">
-        <x:v>KS-T-043</x:v>
-      </x:c>
-      <x:c r="B44" s="6" t="str">
-        <x:v>Trade</x:v>
-      </x:c>
-      <x:c r="C44" s="7" t="str">
-        <x:v>Initiate trade</x:v>
-      </x:c>
-      <x:c r="D44" s="7" t="str">
-        <x:v>1. From chat/detail, propose trade on an item
-2. Other account accepts</x:v>
-      </x:c>
-      <x:c r="E44" s="7" t="str">
-        <x:v>Order/trade created with correct item, price and status</x:v>
-      </x:c>
-      <x:c r="F44" s="8" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G44" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H44" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I44" s="6" t="n">
+    <x:row r="44" ht="15.75" customHeight="1">
+      <x:c r="A44" s="6" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="B44" s="6" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C44" s="7" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="D44" s="7" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="E44" s="7" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="F44" s="8" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G44" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H44" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I44" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J44" s="6" t="str">
-        <x:v>Jack</x:v>
-      </x:c>
-      <x:c r="K44" s="6" t="str">
-        <x:v>Pass</x:v>
+      <x:c r="J44" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K44" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L44" s="6"/>
       <x:c r="M44" s="11"/>
@@ -5435,38 +6462,38 @@
       <x:c r="P44" s="7"/>
     </x:row>
     <x:row r="45" ht="15.75" customHeight="1">
-      <x:c r="A45" s="6" t="str">
-        <x:v>KS-T-044</x:v>
-      </x:c>
-      <x:c r="B45" s="6" t="str">
-        <x:v>Trade</x:v>
-      </x:c>
-      <x:c r="C45" s="7" t="str">
-        <x:v>QR / handshake verification</x:v>
-      </x:c>
-      <x:c r="D45" s="7" t="str">
-        <x:v>1. Both parties meet; complete QR verification flow</x:v>
-      </x:c>
-      <x:c r="E45" s="7" t="str">
-        <x:v>Meetup verified; trade marked completed for both</x:v>
-      </x:c>
-      <x:c r="F45" s="8" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G45" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H45" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I45" s="6" t="n">
+      <x:c r="A45" s="6" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="B45" s="6" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C45" s="7" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="D45" s="7" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="E45" s="7" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="F45" s="8" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G45" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H45" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I45" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J45" s="6" t="str">
-        <x:v>Jack</x:v>
-      </x:c>
-      <x:c r="K45" s="6" t="str">
-        <x:v>Not run</x:v>
+      <x:c r="J45" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K45" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L45" s="6"/>
       <x:c r="M45" s="11"/>
@@ -5475,38 +6502,38 @@
       <x:c r="P45" s="7"/>
     </x:row>
     <x:row r="46" ht="15.75" customHeight="1">
-      <x:c r="A46" s="6" t="str">
-        <x:v>KS-T-045</x:v>
-      </x:c>
-      <x:c r="B46" s="6" t="str">
-        <x:v>Trade</x:v>
-      </x:c>
-      <x:c r="C46" s="7" t="str">
-        <x:v>Cancel trade</x:v>
-      </x:c>
-      <x:c r="D46" s="7" t="str">
-        <x:v>1. Cancel a pending trade</x:v>
-      </x:c>
-      <x:c r="E46" s="7" t="str">
-        <x:v>Status reverts; item available again; both parties notified</x:v>
-      </x:c>
-      <x:c r="F46" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G46" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H46" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I46" s="6" t="n">
+      <x:c r="A46" s="6" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="B46" s="6" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C46" s="7" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="D46" s="7" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="E46" s="7" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="F46" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G46" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H46" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I46" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J46" s="6" t="str">
-        <x:v>Jack</x:v>
-      </x:c>
-      <x:c r="K46" s="6" t="str">
-        <x:v>Not run</x:v>
+      <x:c r="J46" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K46" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L46" s="6"/>
       <x:c r="M46" s="11"/>
@@ -5515,39 +6542,38 @@
       <x:c r="P46" s="7"/>
     </x:row>
     <x:row r="47" ht="15.75" customHeight="1">
-      <x:c r="A47" s="6" t="str">
-        <x:v>KS-T-046</x:v>
-      </x:c>
-      <x:c r="B47" s="6" t="str">
-        <x:v>Trade</x:v>
-      </x:c>
-      <x:c r="C47" s="7" t="str">
-        <x:v>Rating after completion</x:v>
-      </x:c>
-      <x:c r="D47" s="7" t="str">
-        <x:v>1. Complete a trade
-2. Leave a rating/review</x:v>
-      </x:c>
-      <x:c r="E47" s="7" t="str">
-        <x:v>Rating saved and shown on counterparty profile</x:v>
-      </x:c>
-      <x:c r="F47" s="6" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="G47" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H47" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I47" s="6" t="n">
+      <x:c r="A47" s="6" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="B47" s="6" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C47" s="7" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="D47" s="7" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="E47" s="7" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="F47" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G47" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H47" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I47" s="6">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J47" s="6" t="str">
-        <x:v>Jack</x:v>
-      </x:c>
-      <x:c r="K47" s="6" t="str">
-        <x:v>Not run</x:v>
+      <x:c r="J47" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K47" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L47" s="20"/>
       <x:c r="M47" s="11"/>
@@ -5555,178 +6581,177 @@
       <x:c r="O47" s="6"/>
       <x:c r="P47" s="7"/>
     </x:row>
-    <x:row r="48" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A48" s="6" t="str">
-        <x:v>KS-T-047</x:v>
-      </x:c>
-      <x:c r="B48" s="6" t="str">
-        <x:v>Safety</x:v>
-      </x:c>
-      <x:c r="C48" s="7" t="str">
-        <x:v>Report item / user</x:v>
-      </x:c>
-      <x:c r="D48" s="7" t="str">
-        <x:v>1. Report an item and a user with reason + description</x:v>
-      </x:c>
-      <x:c r="E48" s="7" t="str">
-        <x:v>Confirmation shown; report stored server-side</x:v>
-      </x:c>
-      <x:c r="F48" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G48" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H48" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I48" s="6" t="n">
+    <x:row r="48" ht="15.75" customHeight="1">
+      <x:c r="A48" s="6" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="B48" s="6" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="C48" s="7" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="D48" s="7" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="E48" s="7" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="F48" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G48" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H48" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I48" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J48" s="6" t="str">
-        <x:v>Rui</x:v>
-      </x:c>
-      <x:c r="K48" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L48" s="6" t="str">
-        <x:v>Rui / Sam</x:v>
-      </x:c>
-      <x:c r="M48" s="11" t="n">
+      <x:c r="J48" s="6" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K48" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L48" s="6" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M48" s="11">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N48" s="6"/>
       <x:c r="O48" s="6"/>
-      <x:c r="P48" s="7" t="str">
-        <x:v>Imported from the Chinese test plan completed by Rui / Sam on 2026-09-19.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A49" s="6" t="str">
-        <x:v>KS-T-048</x:v>
-      </x:c>
-      <x:c r="B49" s="6" t="str">
-        <x:v>Safety</x:v>
-      </x:c>
-      <x:c r="C49" s="7" t="str">
-        <x:v>Duplicate report handling</x:v>
-      </x:c>
-      <x:c r="D49" s="7" t="str">
-        <x:v>1. Report the same item twice</x:v>
-      </x:c>
-      <x:c r="E49" s="7" t="str">
-        <x:v>Sensible handling (dedupe or allowed) without error/crash</x:v>
-      </x:c>
-      <x:c r="F49" s="6" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="G49" s="6" t="str">
-        <x:v>Error state</x:v>
-      </x:c>
-      <x:c r="H49" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I49" s="6" t="n">
+      <x:c r="P48" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="15.75" customHeight="1">
+      <x:c r="A49" s="6" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="B49" s="6" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="C49" s="7" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="D49" s="7" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="E49" s="7" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="F49" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G49" s="6" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="H49" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I49" s="6">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J49" s="6" t="str">
-        <x:v>Rui</x:v>
-      </x:c>
-      <x:c r="K49" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L49" s="6" t="str">
-        <x:v>Rui / Sam</x:v>
-      </x:c>
-      <x:c r="M49" s="11" t="n">
+      <x:c r="J49" s="6" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K49" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L49" s="6" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M49" s="11">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N49" s="6"/>
       <x:c r="O49" s="6"/>
-      <x:c r="P49" s="7" t="str">
-        <x:v>Imported from the Chinese test plan completed by Rui / Sam on 2026-09-19.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A50" s="6" t="str">
-        <x:v>KS-T-049</x:v>
-      </x:c>
-      <x:c r="B50" s="6" t="str">
-        <x:v>Safety</x:v>
-      </x:c>
-      <x:c r="C50" s="7" t="str">
-        <x:v>Unauthorised data access</x:v>
-      </x:c>
-      <x:c r="D50" s="7" t="str">
-        <x:v>1. As normal user, attempt to edit another user's item via UI</x:v>
-      </x:c>
-      <x:c r="E50" s="7" t="str">
-        <x:v>Rejected with 401/403; no data change</x:v>
-      </x:c>
-      <x:c r="F50" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G50" s="6" t="str">
-        <x:v>Security</x:v>
-      </x:c>
-      <x:c r="H50" s="6" t="str">
-        <x:v>API</x:v>
-      </x:c>
-      <x:c r="I50" s="6" t="n">
+      <x:c r="P49" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="15.75" customHeight="1">
+      <x:c r="A50" s="6" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="B50" s="6" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="C50" s="7" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="D50" s="7" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="E50" s="7" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="F50" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G50" s="6" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H50" s="6" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="I50" s="6">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J50" s="6" t="str">
-        <x:v>Rui</x:v>
-      </x:c>
-      <x:c r="K50" s="6" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="L50" s="6" t="str">
-        <x:v>Rui / Sam</x:v>
-      </x:c>
-      <x:c r="M50" s="11" t="n">
+      <x:c r="J50" s="6" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K50" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L50" s="6" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M50" s="11">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N50" s="6"/>
       <x:c r="O50" s="6"/>
-      <x:c r="P50" s="7" t="str">
-        <x:v>Imported from the Chinese test plan completed by Rui / Sam on 2026-09-19.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A51" s="6" t="str">
-        <x:v>KS-T-050</x:v>
-      </x:c>
-      <x:c r="B51" s="6" t="str">
-        <x:v>API</x:v>
-      </x:c>
-      <x:c r="C51" s="7" t="str">
-        <x:v>Backend health on Render</x:v>
-      </x:c>
-      <x:c r="D51" s="7" t="str">
-        <x:v>1. GET deployed API health endpoint
-2. Load app against Render backend</x:v>
-      </x:c>
-      <x:c r="E51" s="7" t="str">
-        <x:v>Healthy response; app functions against deployed backend</x:v>
-      </x:c>
-      <x:c r="F51" s="8" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G51" s="6" t="str">
-        <x:v>API</x:v>
-      </x:c>
-      <x:c r="H51" s="6" t="str">
-        <x:v>API</x:v>
-      </x:c>
-      <x:c r="I51" s="6" t="n">
+      <x:c r="P50" s="7" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="15.75" customHeight="1">
+      <x:c r="A51" s="6" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="B51" s="6" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="C51" s="7" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="D51" s="7" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="E51" s="7" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="F51" s="8" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G51" s="6" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="H51" s="6" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="I51" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J51" s="6" t="str">
-        <x:v>Sam</x:v>
-      </x:c>
-      <x:c r="K51" s="6" t="str">
-        <x:v>Pass</x:v>
+      <x:c r="J51" s="6" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K51" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L51" s="6"/>
       <x:c r="M51" s="11"/>
@@ -5735,38 +6760,38 @@
       <x:c r="P51" s="7"/>
     </x:row>
     <x:row r="52" ht="15.75" customHeight="1">
-      <x:c r="A52" s="6" t="str">
-        <x:v>KS-T-051</x:v>
-      </x:c>
-      <x:c r="B52" s="6" t="str">
-        <x:v>API</x:v>
-      </x:c>
-      <x:c r="C52" s="7" t="str">
-        <x:v>Unauthenticated access</x:v>
-      </x:c>
-      <x:c r="D52" s="7" t="str">
-        <x:v>1. Call protected endpoints without token (curl/Postman)</x:v>
-      </x:c>
-      <x:c r="E52" s="7" t="str">
-        <x:v>401 returned; no data leak</x:v>
-      </x:c>
-      <x:c r="F52" s="8" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G52" s="6" t="str">
-        <x:v>Security</x:v>
-      </x:c>
-      <x:c r="H52" s="6" t="str">
-        <x:v>API</x:v>
-      </x:c>
-      <x:c r="I52" s="6" t="n">
+      <x:c r="A52" s="6" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="B52" s="6" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="C52" s="7" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="D52" s="7" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="E52" s="7" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="F52" s="8" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G52" s="6" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H52" s="6" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="I52" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J52" s="6" t="str">
-        <x:v>Sam</x:v>
-      </x:c>
-      <x:c r="K52" s="6" t="str">
-        <x:v>Not run</x:v>
+      <x:c r="J52" s="6" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K52" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L52" s="6"/>
       <x:c r="M52" s="11"/>
@@ -5775,38 +6800,38 @@
       <x:c r="P52" s="7"/>
     </x:row>
     <x:row r="53" ht="15.75" customHeight="1">
-      <x:c r="A53" s="6" t="str">
-        <x:v>KS-T-052</x:v>
-      </x:c>
-      <x:c r="B53" s="6" t="str">
-        <x:v>API</x:v>
-      </x:c>
-      <x:c r="C53" s="7" t="str">
-        <x:v>OTP / reset endpoints abuse</x:v>
-      </x:c>
-      <x:c r="D53" s="7" t="str">
-        <x:v>1. Spam request-password-reset rapidly</x:v>
-      </x:c>
-      <x:c r="E53" s="7" t="str">
-        <x:v>Cooldown/429 enforced server-side</x:v>
-      </x:c>
-      <x:c r="F53" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G53" s="6" t="str">
-        <x:v>Security</x:v>
-      </x:c>
-      <x:c r="H53" s="6" t="str">
-        <x:v>API</x:v>
-      </x:c>
-      <x:c r="I53" s="6" t="n">
+      <x:c r="A53" s="6" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="B53" s="6" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="C53" s="7" t="s">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="D53" s="7" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="E53" s="7" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="F53" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G53" s="6" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H53" s="6" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="I53" s="6">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J53" s="6" t="str">
-        <x:v>Sam</x:v>
-      </x:c>
-      <x:c r="K53" s="6" t="str">
-        <x:v>Not run</x:v>
+      <x:c r="J53" s="6" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K53" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L53" s="6"/>
       <x:c r="M53" s="11"/>
@@ -5814,40 +6839,39 @@
       <x:c r="O53" s="6"/>
       <x:c r="P53" s="7"/>
     </x:row>
-    <x:row r="54" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A54" s="6" t="str">
-        <x:v>KS-T-053</x:v>
-      </x:c>
-      <x:c r="B54" s="6" t="str">
-        <x:v>API</x:v>
-      </x:c>
-      <x:c r="C54" s="7" t="str">
-        <x:v>Data persistence</x:v>
-      </x:c>
-      <x:c r="D54" s="7" t="str">
-        <x:v>1. Publish item / send message
-2. Restart app &amp; server round-trip</x:v>
-      </x:c>
-      <x:c r="E54" s="7" t="str">
-        <x:v>Data persists correctly in MongoDB</x:v>
-      </x:c>
-      <x:c r="F54" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G54" s="6" t="str">
-        <x:v>API</x:v>
-      </x:c>
-      <x:c r="H54" s="6" t="str">
-        <x:v>API</x:v>
-      </x:c>
-      <x:c r="I54" s="6" t="n">
+    <x:row r="54" ht="15.75" customHeight="1">
+      <x:c r="A54" s="6" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="B54" s="6" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="C54" s="7" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="D54" s="7" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="E54" s="7" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="F54" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G54" s="6" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="H54" s="6" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="I54" s="6">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J54" s="6" t="str">
-        <x:v>Sam</x:v>
-      </x:c>
-      <x:c r="K54" s="6" t="str">
-        <x:v>Pass</x:v>
+      <x:c r="J54" s="6" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K54" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L54" s="6"/>
       <x:c r="M54" s="11"/>
@@ -5856,40 +6880,38 @@
       <x:c r="P54" s="7"/>
     </x:row>
     <x:row r="55" ht="15.75" customHeight="1">
-      <x:c r="A55" s="6" t="str">
-        <x:v>KS-T-054</x:v>
-      </x:c>
-      <x:c r="B55" s="6" t="str">
-        <x:v>Performance</x:v>
-      </x:c>
-      <x:c r="C55" s="7" t="str">
-        <x:v>App cold start time</x:v>
-      </x:c>
-      <x:c r="D55" s="19" t="str">
-        <x:v>1. Force-kill the app
-2. Cold start on emulator and real device, timing tap-to-home-interactive
-3. Repeat 3x per device</x:v>
-      </x:c>
-      <x:c r="E55" s="7" t="str">
-        <x:v>Cold start consistently fast (target &lt; 3 s), no long white screen; record timings in Evidence</x:v>
-      </x:c>
-      <x:c r="F55" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G55" s="6" t="str">
-        <x:v>Performance</x:v>
-      </x:c>
-      <x:c r="H55" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I55" s="6" t="n">
+      <x:c r="A55" s="6" t="s">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="B55" s="6" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="C55" s="7" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="D55" s="19" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="E55" s="7" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="F55" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G55" s="6" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="H55" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I55" s="6">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J55" s="6" t="str">
-        <x:v>Sam</x:v>
-      </x:c>
-      <x:c r="K55" s="6" t="str">
-        <x:v>Not run</x:v>
+      <x:c r="J55" s="6" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K55" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L55" s="6"/>
       <x:c r="M55" s="11"/>
@@ -5898,40 +6920,38 @@
       <x:c r="P55" s="7"/>
     </x:row>
     <x:row r="56" ht="15.75" customHeight="1">
-      <x:c r="A56" s="6" t="str">
-        <x:v>KS-T-055</x:v>
-      </x:c>
-      <x:c r="B56" s="6" t="str">
-        <x:v>Performance</x:v>
-      </x:c>
-      <x:c r="C56" s="7" t="str">
-        <x:v>Home feed full-scroll smoothness</x:v>
-      </x:c>
-      <x:c r="D56" s="19" t="str">
-        <x:v>1. Seed 50+ items (Test Data sheet)
-2. Scroll the entire home feed on emulator and real device
-3. Note any jank / freezes</x:v>
-      </x:c>
-      <x:c r="E56" s="7" t="str">
-        <x:v>Scrolling stays smooth; no visible frame drops; note which device was used</x:v>
-      </x:c>
-      <x:c r="F56" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G56" s="6" t="str">
-        <x:v>Performance</x:v>
-      </x:c>
-      <x:c r="H56" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I56" s="6" t="n">
+      <x:c r="A56" s="6" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="B56" s="6" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="C56" s="7" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="D56" s="19" t="s">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="E56" s="7" t="s">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="F56" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G56" s="6" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="H56" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I56" s="6">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J56" s="6" t="str">
-        <x:v>Rui</x:v>
-      </x:c>
-      <x:c r="K56" s="6" t="str">
-        <x:v>Not run</x:v>
+      <x:c r="J56" s="6" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K56" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L56" s="6"/>
       <x:c r="M56" s="11"/>
@@ -5940,40 +6960,38 @@
       <x:c r="P56" s="7"/>
     </x:row>
     <x:row r="57" ht="15.75" customHeight="1">
-      <x:c r="A57" s="6" t="str">
-        <x:v>KS-T-056</x:v>
-      </x:c>
-      <x:c r="B57" s="6" t="str">
-        <x:v>Performance</x:v>
-      </x:c>
-      <x:c r="C57" s="7" t="str">
-        <x:v>API latency baseline &amp; light load</x:v>
-      </x:c>
-      <x:c r="D57" s="19" t="str">
-        <x:v>1. Measure response time of key GET endpoints (items list, item detail, chat history)
-2. Load one endpoint with ~20 concurrent requests for 30 s (autocannon/k6/hey)
-3. Record p50/p95 and error count</x:v>
-      </x:c>
-      <x:c r="E57" s="7" t="str">
-        <x:v>Zero errors under light load; latency stable and acceptable; record numbers in Evidence</x:v>
-      </x:c>
-      <x:c r="F57" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G57" s="6" t="str">
-        <x:v>Performance</x:v>
-      </x:c>
-      <x:c r="H57" s="6" t="str">
-        <x:v>API</x:v>
-      </x:c>
-      <x:c r="I57" s="6" t="n">
+      <x:c r="A57" s="6" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="B57" s="6" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="C57" s="7" t="s">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="D57" s="19" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="E57" s="7" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="F57" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G57" s="6" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="H57" s="6" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="I57" s="6">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J57" s="6" t="str">
-        <x:v>Sam</x:v>
-      </x:c>
-      <x:c r="K57" s="6" t="str">
-        <x:v>Not run</x:v>
+      <x:c r="J57" s="6" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K57" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L57" s="6"/>
       <x:c r="M57" s="11"/>
@@ -5981,40 +6999,39 @@
       <x:c r="O57" s="6"/>
       <x:c r="P57" s="7"/>
     </x:row>
-    <x:row r="58" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A58" s="6" t="str">
-        <x:v>KS-T-057</x:v>
-      </x:c>
-      <x:c r="B58" s="6" t="str">
-        <x:v>Performance</x:v>
-      </x:c>
-      <x:c r="C58" s="7" t="str">
-        <x:v>Item detail image loading</x:v>
-      </x:c>
-      <x:c r="D58" s="19" t="str">
-        <x:v>1. Open a 5-photo item on a real device
-2. Repeat on a throttled connection if possible</x:v>
-      </x:c>
-      <x:c r="E58" s="7" t="str">
-        <x:v>Thumbnails load progressively; full images open without freeze or memory warning</x:v>
-      </x:c>
-      <x:c r="F58" s="6" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="G58" s="6" t="str">
-        <x:v>Performance</x:v>
-      </x:c>
-      <x:c r="H58" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I58" s="6" t="n">
+    <x:row r="58" ht="15.75" customHeight="1">
+      <x:c r="A58" s="6" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="B58" s="6" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="C58" s="7" t="s">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="D58" s="19" t="s">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="E58" s="7" t="s">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="F58" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G58" s="6" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="H58" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I58" s="6">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J58" s="6" t="str">
-        <x:v>Jack</x:v>
-      </x:c>
-      <x:c r="K58" s="6" t="str">
-        <x:v>Pass</x:v>
+      <x:c r="J58" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K58" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L58" s="6"/>
       <x:c r="M58" s="11"/>
@@ -6022,40 +7039,39 @@
       <x:c r="O58" s="6"/>
       <x:c r="P58" s="7"/>
     </x:row>
-    <x:row r="59" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A59" s="6" t="str">
-        <x:v>KS-T-058</x:v>
-      </x:c>
-      <x:c r="B59" s="6" t="str">
-        <x:v>Cross-cutting</x:v>
-      </x:c>
-      <x:c r="C59" s="7" t="str">
-        <x:v>Dark mode — auth &amp; profile</x:v>
-      </x:c>
-      <x:c r="D59" s="7" t="str">
-        <x:v>1. Switch system/app to dark mode
-2. Walk login, forgot-password, profile screens</x:v>
-      </x:c>
-      <x:c r="E59" s="7" t="str">
-        <x:v>Text readable, contrast OK, no white-on-white (recent fix)</x:v>
-      </x:c>
-      <x:c r="F59" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G59" s="6" t="str">
-        <x:v>Cross-cutting</x:v>
-      </x:c>
-      <x:c r="H59" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I59" s="6" t="n">
+    <x:row r="59" ht="15.75" customHeight="1">
+      <x:c r="A59" s="6" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="B59" s="6" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="C59" s="7" t="s">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="D59" s="7" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="E59" s="7" t="s">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="F59" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G59" s="6" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="H59" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I59" s="6">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J59" s="6" t="str">
-        <x:v>Jenny</x:v>
-      </x:c>
-      <x:c r="K59" s="6" t="str">
-        <x:v>Pass</x:v>
+      <x:c r="J59" s="6" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K59" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L59" s="6"/>
       <x:c r="M59" s="11"/>
@@ -6063,39 +7079,39 @@
       <x:c r="O59" s="6"/>
       <x:c r="P59" s="7"/>
     </x:row>
-    <x:row r="60" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A60" s="6" t="str">
-        <x:v>KS-T-059</x:v>
-      </x:c>
-      <x:c r="B60" s="6" t="str">
-        <x:v>Cross-cutting</x:v>
-      </x:c>
-      <x:c r="C60" s="7" t="str">
-        <x:v>Dark mode — publish &amp; detail</x:v>
-      </x:c>
-      <x:c r="D60" s="7" t="str">
-        <x:v>1. Dark mode over publish flow and item detail</x:v>
-      </x:c>
-      <x:c r="E60" s="7" t="str">
-        <x:v>All controls readable; images unaffected</x:v>
-      </x:c>
-      <x:c r="F60" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G60" s="6" t="str">
-        <x:v>Cross-cutting</x:v>
-      </x:c>
-      <x:c r="H60" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I60" s="6" t="n">
+    <x:row r="60" ht="15.75" customHeight="1">
+      <x:c r="A60" s="6" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="B60" s="6" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="C60" s="7" t="s">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="D60" s="7" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="E60" s="7" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="F60" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G60" s="6" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="H60" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I60" s="6">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J60" s="6" t="str">
-        <x:v>Jack</x:v>
-      </x:c>
-      <x:c r="K60" s="6" t="str">
-        <x:v>Pass</x:v>
+      <x:c r="J60" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K60" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L60" s="6"/>
       <x:c r="M60" s="11"/>
@@ -6103,85 +7119,85 @@
       <x:c r="O60" s="6"/>
       <x:c r="P60" s="7"/>
     </x:row>
-    <x:row r="61" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A61" s="6" t="str">
-        <x:v>KS-T-060</x:v>
-      </x:c>
-      <x:c r="B61" s="6" t="str">
-        <x:v>Cross-cutting</x:v>
-      </x:c>
-      <x:c r="C61" s="7" t="str">
-        <x:v>Dark mode — discovery &amp; reports</x:v>
-      </x:c>
-      <x:c r="D61" s="7" t="str">
-        <x:v>1. Dark mode over home/search/detail/report dialogs</x:v>
-      </x:c>
-      <x:c r="E61" s="7" t="str">
-        <x:v>Consistent colors, readable text</x:v>
-      </x:c>
-      <x:c r="F61" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G61" s="6" t="str">
-        <x:v>Cross-cutting</x:v>
-      </x:c>
-      <x:c r="H61" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I61" s="6" t="n">
+    <x:row r="61" ht="15.75" customHeight="1">
+      <x:c r="A61" s="6" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="B61" s="6" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="C61" s="7" t="s">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="D61" s="7" t="s">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="E61" s="7" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="F61" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G61" s="6" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="H61" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I61" s="6">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J61" s="6" t="str">
-        <x:v>Rui</x:v>
-      </x:c>
-      <x:c r="K61" s="6" t="str">
-        <x:v>Fail</x:v>
-      </x:c>
-      <x:c r="L61" s="6" t="str">
-        <x:v>Rui / Sam</x:v>
-      </x:c>
-      <x:c r="M61" s="11" t="n">
+      <x:c r="J61" s="6" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K61" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L61" s="6" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M61" s="11">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N61" s="6"/>
       <x:c r="O61" s="6"/>
-      <x:c r="P61" s="7" t="str">
-        <x:v>Marked Fail by Rui / Sam on 2026-09-19; GitHub defect link pending.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A62" s="6" t="str">
-        <x:v>KS-T-061</x:v>
-      </x:c>
-      <x:c r="B62" s="6" t="str">
-        <x:v>Cross-cutting</x:v>
-      </x:c>
-      <x:c r="C62" s="7" t="str">
-        <x:v>Dark mode — chat &amp; watchlist</x:v>
-      </x:c>
-      <x:c r="D62" s="7" t="str">
-        <x:v>1. Dark mode over chat list, conversation, watchlist</x:v>
-      </x:c>
-      <x:c r="E62" s="7" t="str">
-        <x:v>Consistent colors, readable text</x:v>
-      </x:c>
-      <x:c r="F62" s="6" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G62" s="6" t="str">
-        <x:v>Cross-cutting</x:v>
-      </x:c>
-      <x:c r="H62" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I62" s="6" t="n">
+      <x:c r="P61" s="7" t="s">
+        <x:v>225</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="15.75" customHeight="1">
+      <x:c r="A62" s="6" t="s">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="B62" s="6" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="C62" s="7" t="s">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="D62" s="7" t="s">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="E62" s="7" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="F62" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G62" s="6" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="H62" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I62" s="6">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J62" s="6" t="str">
-        <x:v>Jaeger</x:v>
-      </x:c>
-      <x:c r="K62" s="6" t="str">
-        <x:v>Pass</x:v>
+      <x:c r="J62" s="6" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K62" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L62" s="6"/>
       <x:c r="M62" s="11"/>
@@ -6189,39 +7205,39 @@
       <x:c r="O62" s="6"/>
       <x:c r="P62" s="7"/>
     </x:row>
-    <x:row r="63" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A63" s="6" t="str">
-        <x:v>KS-T-062</x:v>
-      </x:c>
-      <x:c r="B63" s="6" t="str">
-        <x:v>Cross-cutting</x:v>
-      </x:c>
-      <x:c r="C63" s="7" t="str">
-        <x:v>First-run empty states</x:v>
-      </x:c>
-      <x:c r="D63" s="7" t="str">
-        <x:v>1. Fresh account with no items/chats/watchlist/reports</x:v>
-      </x:c>
-      <x:c r="E63" s="7" t="str">
-        <x:v>Friendly empty states everywhere; no blank screens</x:v>
-      </x:c>
-      <x:c r="F63" s="6" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="G63" s="6" t="str">
-        <x:v>Empty state</x:v>
-      </x:c>
-      <x:c r="H63" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I63" s="6" t="n">
+    <x:row r="63" ht="15.75" customHeight="1">
+      <x:c r="A63" s="6" t="s">
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="B63" s="6" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="C63" s="7" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="D63" s="7" t="s">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="E63" s="7" t="s">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="F63" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G63" s="6" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="H63" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I63" s="6">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J63" s="6" t="str">
-        <x:v>Rui</x:v>
-      </x:c>
-      <x:c r="K63" s="6" t="str">
-        <x:v>Pass</x:v>
+      <x:c r="J63" s="6" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K63" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L63" s="6"/>
       <x:c r="M63" s="11"/>
@@ -6229,40 +7245,39 @@
       <x:c r="O63" s="6"/>
       <x:c r="P63" s="7"/>
     </x:row>
-    <x:row r="64" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A64" s="6" t="str">
-        <x:v>KS-T-063</x:v>
-      </x:c>
-      <x:c r="B64" s="6" t="str">
-        <x:v>Cross-cutting</x:v>
-      </x:c>
-      <x:c r="C64" s="7" t="str">
-        <x:v>App resume / background</x:v>
-      </x:c>
-      <x:c r="D64" s="19" t="str">
-        <x:v>1. Background app mid-flow
-2. Return after 1 min and 10 min</x:v>
-      </x:c>
-      <x:c r="E64" s="7" t="str">
-        <x:v>Session kept or clean re-auth; no state corruption</x:v>
-      </x:c>
-      <x:c r="F64" s="6" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="G64" s="6" t="str">
-        <x:v>Cross-cutting</x:v>
-      </x:c>
-      <x:c r="H64" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I64" s="6" t="n">
+    <x:row r="64" ht="15.75" customHeight="1">
+      <x:c r="A64" s="6" t="s">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="B64" s="6" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="C64" s="7" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="D64" s="19" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="E64" s="7" t="s">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="F64" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G64" s="6" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="H64" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I64" s="6">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J64" s="6" t="str">
-        <x:v>Sam</x:v>
-      </x:c>
-      <x:c r="K64" s="6" t="str">
-        <x:v>Pass</x:v>
+      <x:c r="J64" s="6" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K64" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L64" s="6"/>
       <x:c r="M64" s="11"/>
@@ -6270,40 +7285,39 @@
       <x:c r="O64" s="6"/>
       <x:c r="P64" s="7"/>
     </x:row>
-    <x:row r="65" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A65" s="6" t="str">
-        <x:v>KS-T-064</x:v>
-      </x:c>
-      <x:c r="B65" s="6" t="str">
-        <x:v>Cross-cutting</x:v>
-      </x:c>
-      <x:c r="C65" s="7" t="str">
-        <x:v>Fresh install vs upgrade</x:v>
-      </x:c>
-      <x:c r="D65" s="7" t="str">
-        <x:v>1. Fresh install and log in
-2. (If applicable) install over existing build</x:v>
-      </x:c>
-      <x:c r="E65" s="7" t="str">
-        <x:v>Clean first-run; existing session/data intact on upgrade</x:v>
-      </x:c>
-      <x:c r="F65" s="6" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="G65" s="6" t="str">
-        <x:v>Cross-cutting</x:v>
-      </x:c>
-      <x:c r="H65" s="6" t="str">
-        <x:v>iOS+Android</x:v>
-      </x:c>
-      <x:c r="I65" s="6" t="n">
+    <x:row r="65" ht="15.75" customHeight="1">
+      <x:c r="A65" s="6" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="B65" s="6" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="C65" s="7" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="D65" s="7" t="s">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="E65" s="7" t="s">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="F65" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G65" s="6" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="H65" s="6" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="I65" s="6">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J65" s="6" t="str">
-        <x:v>Sam</x:v>
-      </x:c>
-      <x:c r="K65" s="6" t="str">
-        <x:v>Pass</x:v>
+      <x:c r="J65" s="6" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K65" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L65" s="6"/>
       <x:c r="M65" s="11"/>
@@ -6311,41 +7325,39 @@
       <x:c r="O65" s="6"/>
       <x:c r="P65" s="7"/>
     </x:row>
-    <x:row r="66" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A66" s="6" t="str">
-        <x:v>KS-T-065</x:v>
-      </x:c>
-      <x:c r="B66" s="6" t="str">
-        <x:v>Cross-cutting</x:v>
-      </x:c>
-      <x:c r="C66" s="7" t="str">
-        <x:v>Real-device regression — iPhone (Auth &amp; Profile)</x:v>
-      </x:c>
-      <x:c r="D66" s="7" t="str">
-        <x:v>1. Install latest pre build on physical iPhone (iOS 13+)
-2. Re-run your module's P0 cases from this sheet on the device
-3. Attach evidence</x:v>
-      </x:c>
-      <x:c r="E66" s="7" t="str">
-        <x:v>All P0 cases pass on real device</x:v>
-      </x:c>
-      <x:c r="F66" s="8" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G66" s="6" t="str">
-        <x:v>Cross-cutting</x:v>
-      </x:c>
-      <x:c r="H66" s="6" t="str">
-        <x:v>iOS</x:v>
-      </x:c>
-      <x:c r="I66" s="6" t="n">
+    <x:row r="66" ht="15.75" customHeight="1">
+      <x:c r="A66" s="6" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="B66" s="6" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="C66" s="7" t="s">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="D66" s="7" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="E66" s="7" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="F66" s="8" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G66" s="6" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="H66" s="6" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="I66" s="6">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J66" s="6" t="str">
-        <x:v>Jenny</x:v>
-      </x:c>
-      <x:c r="K66" s="6" t="str">
-        <x:v>Pass</x:v>
+      <x:c r="J66" s="6" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K66" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L66" s="6"/>
       <x:c r="M66" s="11"/>
@@ -6354,40 +7366,38 @@
       <x:c r="P66" s="7"/>
     </x:row>
     <x:row r="67" ht="15.75" customHeight="1">
-      <x:c r="A67" s="6" t="str">
-        <x:v>KS-T-066</x:v>
-      </x:c>
-      <x:c r="B67" s="6" t="str">
-        <x:v>Cross-cutting</x:v>
-      </x:c>
-      <x:c r="C67" s="7" t="str">
-        <x:v>Real-device regression — iPhone (Publish &amp; Trade)</x:v>
-      </x:c>
-      <x:c r="D67" s="7" t="str">
-        <x:v>1. Install latest pre build on physical iPhone (iOS 13+)
-2. Re-run your module's P0 cases on the device
-3. Attach evidence</x:v>
-      </x:c>
-      <x:c r="E67" s="7" t="str">
-        <x:v>All P0 cases pass on real device</x:v>
-      </x:c>
-      <x:c r="F67" s="8" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G67" s="6" t="str">
-        <x:v>Cross-cutting</x:v>
-      </x:c>
-      <x:c r="H67" s="6" t="str">
-        <x:v>iOS</x:v>
-      </x:c>
-      <x:c r="I67" s="6" t="n">
+      <x:c r="A67" s="6" t="s">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="B67" s="6" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="C67" s="7" t="s">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="D67" s="7" t="s">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="E67" s="7" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="F67" s="8" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G67" s="6" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="H67" s="6" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="I67" s="6">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J67" s="6" t="str">
-        <x:v>Jack</x:v>
-      </x:c>
-      <x:c r="K67" s="6" t="str">
-        <x:v>Not run</x:v>
+      <x:c r="J67" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K67" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L67" s="6"/>
       <x:c r="M67" s="11"/>
@@ -6396,40 +7406,38 @@
       <x:c r="P67" s="7"/>
     </x:row>
     <x:row r="68" ht="15.75" customHeight="1">
-      <x:c r="A68" s="6" t="str">
-        <x:v>KS-T-067</x:v>
-      </x:c>
-      <x:c r="B68" s="6" t="str">
-        <x:v>Cross-cutting</x:v>
-      </x:c>
-      <x:c r="C68" s="7" t="str">
-        <x:v>Real-device regression — iPhone (Discovery &amp; Safety)</x:v>
-      </x:c>
-      <x:c r="D68" s="7" t="str">
-        <x:v>1. Install latest pre build on physical iPhone (iOS 13+)
-2. Re-run your module's P0 cases on the device
-3. Attach evidence</x:v>
-      </x:c>
-      <x:c r="E68" s="7" t="str">
-        <x:v>All P0 cases pass on real device</x:v>
-      </x:c>
-      <x:c r="F68" s="8" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G68" s="6" t="str">
-        <x:v>Cross-cutting</x:v>
-      </x:c>
-      <x:c r="H68" s="6" t="str">
-        <x:v>iOS</x:v>
-      </x:c>
-      <x:c r="I68" s="6" t="n">
+      <x:c r="A68" s="6" t="s">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="B68" s="6" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="C68" s="7" t="s">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="D68" s="7" t="s">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="E68" s="7" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="F68" s="8" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G68" s="6" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="H68" s="6" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="I68" s="6">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J68" s="6" t="str">
-        <x:v>Rui</x:v>
-      </x:c>
-      <x:c r="K68" s="6" t="str">
-        <x:v>Not run</x:v>
+      <x:c r="J68" s="6" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K68" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L68" s="6"/>
       <x:c r="M68" s="11"/>
@@ -6438,40 +7446,38 @@
       <x:c r="P68" s="7"/>
     </x:row>
     <x:row r="69" ht="15.75" customHeight="1">
-      <x:c r="A69" s="6" t="str">
-        <x:v>KS-T-068</x:v>
-      </x:c>
-      <x:c r="B69" s="6" t="str">
-        <x:v>Cross-cutting</x:v>
-      </x:c>
-      <x:c r="C69" s="7" t="str">
-        <x:v>Real-device regression — iPhone (Watchlist &amp; Notifications)</x:v>
-      </x:c>
-      <x:c r="D69" s="7" t="str">
-        <x:v>1. Install latest pre build on physical iPhone (iOS 13+)
-2. Re-run your module's P0 cases on the device
-3. Attach evidence</x:v>
-      </x:c>
-      <x:c r="E69" s="7" t="str">
-        <x:v>All P0 cases pass on real device</x:v>
-      </x:c>
-      <x:c r="F69" s="8" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G69" s="6" t="str">
-        <x:v>Cross-cutting</x:v>
-      </x:c>
-      <x:c r="H69" s="6" t="str">
-        <x:v>iOS</x:v>
-      </x:c>
-      <x:c r="I69" s="6" t="n">
+      <x:c r="A69" s="6" t="s">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="B69" s="6" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="C69" s="7" t="s">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="D69" s="7" t="s">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="E69" s="7" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="F69" s="8" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G69" s="6" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="H69" s="6" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="I69" s="6">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J69" s="6" t="str">
-        <x:v>Sam</x:v>
-      </x:c>
-      <x:c r="K69" s="6" t="str">
-        <x:v>Not run</x:v>
+      <x:c r="J69" s="6" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K69" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L69" s="6"/>
       <x:c r="M69" s="11"/>
@@ -6480,40 +7486,38 @@
       <x:c r="P69" s="7"/>
     </x:row>
     <x:row r="70" ht="15.75" customHeight="1">
-      <x:c r="A70" s="6" t="str">
-        <x:v>KS-T-069</x:v>
-      </x:c>
-      <x:c r="B70" s="6" t="str">
-        <x:v>Cross-cutting</x:v>
-      </x:c>
-      <x:c r="C70" s="7" t="str">
-        <x:v>Real-device regression — Android (Chat)</x:v>
-      </x:c>
-      <x:c r="D70" s="7" t="str">
-        <x:v>1. Install latest pre build on physical Android (7.0+)
-2. Re-run your module's P0 cases on the device
-3. Attach evidence</x:v>
-      </x:c>
-      <x:c r="E70" s="7" t="str">
-        <x:v>All P0 cases pass on real device</x:v>
-      </x:c>
-      <x:c r="F70" s="8" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G70" s="6" t="str">
-        <x:v>Cross-cutting</x:v>
-      </x:c>
-      <x:c r="H70" s="6" t="str">
-        <x:v>Android</x:v>
-      </x:c>
-      <x:c r="I70" s="6" t="n">
+      <x:c r="A70" s="6" t="s">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="B70" s="6" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="C70" s="7" t="s">
+        <x:v>424</x:v>
+      </x:c>
+      <x:c r="D70" s="7" t="s">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="E70" s="7" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="F70" s="8" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G70" s="6" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="H70" s="6" t="s">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="I70" s="6">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J70" s="6" t="str">
-        <x:v>Jaeger</x:v>
-      </x:c>
-      <x:c r="K70" s="6" t="str">
-        <x:v>Not run</x:v>
+      <x:c r="J70" s="6" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K70" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L70" s="6"/>
       <x:c r="M70" s="11"/>
@@ -6521,40 +7525,39 @@
       <x:c r="O70" s="6"/>
       <x:c r="P70" s="7"/>
     </x:row>
-    <x:row r="71" ht="15.75" hidden="1" customHeight="1">
-      <x:c r="A71" s="6" t="str">
-        <x:v>KS-T-070</x:v>
-      </x:c>
-      <x:c r="B71" s="6" t="str">
-        <x:v>Web</x:v>
-      </x:c>
-      <x:c r="C71" s="7" t="str">
-        <x:v>Web app smoke</x:v>
-      </x:c>
-      <x:c r="D71" s="7" t="str">
-        <x:v>1. Open web client in Chrome
-2. Log in, browse, open an item</x:v>
-      </x:c>
-      <x:c r="E71" s="7" t="str">
-        <x:v>Core flows work; no console errors blocking use</x:v>
-      </x:c>
-      <x:c r="F71" s="6" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="G71" s="6" t="str">
-        <x:v>Functional</x:v>
-      </x:c>
-      <x:c r="H71" s="6" t="str">
-        <x:v>Web</x:v>
-      </x:c>
-      <x:c r="I71" s="6" t="n">
+    <x:row r="71" ht="15.75" customHeight="1">
+      <x:c r="A71" s="6" t="s">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="B71" s="6" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="C71" s="7" t="s">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="D71" s="7" t="s">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="E71" s="7" t="s">
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="F71" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G71" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H71" s="6" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="I71" s="6">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J71" s="6" t="str">
-        <x:v>Rui</x:v>
-      </x:c>
-      <x:c r="K71" s="6" t="str">
-        <x:v>Pass</x:v>
+      <x:c r="J71" s="6" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K71" s="6" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L71" s="6"/>
       <x:c r="M71" s="11"/>
@@ -7535,25 +8538,25 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>127</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
         <x:v>115</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>128</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>129</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
-        <x:v>130</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="G1" s="2" t="s">
-        <x:v>131</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>132</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="I1" s="2" t="s">
         <x:v>15</x:v>
@@ -7567,22 +8570,22 @@
     </x:row>
     <x:row r="2" ht="48">
       <x:c r="A2" s="7" t="s">
-        <x:v>133</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="B2" s="7" t="s">
-        <x:v>134</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C2" s="7" t="s">
-        <x:v>135</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D2" s="7" t="s">
-        <x:v>136</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="E2" s="7" t="s">
-        <x:v>137</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="F2" s="7" t="s">
-        <x:v>138</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="G2" s="7" t="s">
         <x:v>41</x:v>
@@ -7591,31 +8594,31 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="I2" s="7" t="s">
-        <x:v>139</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="J2" s="7"/>
       <x:c r="K2" s="7" t="s">
-        <x:v>140</x:v>
+        <x:v>443</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="64">
       <x:c r="A3" s="12" t="s">
-        <x:v>141</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B3" s="12" t="s">
-        <x:v>142</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
-        <x:v>143</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D3" s="12" t="s">
-        <x:v>144</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="E3" s="12" t="s">
-        <x:v>145</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>138</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="G3" s="12" t="s">
         <x:v>41</x:v>
@@ -7624,33 +8627,33 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="I3" s="13" t="s">
-        <x:v>146</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="J3" s="14">
         <x:v>46281</x:v>
       </x:c>
       <x:c r="K3" s="12" t="s">
-        <x:v>147</x:v>
+        <x:v>447</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48">
       <x:c r="A4" s="12" t="s">
-        <x:v>148</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B4" s="12" t="s">
-        <x:v>149</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C4" s="12" t="s">
-        <x:v>143</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D4" s="12" t="s">
-        <x:v>150</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="E4" s="12" t="s">
-        <x:v>151</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="F4" s="13" t="s">
-        <x:v>152</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="G4" s="12" t="s">
         <x:v>41</x:v>
@@ -7659,13 +8662,13 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="I4" s="13" t="s">
-        <x:v>146</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="J4" s="14">
         <x:v>46281</x:v>
       </x:c>
       <x:c r="K4" s="12" t="s">
-        <x:v>153</x:v>
+        <x:v>451</x:v>
       </x:c>
     </x:row>
     <x:row r="5">

--- a/docs/testing-strategy/kiwishare-release-test-results-v0.2.xlsx
+++ b/docs/testing-strategy/kiwishare-release-test-results-v0.2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R7f1f8eec109945ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data &amp; Setup" sheetId="2" r:id="Rfd4bcea8049d437b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="3" r:id="R783d1785f4bd4bb9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Log" sheetId="4" r:id="R9b4c2cd50c5c4b0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R18539823bc4242f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Data &amp; Setup" sheetId="2" r:id="Raeb13060ad444321"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="3" r:id="R990be6f5c41f4b65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Log" sheetId="4" r:id="Ra0236b45f0724db5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1411,7 +1411,7 @@
     <x:t xml:space="preserve">S3 Minor</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Open</x:t>
+    <x:t xml:space="preserve">Closed</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Replace with friendly message</x:t>
@@ -1421,9 +1421,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Register with a 32-character nickname, then edit the nickname in Profile and enter a 33rd character.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Closed</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Fixed in PR #309 by applying the 2-30 character limit consistently; the linked test case now passes.</x:t>
@@ -1512,13 +1509,6 @@
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
       <x:color rgb="FF17352E"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
@@ -1535,6 +1525,7 @@
       <x:sz val="11"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+      <x:family val="2"/>
       <x:scheme val="minor"/>
     </x:font>
     <x:font>
@@ -1542,10 +1533,18 @@
       <x:sz val="11"/>
       <x:color rgb="FF17352E"/>
       <x:name val="Calibri"/>
+      <x:family val="2"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
       <x:scheme val="minor"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -1555,6 +1554,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF2E5E4E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0B6B53"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -1595,7 +1599,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1616,9 +1620,6 @@
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
@@ -1634,7 +1635,7 @@
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1643,11 +1644,23 @@
     <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
@@ -1655,32 +1668,13 @@
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -2248,196 +2242,196 @@
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
-      <x:c r="A47" s="22" t="str">
+      <x:c r="A47" s="25" t="str">
         <x:v>8. Consolidated Test Results</x:v>
       </x:c>
-      <x:c r="B47" s="22" t="str">
+      <x:c r="B47" s="25" t="str">
         <x:v>As of 2026-10-02</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
-      <x:c r="A48" s="23" t="str">
+      <x:c r="A48" s="26" t="str">
         <x:v>Total test cases</x:v>
       </x:c>
-      <x:c r="B48" s="24" t="n">
+      <x:c r="B48" s="27" t="n">
         <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
-      <x:c r="A49" s="23" t="str">
+      <x:c r="A49" s="26" t="str">
         <x:v>Executed</x:v>
       </x:c>
-      <x:c r="B49" s="24" t="n">
+      <x:c r="B49" s="27" t="n">
         <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
-      <x:c r="A50" s="23" t="str">
+      <x:c r="A50" s="26" t="str">
         <x:v>Passed</x:v>
       </x:c>
-      <x:c r="B50" s="24" t="n">
+      <x:c r="B50" s="27" t="n">
         <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
-      <x:c r="A51" s="23" t="str">
+      <x:c r="A51" s="26" t="str">
         <x:v>Failed</x:v>
       </x:c>
-      <x:c r="B51" s="24" t="n">
+      <x:c r="B51" s="27" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
-      <x:c r="A52" s="23" t="str">
+      <x:c r="A52" s="26" t="str">
         <x:v>Blocked</x:v>
       </x:c>
-      <x:c r="B52" s="24" t="n">
+      <x:c r="B52" s="27" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
-      <x:c r="A53" s="23" t="str">
+      <x:c r="A53" s="26" t="str">
         <x:v>Execution rate</x:v>
       </x:c>
-      <x:c r="B53" s="21" t="n">
+      <x:c r="B53" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
-      <x:c r="A54" s="23" t="str">
+      <x:c r="A54" s="26" t="str">
         <x:v>Pass rate (executed cases)</x:v>
       </x:c>
-      <x:c r="B54" s="21" t="n">
+      <x:c r="B54" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A55" s="23" t="str">
+      <x:c r="A55" s="26" t="str">
         <x:v>Latest update</x:v>
       </x:c>
-      <x:c r="B55" s="24" t="str">
+      <x:c r="B55" s="27" t="str">
         <x:v>All 70 planned cases were executed and currently pass after confirmation and retesting with the assigned team members.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A56" s="23" t="str">
-        <x:v>Evidence limitation</x:v>
-      </x:c>
-      <x:c r="B56" s="24" t="str">
-        <x:v>44 executed cases still need complete tester/date metadata or anonymised evidence. Historical failures remain noted for regression traceability.</x:v>
+      <x:c r="A56" s="26" t="str">
+        <x:v>Evidence status</x:v>
+      </x:c>
+      <x:c r="B56" s="27" t="str">
+        <x:v>Tester and date metadata are complete for all 70 executed cases. Retain or add anonymised evidence links where available; historical failures remain noted for regression traceability.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="15.75" customHeight="1"/>
     <x:row r="58" ht="15" customHeight="1">
-      <x:c r="A58" s="15" t="s">
+      <x:c r="A58" s="14" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="B58" s="15" t="s">
+      <x:c r="B58" s="14" t="s">
         <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="15" customHeight="1">
-      <x:c r="A59" s="16" t="s">
+      <x:c r="A59" s="15" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="B59" s="17" t="s">
+      <x:c r="B59" s="16" t="s">
         <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15" customHeight="1">
-      <x:c r="A60" s="16" t="s">
+      <x:c r="A60" s="15" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="B60" s="17" t="s">
+      <x:c r="B60" s="16" t="s">
         <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="15" customHeight="1">
-      <x:c r="A61" s="16" t="s">
+      <x:c r="A61" s="15" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B61" s="17" t="s">
+      <x:c r="B61" s="16" t="s">
         <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="15" customHeight="1">
-      <x:c r="A62" s="16" t="s">
+      <x:c r="A62" s="15" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B62" s="17" t="s">
+      <x:c r="B62" s="16" t="s">
         <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="15.75" customHeight="1"/>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
-      <x:c r="A64" s="33" t="str">
+      <x:c r="A64" s="28" t="str">
         <x:v>10. Multi-round QA &amp; Defect Evidence</x:v>
       </x:c>
-      <x:c r="B64" s="33" t="str">
+      <x:c r="B64" s="28" t="str">
         <x:v>GitHub issues created from 2026-09-19</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
-      <x:c r="A65" s="34" t="str">
+      <x:c r="A65" s="26" t="str">
         <x:v>Documented QA rounds</x:v>
       </x:c>
-      <x:c r="B65" s="24" t="str">
+      <x:c r="B65" s="27" t="str">
         <x:v>4 rounds: #279 (09/19), #318 (09/22), #336 (09/23), #355 (09/24)</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
-      <x:c r="A66" s="34" t="str">
+      <x:c r="A66" s="26" t="str">
         <x:v>Individual bug-labelled issues</x:v>
       </x:c>
-      <x:c r="B66" s="24" t="n">
+      <x:c r="B66" s="27" t="n">
         <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
-      <x:c r="A67" s="34" t="str">
+      <x:c r="A67" s="26" t="str">
         <x:v>Closed bug-labelled issues</x:v>
       </x:c>
-      <x:c r="B67" s="24" t="n">
+      <x:c r="B67" s="27" t="n">
         <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
-      <x:c r="A68" s="34" t="str">
+      <x:c r="A68" s="26" t="str">
         <x:v>Open bug-labelled issues</x:v>
       </x:c>
-      <x:c r="B68" s="24" t="n">
+      <x:c r="B68" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
-      <x:c r="A69" s="34" t="str">
+      <x:c r="A69" s="26" t="str">
         <x:v>Recorded closure rate</x:v>
       </x:c>
-      <x:c r="B69" s="21" t="n">
+      <x:c r="B69" s="24" t="n">
         <x:v>0.933</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
-      <x:c r="A70" s="34" t="str">
+      <x:c r="A70" s="26" t="str">
         <x:v>Median resolution time</x:v>
       </x:c>
-      <x:c r="B70" s="24" t="str">
+      <x:c r="B70" s="27" t="str">
         <x:v>Approximately 3.42 days</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
-      <x:c r="A71" s="34" t="str">
+      <x:c r="A71" s="26" t="str">
         <x:v>Priority distribution</x:v>
       </x:c>
-      <x:c r="B71" s="24" t="str">
+      <x:c r="B71" s="27" t="str">
         <x:v>21 Urgent; 12 High; 9 Medium; 3 Low</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A72" s="34" t="str">
+      <x:c r="A72" s="26" t="str">
         <x:v>Classification note</x:v>
       </x:c>
-      <x:c r="B72" s="24" t="str">
+      <x:c r="B72" s="27" t="str">
         <x:v>The 3 open bug-labelled items concern presentation preparation, security evidence review, and dependency maintenance rather than confirmed product defects.</x:v>
       </x:c>
     </x:row>
@@ -4525,7 +4519,7 @@
     <x:col min="9" max="9" width="8" customWidth="1"/>
     <x:col min="10" max="10" width="9" customWidth="1"/>
     <x:col min="11" max="11" width="10" customWidth="1"/>
-    <x:col min="12" max="12" width="24.5" customWidth="1"/>
+    <x:col min="12" max="12" width="24.5" style="23" customWidth="1"/>
     <x:col min="13" max="13" width="11" customWidth="1"/>
     <x:col min="14" max="14" width="16" customWidth="1"/>
     <x:col min="15" max="15" width="10" customWidth="1"/>
@@ -4567,7 +4561,7 @@
       <x:c r="K1" s="2" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="L1" s="2" t="s">
+      <x:c r="L1" s="21" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="M1" s="2" t="s">
@@ -4617,10 +4611,10 @@
       <x:c r="K2" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L2" s="6" t="s">
+      <x:c r="L2" s="22" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="M2" s="11">
+      <x:c r="M2" s="10">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N2" s="6"/>
@@ -4663,10 +4657,10 @@
       <x:c r="K3" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L3" s="6" t="s">
+      <x:c r="L3" s="22" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="M3" s="11">
+      <x:c r="M3" s="10">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N3" s="6"/>
@@ -4709,10 +4703,10 @@
       <x:c r="K4" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L4" s="6" t="s">
+      <x:c r="L4" s="22" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="M4" s="11">
+      <x:c r="M4" s="10">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N4" s="6"/>
@@ -4755,10 +4749,10 @@
       <x:c r="K5" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L5" s="6" t="s">
+      <x:c r="L5" s="22" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="M5" s="11">
+      <x:c r="M5" s="10">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N5" s="6"/>
@@ -4801,10 +4795,10 @@
       <x:c r="K6" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L6" s="10" t="s">
+      <x:c r="L6" s="22" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="M6" s="11">
+      <x:c r="M6" s="10">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N6" s="6"/>
@@ -4847,10 +4841,12 @@
       <x:c r="K7" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="22" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="M7" s="11"/>
+      <x:c r="M7" s="10">
+        <x:v>46285</x:v>
+      </x:c>
       <x:c r="N7" s="6"/>
       <x:c r="O7" s="6"/>
       <x:c r="P7" s="7"/>
@@ -4889,10 +4885,12 @@
       <x:c r="K8" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L8" s="10" t="s">
+      <x:c r="L8" s="22" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="M8" s="11"/>
+      <x:c r="M8" s="10">
+        <x:v>46285</x:v>
+      </x:c>
       <x:c r="N8" s="6"/>
       <x:c r="O8" s="6"/>
       <x:c r="P8" s="7"/>
@@ -4931,10 +4929,12 @@
       <x:c r="K9" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L9" s="6" t="s">
+      <x:c r="L9" s="22" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="M9" s="11"/>
+      <x:c r="M9" s="10">
+        <x:v>46285</x:v>
+      </x:c>
       <x:c r="N9" s="6"/>
       <x:c r="O9" s="6" t="s">
         <x:v>168</x:v>
@@ -4977,10 +4977,12 @@
       <x:c r="K10" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L10" s="6" t="s">
+      <x:c r="L10" s="22" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="M10" s="11"/>
+      <x:c r="M10" s="10">
+        <x:v>46285</x:v>
+      </x:c>
       <x:c r="N10" s="6"/>
       <x:c r="O10" s="6"/>
       <x:c r="P10" s="7"/>
@@ -5019,10 +5021,10 @@
       <x:c r="K11" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L11" s="6" t="s">
+      <x:c r="L11" s="22" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="M11" s="11">
+      <x:c r="M11" s="10">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N11" s="6"/>
@@ -5065,10 +5067,12 @@
       <x:c r="K12" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L12" s="6" t="s">
+      <x:c r="L12" s="22" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="M12" s="11"/>
+      <x:c r="M12" s="10">
+        <x:v>46285</x:v>
+      </x:c>
       <x:c r="N12" s="6"/>
       <x:c r="O12" s="6"/>
       <x:c r="P12" s="7"/>
@@ -5107,10 +5111,10 @@
       <x:c r="K13" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L13" s="6" t="s">
+      <x:c r="L13" s="22" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="M13" s="11">
+      <x:c r="M13" s="10">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N13" s="6"/>
@@ -5153,10 +5157,12 @@
       <x:c r="K14" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L14" s="9" t="s">
+      <x:c r="L14" s="23" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="M14" s="11"/>
+      <x:c r="M14" s="10">
+        <x:v>46285</x:v>
+      </x:c>
       <x:c r="N14" s="6"/>
       <x:c r="O14" s="6" t="s">
         <x:v>191</x:v>
@@ -5199,10 +5205,10 @@
       <x:c r="K15" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L15" s="6" t="s">
+      <x:c r="L15" s="22" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="M15" s="11">
+      <x:c r="M15" s="10">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N15" s="6"/>
@@ -5245,10 +5251,10 @@
       <x:c r="K16" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L16" s="6" t="s">
+      <x:c r="L16" s="22" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="M16" s="11">
+      <x:c r="M16" s="10">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N16" s="6"/>
@@ -5291,10 +5297,10 @@
       <x:c r="K17" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L17" s="6" t="s">
+      <x:c r="L17" s="22" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="M17" s="11">
+      <x:c r="M17" s="10">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N17" s="6"/>
@@ -5337,10 +5343,10 @@
       <x:c r="K18" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L18" s="6" t="s">
+      <x:c r="L18" s="22" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="M18" s="11">
+      <x:c r="M18" s="10">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N18" s="6"/>
@@ -5362,7 +5368,7 @@
       <x:c r="D19" s="7" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="E19" s="19" t="s">
+      <x:c r="E19" s="18" t="s">
         <x:v>216</x:v>
       </x:c>
       <x:c r="F19" s="8" t="s">
@@ -5383,10 +5389,12 @@
       <x:c r="K19" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L19" s="20" t="s">
+      <x:c r="L19" s="22" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="M19" s="11"/>
+      <x:c r="M19" s="10">
+        <x:v>46294</x:v>
+      </x:c>
       <x:c r="N19" s="6"/>
       <x:c r="O19" s="6"/>
       <x:c r="P19" s="7"/>
@@ -5425,8 +5433,12 @@
       <x:c r="K20" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L20" s="6"/>
-      <x:c r="M20" s="11"/>
+      <x:c r="L20" s="22" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="M20" s="10">
+        <x:v>46284</x:v>
+      </x:c>
       <x:c r="N20" s="6"/>
       <x:c r="O20" s="6"/>
       <x:c r="P20" s="7"/>
@@ -5465,10 +5477,10 @@
       <x:c r="K21" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L21" s="6" t="s">
+      <x:c r="L21" s="22" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="M21" s="11">
+      <x:c r="M21" s="10">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N21" s="6"/>
@@ -5511,10 +5523,10 @@
       <x:c r="K22" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L22" s="6" t="s">
+      <x:c r="L22" s="22" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="M22" s="11">
+      <x:c r="M22" s="10">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N22" s="6"/>
@@ -5533,7 +5545,7 @@
       <x:c r="C23" s="7" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="D23" s="19" t="s">
+      <x:c r="D23" s="18" t="s">
         <x:v>232</x:v>
       </x:c>
       <x:c r="E23" s="7" t="s">
@@ -5557,10 +5569,12 @@
       <x:c r="K23" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L23" s="20" t="s">
+      <x:c r="L23" s="22" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="M23" s="11"/>
+      <x:c r="M23" s="10">
+        <x:v>46294</x:v>
+      </x:c>
       <x:c r="N23" s="6"/>
       <x:c r="O23" s="6"/>
       <x:c r="P23" s="7"/>
@@ -5599,10 +5613,10 @@
       <x:c r="K24" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L24" s="6" t="s">
+      <x:c r="L24" s="22" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="M24" s="11">
+      <x:c r="M24" s="10">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N24" s="6"/>
@@ -5645,10 +5659,10 @@
       <x:c r="K25" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L25" s="6" t="s">
+      <x:c r="L25" s="22" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="M25" s="11">
+      <x:c r="M25" s="10">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N25" s="6"/>
@@ -5691,10 +5705,10 @@
       <x:c r="K26" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L26" s="6" t="s">
+      <x:c r="L26" s="22" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="M26" s="11">
+      <x:c r="M26" s="10">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N26" s="6"/>
@@ -5737,10 +5751,10 @@
       <x:c r="K27" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L27" s="6" t="s">
+      <x:c r="L27" s="22" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="M27" s="11">
+      <x:c r="M27" s="10">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N27" s="6"/>
@@ -5783,10 +5797,12 @@
       <x:c r="K28" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L28" s="20" t="s">
+      <x:c r="L28" s="22" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="M28" s="11"/>
+      <x:c r="M28" s="10">
+        <x:v>46297</x:v>
+      </x:c>
       <x:c r="N28" s="6"/>
       <x:c r="O28" s="6"/>
       <x:c r="P28" s="7"/>
@@ -5825,8 +5841,12 @@
       <x:c r="K29" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L29" s="6"/>
-      <x:c r="M29" s="11"/>
+      <x:c r="L29" s="22" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M29" s="10">
+        <x:v>46284</x:v>
+      </x:c>
       <x:c r="N29" s="6"/>
       <x:c r="O29" s="6"/>
       <x:c r="P29" s="7"/>
@@ -5865,8 +5885,12 @@
       <x:c r="K30" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L30" s="6"/>
-      <x:c r="M30" s="11"/>
+      <x:c r="L30" s="22" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M30" s="10">
+        <x:v>46284</x:v>
+      </x:c>
       <x:c r="N30" s="6"/>
       <x:c r="O30" s="6"/>
       <x:c r="P30" s="7"/>
@@ -5905,10 +5929,10 @@
       <x:c r="K31" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L31" s="6" t="s">
+      <x:c r="L31" s="22" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="M31" s="11">
+      <x:c r="M31" s="10">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N31" s="6"/>
@@ -5951,10 +5975,10 @@
       <x:c r="K32" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L32" s="6" t="s">
+      <x:c r="L32" s="22" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="M32" s="11">
+      <x:c r="M32" s="10">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N32" s="6"/>
@@ -5997,10 +6021,10 @@
       <x:c r="K33" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L33" s="6" t="s">
+      <x:c r="L33" s="22" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="M33" s="11">
+      <x:c r="M33" s="10">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N33" s="6"/>
@@ -6043,8 +6067,12 @@
       <x:c r="K34" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L34" s="6"/>
-      <x:c r="M34" s="11"/>
+      <x:c r="L34" s="22" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M34" s="10">
+        <x:v>46284</x:v>
+      </x:c>
       <x:c r="N34" s="6"/>
       <x:c r="O34" s="6"/>
       <x:c r="P34" s="7"/>
@@ -6083,8 +6111,12 @@
       <x:c r="K35" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L35" s="6"/>
-      <x:c r="M35" s="11"/>
+      <x:c r="L35" s="22" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M35" s="10">
+        <x:v>46284</x:v>
+      </x:c>
       <x:c r="N35" s="6"/>
       <x:c r="O35" s="6"/>
       <x:c r="P35" s="7"/>
@@ -6099,7 +6131,7 @@
       <x:c r="C36" s="7" t="s">
         <x:v>288</x:v>
       </x:c>
-      <x:c r="D36" s="19" t="s">
+      <x:c r="D36" s="18" t="s">
         <x:v>289</x:v>
       </x:c>
       <x:c r="E36" s="7" t="s">
@@ -6123,8 +6155,12 @@
       <x:c r="K36" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L36" s="6"/>
-      <x:c r="M36" s="11"/>
+      <x:c r="L36" s="22" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M36" s="10">
+        <x:v>46284</x:v>
+      </x:c>
       <x:c r="N36" s="6"/>
       <x:c r="O36" s="6"/>
       <x:c r="P36" s="7"/>
@@ -6163,10 +6199,10 @@
       <x:c r="K37" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L37" s="6" t="s">
+      <x:c r="L37" s="22" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="M37" s="11">
+      <x:c r="M37" s="10">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N37" s="6"/>
@@ -6209,8 +6245,12 @@
       <x:c r="K38" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L38" s="6"/>
-      <x:c r="M38" s="11"/>
+      <x:c r="L38" s="6" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="M38" s="10">
+        <x:v>46294</x:v>
+      </x:c>
       <x:c r="N38" s="6"/>
       <x:c r="O38" s="6"/>
       <x:c r="P38" s="7"/>
@@ -6249,10 +6289,10 @@
       <x:c r="K39" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L39" s="6" t="s">
+      <x:c r="L39" s="22" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="M39" s="11">
+      <x:c r="M39" s="10">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N39" s="6"/>
@@ -6295,8 +6335,12 @@
       <x:c r="K40" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L40" s="6"/>
-      <x:c r="M40" s="11"/>
+      <x:c r="L40" s="6" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="M40" s="10">
+        <x:v>46294</x:v>
+      </x:c>
       <x:c r="N40" s="6"/>
       <x:c r="O40" s="6"/>
       <x:c r="P40" s="7"/>
@@ -6335,8 +6379,12 @@
       <x:c r="K41" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L41" s="6"/>
-      <x:c r="M41" s="11"/>
+      <x:c r="L41" s="6" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="M41" s="10">
+        <x:v>46294</x:v>
+      </x:c>
       <x:c r="N41" s="6"/>
       <x:c r="O41" s="6"/>
       <x:c r="P41" s="7"/>
@@ -6375,8 +6423,12 @@
       <x:c r="K42" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L42" s="6"/>
-      <x:c r="M42" s="11"/>
+      <x:c r="L42" s="6" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="M42" s="10">
+        <x:v>46294</x:v>
+      </x:c>
       <x:c r="N42" s="6"/>
       <x:c r="O42" s="6"/>
       <x:c r="P42" s="7"/>
@@ -6391,7 +6443,7 @@
       <x:c r="C43" s="7" t="s">
         <x:v>317</x:v>
       </x:c>
-      <x:c r="D43" s="19" t="s">
+      <x:c r="D43" s="18" t="s">
         <x:v>318</x:v>
       </x:c>
       <x:c r="E43" s="7" t="s">
@@ -6415,8 +6467,12 @@
       <x:c r="K43" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L43" s="6"/>
-      <x:c r="M43" s="11"/>
+      <x:c r="L43" s="6" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="M43" s="10">
+        <x:v>46294</x:v>
+      </x:c>
       <x:c r="N43" s="6"/>
       <x:c r="O43" s="6"/>
       <x:c r="P43" s="7"/>
@@ -6455,8 +6511,12 @@
       <x:c r="K44" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L44" s="6"/>
-      <x:c r="M44" s="11"/>
+      <x:c r="L44" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="M44" s="10">
+        <x:v>46294</x:v>
+      </x:c>
       <x:c r="N44" s="6"/>
       <x:c r="O44" s="6"/>
       <x:c r="P44" s="7"/>
@@ -6495,8 +6555,12 @@
       <x:c r="K45" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L45" s="6"/>
-      <x:c r="M45" s="11"/>
+      <x:c r="L45" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="M45" s="10">
+        <x:v>46294</x:v>
+      </x:c>
       <x:c r="N45" s="6"/>
       <x:c r="O45" s="6"/>
       <x:c r="P45" s="7"/>
@@ -6535,8 +6599,12 @@
       <x:c r="K46" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L46" s="6"/>
-      <x:c r="M46" s="11"/>
+      <x:c r="L46" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="M46" s="10">
+        <x:v>46294</x:v>
+      </x:c>
       <x:c r="N46" s="6"/>
       <x:c r="O46" s="6"/>
       <x:c r="P46" s="7"/>
@@ -6575,8 +6643,12 @@
       <x:c r="K47" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L47" s="20"/>
-      <x:c r="M47" s="11"/>
+      <x:c r="L47" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="M47" s="10">
+        <x:v>46294</x:v>
+      </x:c>
       <x:c r="N47" s="6"/>
       <x:c r="O47" s="6"/>
       <x:c r="P47" s="7"/>
@@ -6615,10 +6687,10 @@
       <x:c r="K48" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L48" s="6" t="s">
+      <x:c r="L48" s="22" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="M48" s="11">
+      <x:c r="M48" s="10">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N48" s="6"/>
@@ -6661,10 +6733,10 @@
       <x:c r="K49" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L49" s="6" t="s">
+      <x:c r="L49" s="22" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="M49" s="11">
+      <x:c r="M49" s="10">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N49" s="6"/>
@@ -6707,10 +6779,10 @@
       <x:c r="K50" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L50" s="6" t="s">
+      <x:c r="L50" s="22" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="M50" s="11">
+      <x:c r="M50" s="10">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N50" s="6"/>
@@ -6753,8 +6825,12 @@
       <x:c r="K51" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L51" s="6"/>
-      <x:c r="M51" s="11"/>
+      <x:c r="L51" s="22" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M51" s="10">
+        <x:v>46284</x:v>
+      </x:c>
       <x:c r="N51" s="6"/>
       <x:c r="O51" s="6"/>
       <x:c r="P51" s="7"/>
@@ -6793,8 +6869,12 @@
       <x:c r="K52" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L52" s="6"/>
-      <x:c r="M52" s="11"/>
+      <x:c r="L52" s="22" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M52" s="10">
+        <x:v>46284</x:v>
+      </x:c>
       <x:c r="N52" s="6"/>
       <x:c r="O52" s="6"/>
       <x:c r="P52" s="7"/>
@@ -6833,8 +6913,12 @@
       <x:c r="K53" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L53" s="6"/>
-      <x:c r="M53" s="11"/>
+      <x:c r="L53" s="22" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M53" s="10">
+        <x:v>46284</x:v>
+      </x:c>
       <x:c r="N53" s="6"/>
       <x:c r="O53" s="6"/>
       <x:c r="P53" s="7"/>
@@ -6873,8 +6957,12 @@
       <x:c r="K54" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L54" s="6"/>
-      <x:c r="M54" s="11"/>
+      <x:c r="L54" s="22" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M54" s="10">
+        <x:v>46284</x:v>
+      </x:c>
       <x:c r="N54" s="6"/>
       <x:c r="O54" s="6"/>
       <x:c r="P54" s="7"/>
@@ -6889,7 +6977,7 @@
       <x:c r="C55" s="7" t="s">
         <x:v>368</x:v>
       </x:c>
-      <x:c r="D55" s="19" t="s">
+      <x:c r="D55" s="18" t="s">
         <x:v>369</x:v>
       </x:c>
       <x:c r="E55" s="7" t="s">
@@ -6913,8 +7001,12 @@
       <x:c r="K55" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L55" s="6"/>
-      <x:c r="M55" s="11"/>
+      <x:c r="L55" s="22" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M55" s="10">
+        <x:v>46284</x:v>
+      </x:c>
       <x:c r="N55" s="6"/>
       <x:c r="O55" s="6"/>
       <x:c r="P55" s="7"/>
@@ -6929,7 +7021,7 @@
       <x:c r="C56" s="7" t="s">
         <x:v>372</x:v>
       </x:c>
-      <x:c r="D56" s="19" t="s">
+      <x:c r="D56" s="18" t="s">
         <x:v>373</x:v>
       </x:c>
       <x:c r="E56" s="7" t="s">
@@ -6953,8 +7045,12 @@
       <x:c r="K56" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L56" s="6"/>
-      <x:c r="M56" s="11"/>
+      <x:c r="L56" s="22" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M56" s="10">
+        <x:v>46284</x:v>
+      </x:c>
       <x:c r="N56" s="6"/>
       <x:c r="O56" s="6"/>
       <x:c r="P56" s="7"/>
@@ -6969,7 +7065,7 @@
       <x:c r="C57" s="7" t="s">
         <x:v>376</x:v>
       </x:c>
-      <x:c r="D57" s="19" t="s">
+      <x:c r="D57" s="18" t="s">
         <x:v>377</x:v>
       </x:c>
       <x:c r="E57" s="7" t="s">
@@ -6993,8 +7089,12 @@
       <x:c r="K57" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L57" s="6"/>
-      <x:c r="M57" s="11"/>
+      <x:c r="L57" s="22" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M57" s="10">
+        <x:v>46284</x:v>
+      </x:c>
       <x:c r="N57" s="6"/>
       <x:c r="O57" s="6"/>
       <x:c r="P57" s="7"/>
@@ -7009,7 +7109,7 @@
       <x:c r="C58" s="7" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="D58" s="19" t="s">
+      <x:c r="D58" s="18" t="s">
         <x:v>381</x:v>
       </x:c>
       <x:c r="E58" s="7" t="s">
@@ -7033,8 +7133,12 @@
       <x:c r="K58" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L58" s="6"/>
-      <x:c r="M58" s="11"/>
+      <x:c r="L58" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="M58" s="10">
+        <x:v>46294</x:v>
+      </x:c>
       <x:c r="N58" s="6"/>
       <x:c r="O58" s="6"/>
       <x:c r="P58" s="7"/>
@@ -7073,8 +7177,12 @@
       <x:c r="K59" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L59" s="6"/>
-      <x:c r="M59" s="11"/>
+      <x:c r="L59" s="22" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M59" s="10">
+        <x:v>46294</x:v>
+      </x:c>
       <x:c r="N59" s="6"/>
       <x:c r="O59" s="6"/>
       <x:c r="P59" s="7"/>
@@ -7113,8 +7221,12 @@
       <x:c r="K60" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L60" s="6"/>
-      <x:c r="M60" s="11"/>
+      <x:c r="L60" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="M60" s="10">
+        <x:v>46294</x:v>
+      </x:c>
       <x:c r="N60" s="6"/>
       <x:c r="O60" s="6"/>
       <x:c r="P60" s="7"/>
@@ -7153,10 +7265,10 @@
       <x:c r="K61" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L61" s="6" t="s">
+      <x:c r="L61" s="22" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="M61" s="11">
+      <x:c r="M61" s="10">
         <x:v>46284</x:v>
       </x:c>
       <x:c r="N61" s="6"/>
@@ -7199,8 +7311,12 @@
       <x:c r="K62" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L62" s="6"/>
-      <x:c r="M62" s="11"/>
+      <x:c r="L62" s="6" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="M62" s="10">
+        <x:v>46294</x:v>
+      </x:c>
       <x:c r="N62" s="6"/>
       <x:c r="O62" s="6"/>
       <x:c r="P62" s="7"/>
@@ -7239,8 +7355,12 @@
       <x:c r="K63" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L63" s="6"/>
-      <x:c r="M63" s="11"/>
+      <x:c r="L63" s="22" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M63" s="10">
+        <x:v>46284</x:v>
+      </x:c>
       <x:c r="N63" s="6"/>
       <x:c r="O63" s="6"/>
       <x:c r="P63" s="7"/>
@@ -7255,7 +7375,7 @@
       <x:c r="C64" s="7" t="s">
         <x:v>404</x:v>
       </x:c>
-      <x:c r="D64" s="19" t="s">
+      <x:c r="D64" s="18" t="s">
         <x:v>405</x:v>
       </x:c>
       <x:c r="E64" s="7" t="s">
@@ -7279,8 +7399,12 @@
       <x:c r="K64" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L64" s="6"/>
-      <x:c r="M64" s="11"/>
+      <x:c r="L64" s="22" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M64" s="10">
+        <x:v>46284</x:v>
+      </x:c>
       <x:c r="N64" s="6"/>
       <x:c r="O64" s="6"/>
       <x:c r="P64" s="7"/>
@@ -7319,8 +7443,12 @@
       <x:c r="K65" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L65" s="6"/>
-      <x:c r="M65" s="11"/>
+      <x:c r="L65" s="22" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M65" s="10">
+        <x:v>46284</x:v>
+      </x:c>
       <x:c r="N65" s="6"/>
       <x:c r="O65" s="6"/>
       <x:c r="P65" s="7"/>
@@ -7359,8 +7487,12 @@
       <x:c r="K66" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L66" s="6"/>
-      <x:c r="M66" s="11"/>
+      <x:c r="L66" s="22" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M66" s="10">
+        <x:v>46294</x:v>
+      </x:c>
       <x:c r="N66" s="6"/>
       <x:c r="O66" s="6"/>
       <x:c r="P66" s="7"/>
@@ -7399,8 +7531,12 @@
       <x:c r="K67" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L67" s="6"/>
-      <x:c r="M67" s="11"/>
+      <x:c r="L67" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="M67" s="10">
+        <x:v>46294</x:v>
+      </x:c>
       <x:c r="N67" s="6"/>
       <x:c r="O67" s="6"/>
       <x:c r="P67" s="7"/>
@@ -7439,8 +7575,12 @@
       <x:c r="K68" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L68" s="6"/>
-      <x:c r="M68" s="11"/>
+      <x:c r="L68" s="22" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M68" s="10">
+        <x:v>46284</x:v>
+      </x:c>
       <x:c r="N68" s="6"/>
       <x:c r="O68" s="6"/>
       <x:c r="P68" s="7"/>
@@ -7479,8 +7619,12 @@
       <x:c r="K69" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L69" s="6"/>
-      <x:c r="M69" s="11"/>
+      <x:c r="L69" s="22" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M69" s="10">
+        <x:v>46284</x:v>
+      </x:c>
       <x:c r="N69" s="6"/>
       <x:c r="O69" s="6"/>
       <x:c r="P69" s="7"/>
@@ -7519,8 +7663,12 @@
       <x:c r="K70" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L70" s="6"/>
-      <x:c r="M70" s="11"/>
+      <x:c r="L70" s="6" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="M70" s="10">
+        <x:v>46294</x:v>
+      </x:c>
       <x:c r="N70" s="6"/>
       <x:c r="O70" s="6"/>
       <x:c r="P70" s="7"/>
@@ -7559,8 +7707,12 @@
       <x:c r="K71" s="6" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L71" s="6"/>
-      <x:c r="M71" s="11"/>
+      <x:c r="L71" s="22" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="M71" s="10">
+        <x:v>46284</x:v>
+      </x:c>
       <x:c r="N71" s="6"/>
       <x:c r="O71" s="6"/>
       <x:c r="P71" s="7"/>
@@ -8602,73 +8754,73 @@
       </x:c>
     </x:row>
     <x:row r="3" ht="64">
-      <x:c r="A3" s="12" t="s">
+      <x:c r="A3" s="11" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="B3" s="12" t="s">
+      <x:c r="B3" s="11" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="C3" s="12" t="s">
+      <x:c r="C3" s="11" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="D3" s="12" t="s">
+      <x:c r="D3" s="11" t="s">
         <x:v>444</x:v>
       </x:c>
-      <x:c r="E3" s="12" t="s">
+      <x:c r="E3" s="11" t="s">
         <x:v>445</x:v>
       </x:c>
-      <x:c r="F3" s="13" t="s">
+      <x:c r="F3" s="12" t="s">
         <x:v>441</x:v>
       </x:c>
-      <x:c r="G3" s="12" t="s">
+      <x:c r="G3" s="11" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="H3" s="12" t="s">
+      <x:c r="H3" s="11" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I3" s="13" t="s">
+      <x:c r="I3" s="12" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="J3" s="13">
+        <x:v>46281</x:v>
+      </x:c>
+      <x:c r="K3" s="11" t="s">
         <x:v>446</x:v>
       </x:c>
-      <x:c r="J3" s="14">
+    </x:row>
+    <x:row r="4" ht="48">
+      <x:c r="A4" s="11" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="B4" s="11" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="D4" s="11" t="s">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="E4" s="11" t="s">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="F4" s="12" t="s">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="G4" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H4" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I4" s="12" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="J4" s="13">
         <x:v>46281</x:v>
       </x:c>
-      <x:c r="K3" s="12" t="s">
-        <x:v>447</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="48">
-      <x:c r="A4" s="12" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="B4" s="12" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="C4" s="12" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="D4" s="12" t="s">
-        <x:v>448</x:v>
-      </x:c>
-      <x:c r="E4" s="12" t="s">
-        <x:v>449</x:v>
-      </x:c>
-      <x:c r="F4" s="13" t="s">
+      <x:c r="K4" s="11" t="s">
         <x:v>450</x:v>
-      </x:c>
-      <x:c r="G4" s="12" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="H4" s="12" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="I4" s="13" t="s">
-        <x:v>446</x:v>
-      </x:c>
-      <x:c r="J4" s="14">
-        <x:v>46281</x:v>
-      </x:c>
-      <x:c r="K4" s="12" t="s">
-        <x:v>451</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
